--- a/간트차트_250526.xlsx
+++ b/간트차트_250526.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{067969B9-1DE1-4675-8B93-AE522AB97C2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD38511-BA64-4201-93C7-9812686991FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="간트 차트 시각화" sheetId="1" r:id="rId1"/>
@@ -1584,20 +1584,90 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="25">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2013,82 +2083,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BE226"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="31.58203125" customWidth="1"/>
-    <col min="2" max="3" width="14.33203125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="3" width="14.375" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="3" customWidth="1"/>
-    <col min="5" max="330" width="5.83203125" customWidth="1"/>
+    <col min="5" max="330" width="5.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
     </row>
-    <row r="2" spans="1:57" ht="34" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:57" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="33" t="s">
+      <c r="E2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="33" t="s">
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="33" t="s">
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="33" t="s">
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="33" t="s">
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="34"/>
-      <c r="X2" s="34"/>
-      <c r="Y2" s="34"/>
-      <c r="Z2" s="34"/>
-      <c r="AA2" s="33" t="s">
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+      <c r="Y2" s="35"/>
+      <c r="Z2" s="35"/>
+      <c r="AA2" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="AB2" s="34"/>
-      <c r="AC2" s="34"/>
-      <c r="AD2" s="34"/>
-      <c r="AE2" s="33" t="s">
+      <c r="AB2" s="35"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="35"/>
+      <c r="AE2" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="34"/>
-      <c r="AG2" s="34"/>
-      <c r="AH2" s="34"/>
-      <c r="AI2" s="33" t="s">
+      <c r="AF2" s="35"/>
+      <c r="AG2" s="35"/>
+      <c r="AH2" s="35"/>
+      <c r="AI2" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="AJ2" s="34"/>
-      <c r="AK2" s="34"/>
-      <c r="AL2" s="34"/>
-      <c r="AM2" s="34"/>
-      <c r="AN2" s="33" t="s">
+      <c r="AJ2" s="35"/>
+      <c r="AK2" s="35"/>
+      <c r="AL2" s="35"/>
+      <c r="AM2" s="35"/>
+      <c r="AN2" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="AO2" s="34"/>
-      <c r="AP2" s="34"/>
-      <c r="AQ2" s="34"/>
-    </row>
-    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="AO2" s="35"/>
+      <c r="AP2" s="35"/>
+      <c r="AQ2" s="35"/>
+    </row>
+    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>240</v>
       </c>
@@ -2233,7 +2303,7 @@
       <c r="BD3"/>
       <c r="BE3"/>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>241</v>
       </c>
@@ -2253,7 +2323,7 @@
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
@@ -2266,7 +2336,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -2280,7 +2350,7 @@
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -2295,7 +2365,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
@@ -2309,7 +2379,7 @@
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2328,7 +2398,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
@@ -2345,7 +2415,7 @@
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2358,7 +2428,7 @@
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2366,7 +2436,7 @@
       <c r="C12" s="11"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2379,7 +2449,7 @@
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2387,7 +2457,7 @@
       <c r="C14" s="11"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A15" s="8" t="s">
         <v>27</v>
       </c>
@@ -2398,7 +2468,7 @@
       </c>
       <c r="E15" s="17"/>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
       <c r="A16" s="8" t="s">
         <v>28</v>
       </c>
@@ -2406,7 +2476,7 @@
       <c r="C16" s="11"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="8" t="s">
         <v>29</v>
       </c>
@@ -2417,7 +2487,7 @@
       </c>
       <c r="E17" s="17"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="8" t="s">
         <v>30</v>
       </c>
@@ -2425,7 +2495,7 @@
       <c r="C18" s="11"/>
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="8" t="s">
         <v>31</v>
       </c>
@@ -2437,7 +2507,7 @@
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="8" t="s">
         <v>32</v>
       </c>
@@ -2445,7 +2515,7 @@
       <c r="C20" s="11"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -2459,7 +2529,7 @@
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -2467,7 +2537,7 @@
       <c r="C22" s="11"/>
       <c r="D22" s="5"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -2481,7 +2551,7 @@
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -2491,7 +2561,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
@@ -2508,7 +2578,7 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -2521,7 +2591,7 @@
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -2529,7 +2599,7 @@
       <c r="C27" s="11"/>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="8" t="s">
         <v>40</v>
       </c>
@@ -2540,7 +2610,7 @@
       </c>
       <c r="E28" s="17"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" s="8" t="s">
         <v>41</v>
       </c>
@@ -2548,7 +2618,7 @@
       <c r="C29" s="11"/>
       <c r="D29" s="5"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" s="8" t="s">
         <v>42</v>
       </c>
@@ -2560,7 +2630,7 @@
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" s="8" t="s">
         <v>43</v>
       </c>
@@ -2568,7 +2638,7 @@
       <c r="C31" s="11"/>
       <c r="D31" s="5"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="8" t="s">
         <v>44</v>
       </c>
@@ -2580,7 +2650,7 @@
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" s="8" t="s">
         <v>45</v>
       </c>
@@ -2588,7 +2658,7 @@
       <c r="C33" s="11"/>
       <c r="D33" s="5"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" s="8" t="s">
         <v>46</v>
       </c>
@@ -2597,7 +2667,7 @@
       <c r="D34" s="5"/>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" s="8" t="s">
         <v>47</v>
       </c>
@@ -2605,7 +2675,7 @@
       <c r="C35" s="11"/>
       <c r="D35" s="5"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -2619,7 +2689,7 @@
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -2627,7 +2697,7 @@
       <c r="C37" s="11"/>
       <c r="D37" s="5"/>
     </row>
-    <row r="38" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -2645,7 +2715,7 @@
       <c r="Q38" s="22"/>
       <c r="R38" s="22"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>51</v>
       </c>
@@ -2659,7 +2729,7 @@
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -2668,7 +2738,7 @@
       <c r="D40" s="5"/>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -2678,7 +2748,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" s="8" t="s">
         <v>54</v>
       </c>
@@ -2687,7 +2757,7 @@
       <c r="D42" s="5"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" s="8" t="s">
         <v>55</v>
       </c>
@@ -2697,7 +2767,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" s="8" t="s">
         <v>56</v>
       </c>
@@ -2706,7 +2776,7 @@
       <c r="D44" s="5"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" s="8" t="s">
         <v>57</v>
       </c>
@@ -2716,7 +2786,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" s="8" t="s">
         <v>58</v>
       </c>
@@ -2725,7 +2795,7 @@
       <c r="D46" s="5"/>
       <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" s="8" t="s">
         <v>59</v>
       </c>
@@ -2735,7 +2805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -2744,7 +2814,7 @@
       <c r="D48" s="5"/>
       <c r="L48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -2754,7 +2824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="8" t="s">
         <v>62</v>
       </c>
@@ -2763,7 +2833,7 @@
       <c r="D50" s="5"/>
       <c r="L50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="8" t="s">
         <v>63</v>
       </c>
@@ -2773,7 +2843,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="8" t="s">
         <v>64</v>
       </c>
@@ -2782,7 +2852,7 @@
       <c r="D52" s="5"/>
       <c r="L52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="8" t="s">
         <v>65</v>
       </c>
@@ -2792,7 +2862,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="8" t="s">
         <v>66</v>
       </c>
@@ -2801,7 +2871,7 @@
       <c r="D54" s="5"/>
       <c r="L54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="8" t="s">
         <v>67</v>
       </c>
@@ -2811,7 +2881,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="8" t="s">
         <v>68</v>
       </c>
@@ -2820,7 +2890,7 @@
       <c r="D56" s="5"/>
       <c r="L56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="8" t="s">
         <v>69</v>
       </c>
@@ -2830,7 +2900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -2839,7 +2909,7 @@
       <c r="D58" s="5"/>
       <c r="M58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>71</v>
       </c>
@@ -2850,7 +2920,7 @@
       </c>
       <c r="M59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="8" t="s">
         <v>72</v>
       </c>
@@ -2858,7 +2928,7 @@
       <c r="C60" s="11"/>
       <c r="D60" s="5"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="8" t="s">
         <v>73</v>
       </c>
@@ -2869,7 +2939,7 @@
       </c>
       <c r="M61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="8" t="s">
         <v>74</v>
       </c>
@@ -2877,7 +2947,7 @@
       <c r="C62" s="11"/>
       <c r="D62" s="5"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="8" t="s">
         <v>75</v>
       </c>
@@ -2887,7 +2957,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -2897,7 +2967,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -2908,7 +2978,7 @@
       </c>
       <c r="M65" s="17"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66" s="8" t="s">
         <v>78</v>
       </c>
@@ -2917,7 +2987,7 @@
       <c r="D66" s="5"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67" s="8" t="s">
         <v>79</v>
       </c>
@@ -2927,7 +2997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68" s="8" t="s">
         <v>80</v>
       </c>
@@ -2935,7 +3005,7 @@
       <c r="C68" s="11"/>
       <c r="D68" s="5"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69" s="8" t="s">
         <v>81</v>
       </c>
@@ -2945,7 +3015,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>82</v>
       </c>
@@ -2954,7 +3024,7 @@
       <c r="D70" s="5"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2964,7 +3034,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -2973,7 +3043,7 @@
       <c r="D72" s="5"/>
       <c r="O72" s="17"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -2983,7 +3053,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74" s="8" t="s">
         <v>86</v>
       </c>
@@ -2992,7 +3062,7 @@
       <c r="D74" s="5"/>
       <c r="O74" s="17"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75" s="8" t="s">
         <v>87</v>
       </c>
@@ -3002,7 +3072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76" s="8" t="s">
         <v>88</v>
       </c>
@@ -3011,7 +3081,7 @@
       <c r="D76" s="5"/>
       <c r="O76" s="17"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77" s="8" t="s">
         <v>89</v>
       </c>
@@ -3021,7 +3091,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>90</v>
       </c>
@@ -3035,7 +3105,7 @@
       <c r="Q78" s="17"/>
       <c r="R78" s="17"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -3044,7 +3114,7 @@
       <c r="D79" s="5"/>
       <c r="O79" s="17"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -3054,7 +3124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" s="8" t="s">
         <v>93</v>
       </c>
@@ -3063,7 +3133,7 @@
       <c r="D81" s="5"/>
       <c r="O81" s="17"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" s="8" t="s">
         <v>94</v>
       </c>
@@ -3073,7 +3143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" s="8" t="s">
         <v>95</v>
       </c>
@@ -3082,7 +3152,7 @@
       <c r="D83" s="5"/>
       <c r="O83" s="17"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" s="8" t="s">
         <v>96</v>
       </c>
@@ -3092,7 +3162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" s="8" t="s">
         <v>97</v>
       </c>
@@ -3101,7 +3171,7 @@
       <c r="D85" s="5"/>
       <c r="O85" s="17"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" s="8" t="s">
         <v>98</v>
       </c>
@@ -3111,7 +3181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" s="8" t="s">
         <v>99</v>
       </c>
@@ -3120,7 +3190,7 @@
       <c r="D87" s="5"/>
       <c r="O87" s="17"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" s="8" t="s">
         <v>100</v>
       </c>
@@ -3130,7 +3200,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" s="8" t="s">
         <v>101</v>
       </c>
@@ -3139,7 +3209,7 @@
       <c r="D89" s="5"/>
       <c r="O89" s="17"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" s="8" t="s">
         <v>102</v>
       </c>
@@ -3149,7 +3219,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -3159,7 +3229,7 @@
       <c r="O91" s="17"/>
       <c r="P91" s="17"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -3169,7 +3239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -3179,7 +3249,7 @@
       <c r="P93" s="17"/>
       <c r="Q93" s="17"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -3189,7 +3259,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" s="8" t="s">
         <v>107</v>
       </c>
@@ -3198,7 +3268,7 @@
       <c r="D95" s="5"/>
       <c r="P95" s="17"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" s="8" t="s">
         <v>108</v>
       </c>
@@ -3208,7 +3278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A97" s="8" t="s">
         <v>109</v>
       </c>
@@ -3217,7 +3287,7 @@
       <c r="D97" s="5"/>
       <c r="P97" s="17"/>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A98" s="8" t="s">
         <v>110</v>
       </c>
@@ -3227,7 +3297,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A99" s="8" t="s">
         <v>111</v>
       </c>
@@ -3236,7 +3306,7 @@
       <c r="D99" s="5"/>
       <c r="Q99" s="17"/>
     </row>
-    <row r="100" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="8" t="s">
         <v>112</v>
       </c>
@@ -3246,7 +3316,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A101" s="8" t="s">
         <v>113</v>
       </c>
@@ -3255,7 +3325,7 @@
       <c r="D101" s="5"/>
       <c r="Q101" s="17"/>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A102" s="8" t="s">
         <v>114</v>
       </c>
@@ -3265,7 +3335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -3275,7 +3345,7 @@
       <c r="Q103" s="17"/>
       <c r="R103" s="17"/>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -3285,7 +3355,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A105" s="8" t="s">
         <v>117</v>
       </c>
@@ -3295,7 +3365,7 @@
       <c r="Q105" s="17"/>
       <c r="R105" s="17"/>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A106" s="8" t="s">
         <v>118</v>
       </c>
@@ -3305,7 +3375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A107" s="8" t="s">
         <v>119</v>
       </c>
@@ -3315,7 +3385,7 @@
       <c r="Q107" s="17"/>
       <c r="R107" s="17"/>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A108" s="8" t="s">
         <v>120</v>
       </c>
@@ -3325,7 +3395,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A109" s="8" t="s">
         <v>121</v>
       </c>
@@ -3334,7 +3404,7 @@
       <c r="D109" s="5"/>
       <c r="R109" s="17"/>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A110" s="8" t="s">
         <v>122</v>
       </c>
@@ -3344,7 +3414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A111" s="8" t="s">
         <v>388</v>
       </c>
@@ -3352,7 +3422,7 @@
       <c r="C111" s="11"/>
       <c r="D111" s="5"/>
     </row>
-    <row r="112" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>123</v>
       </c>
@@ -3376,7 +3446,7 @@
       <c r="V112" s="22"/>
       <c r="W112" s="22"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>124</v>
       </c>
@@ -3388,7 +3458,7 @@
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>125</v>
       </c>
@@ -3399,7 +3469,7 @@
       </c>
       <c r="J114" s="17"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>126</v>
       </c>
@@ -3409,7 +3479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>127</v>
       </c>
@@ -3420,7 +3490,7 @@
       </c>
       <c r="K116" s="17"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>128</v>
       </c>
@@ -3428,7 +3498,7 @@
       <c r="C117" s="11"/>
       <c r="D117" s="5"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>129</v>
       </c>
@@ -3444,7 +3514,7 @@
       <c r="P118" s="17"/>
       <c r="Q118" s="17"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>130</v>
       </c>
@@ -3456,7 +3526,7 @@
       <c r="L119" s="17"/>
       <c r="M119" s="17"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>131</v>
       </c>
@@ -3464,7 +3534,7 @@
       <c r="C120" s="11"/>
       <c r="D120" s="5"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" s="8" t="s">
         <v>132</v>
       </c>
@@ -3475,7 +3545,7 @@
       </c>
       <c r="L121" s="17"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" s="8" t="s">
         <v>133</v>
       </c>
@@ -3483,7 +3553,7 @@
       <c r="C122" s="11"/>
       <c r="D122" s="5"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" s="8" t="s">
         <v>134</v>
       </c>
@@ -3494,7 +3564,7 @@
       </c>
       <c r="L123" s="17"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" s="8" t="s">
         <v>135</v>
       </c>
@@ -3502,7 +3572,7 @@
       <c r="C124" s="11"/>
       <c r="D124" s="5"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" s="8" t="s">
         <v>136</v>
       </c>
@@ -3514,7 +3584,7 @@
       <c r="L125" s="17"/>
       <c r="M125" s="17"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" s="8" t="s">
         <v>137</v>
       </c>
@@ -3522,7 +3592,7 @@
       <c r="C126" s="11"/>
       <c r="D126" s="5"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" s="8" t="s">
         <v>138</v>
       </c>
@@ -3533,7 +3603,7 @@
       </c>
       <c r="M127" s="17"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" s="8" t="s">
         <v>139</v>
       </c>
@@ -3541,7 +3611,7 @@
       <c r="C128" s="11"/>
       <c r="D128" s="5"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="8" t="s">
         <v>140</v>
       </c>
@@ -3552,7 +3622,7 @@
       </c>
       <c r="M129" s="17"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="8" t="s">
         <v>141</v>
       </c>
@@ -3560,7 +3630,7 @@
       <c r="C130" s="11"/>
       <c r="D130" s="5"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="8" t="s">
         <v>142</v>
       </c>
@@ -3571,7 +3641,7 @@
       </c>
       <c r="M131" s="17"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="8" t="s">
         <v>143</v>
       </c>
@@ -3579,7 +3649,7 @@
       <c r="C132" s="11"/>
       <c r="D132" s="5"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>144</v>
       </c>
@@ -3590,7 +3660,7 @@
       </c>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>145</v>
       </c>
@@ -3598,7 +3668,7 @@
       <c r="C134" s="11"/>
       <c r="D134" s="5"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A135" s="8" t="s">
         <v>146</v>
       </c>
@@ -3609,7 +3679,7 @@
       </c>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="8" t="s">
         <v>147</v>
       </c>
@@ -3617,7 +3687,7 @@
       <c r="C136" s="11"/>
       <c r="D136" s="5"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="8" t="s">
         <v>148</v>
       </c>
@@ -3628,7 +3698,7 @@
       </c>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="8" t="s">
         <v>149</v>
       </c>
@@ -3636,7 +3706,7 @@
       <c r="C138" s="11"/>
       <c r="D138" s="5"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="8" t="s">
         <v>150</v>
       </c>
@@ -3647,7 +3717,7 @@
       </c>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A140" s="8" t="s">
         <v>151</v>
       </c>
@@ -3655,7 +3725,7 @@
       <c r="C140" s="11"/>
       <c r="D140" s="5"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="8" t="s">
         <v>152</v>
       </c>
@@ -3666,7 +3736,7 @@
       </c>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="8" t="s">
         <v>153</v>
       </c>
@@ -3674,7 +3744,7 @@
       <c r="C142" s="11"/>
       <c r="D142" s="5"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>154</v>
       </c>
@@ -3685,7 +3755,7 @@
       </c>
       <c r="O143" s="17"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>155</v>
       </c>
@@ -3693,7 +3763,7 @@
       <c r="C144" s="11"/>
       <c r="D144" s="5"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A145" s="8" t="s">
         <v>156</v>
       </c>
@@ -3704,7 +3774,7 @@
       </c>
       <c r="O145" s="17"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A146" s="8" t="s">
         <v>157</v>
       </c>
@@ -3712,7 +3782,7 @@
       <c r="C146" s="11"/>
       <c r="D146" s="5"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A147" s="8" t="s">
         <v>158</v>
       </c>
@@ -3723,7 +3793,7 @@
       </c>
       <c r="O147" s="17"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A148" s="8" t="s">
         <v>159</v>
       </c>
@@ -3731,7 +3801,7 @@
       <c r="C148" s="11"/>
       <c r="D148" s="5"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>160</v>
       </c>
@@ -3742,7 +3812,7 @@
       </c>
       <c r="O149" s="17"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>161</v>
       </c>
@@ -3750,7 +3820,7 @@
       <c r="C150" s="11"/>
       <c r="D150" s="5"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A151" s="8" t="s">
         <v>162</v>
       </c>
@@ -3761,7 +3831,7 @@
       </c>
       <c r="O151" s="17"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A152" s="8" t="s">
         <v>163</v>
       </c>
@@ -3769,7 +3839,7 @@
       <c r="C152" s="11"/>
       <c r="D152" s="5"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A153" s="8" t="s">
         <v>164</v>
       </c>
@@ -3780,7 +3850,7 @@
       </c>
       <c r="O153" s="17"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A154" s="8" t="s">
         <v>165</v>
       </c>
@@ -3788,7 +3858,7 @@
       <c r="C154" s="11"/>
       <c r="D154" s="5"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>166</v>
       </c>
@@ -3799,7 +3869,7 @@
       </c>
       <c r="O155" s="17"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>167</v>
       </c>
@@ -3807,7 +3877,7 @@
       <c r="C156" s="11"/>
       <c r="D156" s="5"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>168</v>
       </c>
@@ -3818,7 +3888,7 @@
       </c>
       <c r="P157" s="17"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>169</v>
       </c>
@@ -3826,7 +3896,7 @@
       <c r="C158" s="11"/>
       <c r="D158" s="5"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A159" s="8" t="s">
         <v>170</v>
       </c>
@@ -3837,7 +3907,7 @@
       </c>
       <c r="P159" s="17"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A160" s="8" t="s">
         <v>171</v>
       </c>
@@ -3845,7 +3915,7 @@
       <c r="C160" s="11"/>
       <c r="D160" s="5"/>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A161" s="8" t="s">
         <v>172</v>
       </c>
@@ -3856,7 +3926,7 @@
       </c>
       <c r="P161" s="17"/>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A162" s="8" t="s">
         <v>173</v>
       </c>
@@ -3864,7 +3934,7 @@
       <c r="C162" s="11"/>
       <c r="D162" s="5"/>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A163" s="6" t="s">
         <v>174</v>
       </c>
@@ -3879,7 +3949,7 @@
       <c r="T163" s="17"/>
       <c r="U163" s="17"/>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>175</v>
       </c>
@@ -3891,7 +3961,7 @@
       <c r="Q164" s="17"/>
       <c r="R164" s="17"/>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>176</v>
       </c>
@@ -3899,7 +3969,7 @@
       <c r="C165" s="11"/>
       <c r="D165" s="5"/>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A166" s="8" t="s">
         <v>177</v>
       </c>
@@ -3910,7 +3980,7 @@
       </c>
       <c r="Q166" s="17"/>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A167" s="8" t="s">
         <v>178</v>
       </c>
@@ -3918,7 +3988,7 @@
       <c r="C167" s="11"/>
       <c r="D167" s="5"/>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A168" s="8" t="s">
         <v>179</v>
       </c>
@@ -3930,7 +4000,7 @@
       <c r="Q168" s="17"/>
       <c r="R168" s="17"/>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A169" s="8" t="s">
         <v>180</v>
       </c>
@@ -3938,7 +4008,7 @@
       <c r="C169" s="11"/>
       <c r="D169" s="5"/>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A170" s="8" t="s">
         <v>181</v>
       </c>
@@ -3949,7 +4019,7 @@
       </c>
       <c r="R170" s="17"/>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A171" s="8" t="s">
         <v>182</v>
       </c>
@@ -3957,7 +4027,7 @@
       <c r="C171" s="11"/>
       <c r="D171" s="5"/>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>183</v>
       </c>
@@ -3969,7 +4039,7 @@
       <c r="R172" s="17"/>
       <c r="S172" s="17"/>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>184</v>
       </c>
@@ -3977,7 +4047,7 @@
       <c r="C173" s="11"/>
       <c r="D173" s="5"/>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A174" s="8" t="s">
         <v>185</v>
       </c>
@@ -3988,7 +4058,7 @@
       </c>
       <c r="R174" s="17"/>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A175" s="8" t="s">
         <v>186</v>
       </c>
@@ -3996,7 +4066,7 @@
       <c r="C175" s="11"/>
       <c r="D175" s="5"/>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A176" s="8" t="s">
         <v>187</v>
       </c>
@@ -4008,7 +4078,7 @@
       <c r="R176" s="17"/>
       <c r="S176" s="17"/>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A177" s="8" t="s">
         <v>188</v>
       </c>
@@ -4016,7 +4086,7 @@
       <c r="C177" s="11"/>
       <c r="D177" s="5"/>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A178" s="8" t="s">
         <v>189</v>
       </c>
@@ -4028,7 +4098,7 @@
       <c r="R178" s="17"/>
       <c r="S178" s="17"/>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A179" s="8" t="s">
         <v>190</v>
       </c>
@@ -4036,7 +4106,7 @@
       <c r="C179" s="11"/>
       <c r="D179" s="5"/>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A180" s="8" t="s">
         <v>191</v>
       </c>
@@ -4048,7 +4118,7 @@
       <c r="R180" s="17"/>
       <c r="S180" s="17"/>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A181" s="8" t="s">
         <v>192</v>
       </c>
@@ -4056,7 +4126,7 @@
       <c r="C181" s="11"/>
       <c r="D181" s="5"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A182" s="8" t="s">
         <v>193</v>
       </c>
@@ -4067,7 +4137,7 @@
       </c>
       <c r="R182" s="17"/>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A183" s="8" t="s">
         <v>194</v>
       </c>
@@ -4075,7 +4145,7 @@
       <c r="C183" s="11"/>
       <c r="D183" s="5"/>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>195</v>
       </c>
@@ -4086,7 +4156,7 @@
       </c>
       <c r="S184" s="17"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>196</v>
       </c>
@@ -4094,7 +4164,7 @@
       <c r="C185" s="11"/>
       <c r="D185" s="5"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A186" s="8" t="s">
         <v>197</v>
       </c>
@@ -4105,7 +4175,7 @@
       </c>
       <c r="S186" s="17"/>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A187" s="8" t="s">
         <v>198</v>
       </c>
@@ -4113,7 +4183,7 @@
       <c r="C187" s="11"/>
       <c r="D187" s="5"/>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A188" s="8" t="s">
         <v>199</v>
       </c>
@@ -4124,7 +4194,7 @@
       </c>
       <c r="S188" s="17"/>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A189" s="8" t="s">
         <v>200</v>
       </c>
@@ -4132,7 +4202,7 @@
       <c r="C189" s="11"/>
       <c r="D189" s="5"/>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>201</v>
       </c>
@@ -4144,7 +4214,7 @@
       <c r="S190" s="17"/>
       <c r="T190" s="17"/>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>202</v>
       </c>
@@ -4152,7 +4222,7 @@
       <c r="C191" s="11"/>
       <c r="D191" s="5"/>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A192" s="8" t="s">
         <v>203</v>
       </c>
@@ -4163,7 +4233,7 @@
       </c>
       <c r="S192" s="17"/>
     </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A193" s="8" t="s">
         <v>204</v>
       </c>
@@ -4171,7 +4241,7 @@
       <c r="C193" s="11"/>
       <c r="D193" s="5"/>
     </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A194" s="8" t="s">
         <v>205</v>
       </c>
@@ -4182,7 +4252,7 @@
       </c>
       <c r="T194" s="17"/>
     </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A195" s="8" t="s">
         <v>206</v>
       </c>
@@ -4190,7 +4260,7 @@
       <c r="C195" s="11"/>
       <c r="D195" s="5"/>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A196" s="8" t="s">
         <v>207</v>
       </c>
@@ -4201,7 +4271,7 @@
       </c>
       <c r="T196" s="17"/>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A197" s="8" t="s">
         <v>208</v>
       </c>
@@ -4209,7 +4279,7 @@
       <c r="C197" s="11"/>
       <c r="D197" s="5"/>
     </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A198" s="8" t="s">
         <v>209</v>
       </c>
@@ -4220,7 +4290,7 @@
       </c>
       <c r="T198" s="17"/>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A199" s="8" t="s">
         <v>210</v>
       </c>
@@ -4228,7 +4298,7 @@
       <c r="C199" s="11"/>
       <c r="D199" s="5"/>
     </row>
-    <row r="200" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>211</v>
       </c>
@@ -4240,7 +4310,7 @@
       <c r="T200" s="18"/>
       <c r="U200" s="18"/>
     </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>212</v>
       </c>
@@ -4248,7 +4318,7 @@
       <c r="C201" s="11"/>
       <c r="D201" s="5"/>
     </row>
-    <row r="202" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A202" s="8" t="s">
         <v>213</v>
       </c>
@@ -4259,7 +4329,7 @@
       </c>
       <c r="T202" s="18"/>
     </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A203" s="8" t="s">
         <v>214</v>
       </c>
@@ -4267,7 +4337,7 @@
       <c r="C203" s="11"/>
       <c r="D203" s="5"/>
     </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A204" s="8" t="s">
         <v>215</v>
       </c>
@@ -4278,7 +4348,7 @@
       </c>
       <c r="U204" s="17"/>
     </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A205" s="8" t="s">
         <v>216</v>
       </c>
@@ -4286,7 +4356,7 @@
       <c r="C205" s="11"/>
       <c r="D205" s="5"/>
     </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A206" s="8" t="s">
         <v>217</v>
       </c>
@@ -4297,7 +4367,7 @@
       </c>
       <c r="U206" s="17"/>
     </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A207" s="8" t="s">
         <v>218</v>
       </c>
@@ -4305,7 +4375,7 @@
       <c r="C207" s="11"/>
       <c r="D207" s="5"/>
     </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A208" s="6" t="s">
         <v>219</v>
       </c>
@@ -4317,7 +4387,7 @@
       <c r="U208" s="17"/>
       <c r="V208" s="17"/>
     </row>
-    <row r="209" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>220</v>
       </c>
@@ -4328,7 +4398,7 @@
       </c>
       <c r="U209" s="17"/>
     </row>
-    <row r="210" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>221</v>
       </c>
@@ -4336,7 +4406,7 @@
       <c r="C210" s="11"/>
       <c r="D210" s="5"/>
     </row>
-    <row r="211" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>222</v>
       </c>
@@ -4347,7 +4417,7 @@
       </c>
       <c r="V211" s="17"/>
     </row>
-    <row r="212" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>223</v>
       </c>
@@ -4355,7 +4425,7 @@
       <c r="C212" s="11"/>
       <c r="D212" s="5"/>
     </row>
-    <row r="213" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>224</v>
       </c>
@@ -4375,7 +4445,7 @@
       <c r="AD213" s="22"/>
       <c r="AE213" s="22"/>
     </row>
-    <row r="214" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A214" s="6" t="s">
         <v>225</v>
       </c>
@@ -4383,7 +4453,7 @@
       <c r="C214" s="11"/>
       <c r="D214" s="5"/>
     </row>
-    <row r="215" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A215" s="6" t="s">
         <v>226</v>
       </c>
@@ -4391,7 +4461,7 @@
       <c r="C215" s="11"/>
       <c r="D215" s="5"/>
     </row>
-    <row r="216" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>227</v>
       </c>
@@ -4412,7 +4482,7 @@
       <c r="AN216" s="22"/>
       <c r="AO216" s="22"/>
     </row>
-    <row r="217" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A217" s="6" t="s">
         <v>228</v>
       </c>
@@ -4420,7 +4490,7 @@
       <c r="C217" s="11"/>
       <c r="D217" s="5"/>
     </row>
-    <row r="218" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A218" s="6" t="s">
         <v>229</v>
       </c>
@@ -4428,7 +4498,7 @@
       <c r="C218" s="11"/>
       <c r="D218" s="5"/>
     </row>
-    <row r="219" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>230</v>
       </c>
@@ -4436,7 +4506,7 @@
       <c r="C219" s="11"/>
       <c r="D219" s="5"/>
     </row>
-    <row r="220" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>231</v>
       </c>
@@ -4444,7 +4514,7 @@
       <c r="C220" s="11"/>
       <c r="D220" s="5"/>
     </row>
-    <row r="221" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>232</v>
       </c>
@@ -4452,7 +4522,7 @@
       <c r="C221" s="11"/>
       <c r="D221" s="5"/>
     </row>
-    <row r="222" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>233</v>
       </c>
@@ -4460,7 +4530,7 @@
       <c r="C222" s="11"/>
       <c r="D222" s="5"/>
     </row>
-    <row r="223" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>234</v>
       </c>
@@ -4468,7 +4538,7 @@
       <c r="C223" s="11"/>
       <c r="D223" s="5"/>
     </row>
-    <row r="224" spans="1:41" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>235</v>
       </c>
@@ -4476,7 +4546,7 @@
       <c r="C224" s="11"/>
       <c r="D224" s="5"/>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>236</v>
       </c>
@@ -4484,7 +4554,7 @@
       <c r="C225" s="11"/>
       <c r="D225" s="5"/>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>237</v>
       </c>
@@ -4506,57 +4576,57 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E42:K42 M42:JK42 E44:K44 M44:JK44 E46:K46 M46:JK46 E50:L50 N50:JK50 E52:L52 N52:JK52 E54:L54 N54:JK54 E56:L56 N56:JK56 E60:L60 Q60:JK60 E62:L62 Q62:JK62 E66:L66 Q66:JK66 E68:JK68 E74:M74 R74:JK74 E76:M76 R76:JK76 E81:N81 P81:JK81 E83:N83 P83:JK83 E85:N85 P85:JK85 E87:N87 P87:JK87 E89:N89 P89:JK89 E95:O95 Q95:JK95 E97:O97 Q97:JK97 E99:P99 R99:JK99 E101:P101 R101:JK101 E105:P105 S105:JK105 E107:P107 S107:JK107 E109:Q109 S109:JK109">
-    <cfRule type="expression" dxfId="14" priority="427">
+    <cfRule type="expression" dxfId="24" priority="427">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E51:K51 N51:JK51 E53:K53 N53:JK53 E55:K55 N55:JK55 E61:L61 Q61:JK61 E75:M75 R75:JK75 E82:JK82 E84:JK84 E86:JK86 E88:JK88 E96:JK96 E98:JK98 E100:JK100 E106:JK106 E108:JK108">
-    <cfRule type="expression" dxfId="13" priority="510">
+    <cfRule type="expression" dxfId="23" priority="510">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= $B51, E$2 &lt;= $C51)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E3:JK11 E13:JK13 E15:JK15 E17:JK17 E19:JK19 E21:JK21 E23:JK23 E25:JK26 E28:JK28 E30:JK30 E32:JK32 E36:JK36 E38:JK39 E40:J40 M40:JK40 E48:K48 N48:JK48 E58:L58 Q58:JK58 E64:L64 Q64:JK64 E70:M70 R70:JK70 E72:M72 R72:JK72 E78:JK79 E91:JK91 E93:JK93 E112:JK114 E116:JK116 E118:JK119 E121:JK121 E123:JK123 E125:JK125 E127:JK127 E129:JK129 E131:JK131 E133:JK133 E135:JK135 E137:JK137 E139:JK139 E141:JK141 E143:JK143 E145:JK145 E147:JK147 E149:JK149 E151:JK151 E153:JK153 E155:JK155 E157:JK157 E159:JK159 E161:JK161 E163:JK164 E166:JK166 E168:JK168 E170:JK170 E172:JK172 E174:JK174 E176:JK176 E178:JK178 E180:JK180 E182:JK182 E184:JK184 E186:JK186 E188:JK188 E190:JK190 E192:JK192 E194:JK194 E196:JK196 E198:JK198 E200:JK200 E202:JK202 E204:JK204 E206:JK206 E208:JK209 E211:JK211 E213:JK219 E221:JK221 E223:JK223 E225:JK225 E103:JK103 O81 O83 O85 O87 O89 P95 P97 Q99 Q101 Q105:R105 Q107:R107 R109">
-    <cfRule type="expression" dxfId="12" priority="208">
+  <conditionalFormatting sqref="E3:JK11 E13:JK13 E15:JK15 E17:JK17 E19:JK19 E21:JK21 E23:JK23 E25:JK26 E28:JK28 E30:JK30 E32:JK32 E36:JK36 E38:JK39 E40:J40 M40:JK40 E48:K48 N48:JK48 E58:L58 Q58:JK58 E64:L64 Q64:JK64 E70:M70 R70:JK70 E72:M72 R72:JK72 E78:JK79 O81 O83 O85 O87 O89 E91:JK91 E93:JK93 P95 P97 Q99 Q101 E103:JK103 Q105:R105 Q107:R107 R109 E112:JK114 E116:JK116 E118:JK119 E121:JK121 E123:JK123 E125:JK125 E127:JK127 E129:JK129 E131:JK131 E133:JK133 E135:JK135 E137:JK137 E139:JK139 E141:JK141 E143:JK143 E145:JK145 E147:JK147 E149:JK149 E151:JK151 E153:JK153 E155:JK155 E157:JK157 E159:JK159 E161:JK161 E163:JK164 E166:JK166 E168:JK168 E170:JK170 E172:JK172 E174:JK174 E176:JK176 E178:JK178 E180:JK180 E182:JK182 E184:JK184 E186:JK186 E188:JK188 E190:JK190 E192:JK192 E194:JK194 E196:JK196 E198:JK198 E200:JK200 E202:JK202 E204:JK204 E206:JK206 E208:JK209 E211:JK211 E213:JK219 E221:JK221 E223:JK223 E225:JK225">
+    <cfRule type="expression" dxfId="22" priority="208">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= $B3, E$2 &lt;= $C3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:JK12 E14:JK14 E16:JK16 E18:JK18 E20:JK20 E22:JK22 E24:JK24 E27:JK27 E29:JK29 E31:JK31 E33:JK33 E34:F34 H34:JK34 E35:JK35 E37:JK37 E41:JK41 E43:JK43 E45:JK45 E49:K49 N49:JK49 E57:JK57 E59:L59 Q59:JK59 E63:L63 Q63:JK63 E65:L65 Q65:JK65 E67:JK67 E69:JK69 E71:M71 R71:JK71 E73:M73 R73:JK73 E77:M77 R77:JK77 E80:JK80 E90:JK90 E92:JK92 E94:JK94 E102:JK102 E104:JK104 E110:JK111 E115:JK115 E117:JK117 E120:JK120 E122:JK122 E124:JK124 E126:JK126 E128:JK128 E130:JK130 E132:JK132 E134:JK134 E136:JK136 E138:JK138 E140:JK140 E142:JK142 E144:JK144 E146:JK146 E148:JK148 E150:JK150 E152:JK152 E154:JK154 E156:JK156 E158:JK158 E160:JK160 E162:JK162 E165:JK165 E167:JK167 E169:JK169 E171:JK171 E173:JK173 E175:JK175 E177:JK177 E179:JK179 E181:JK181 E183:JK183 E185:JK185 E187:JK187 E189:JK189 E191:JK191 E193:JK193 E195:JK195 E197:JK197 E201:JK201 E203:JK203 E205:JK205 E207:JK207 E210:JK210 E212:JK212 E220:JK220 E222:JK222 E224:JK224 E226:JK226">
-    <cfRule type="expression" dxfId="11" priority="1227">
+    <cfRule type="expression" dxfId="21" priority="1227">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47:JK47">
-    <cfRule type="expression" dxfId="10" priority="584">
+    <cfRule type="expression" dxfId="20" priority="584">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E199:JK199">
-    <cfRule type="expression" dxfId="9" priority="1324">
+    <cfRule type="expression" dxfId="19" priority="1324">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="8" priority="30">
+    <cfRule type="expression" dxfId="18" priority="30">
       <formula>AND(ISNUMBER(G$2), G$2 &gt;= $B34, G$2 &lt;= $C34)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40 K42 K44 K46 L48 L50 L52 L54 L56 N58:O58 M58:M59 M61 N64:O64 M64:M65 N66 N70:P70 N72:P72 O74 O76">
-    <cfRule type="expression" dxfId="7" priority="1391">
+    <cfRule type="expression" dxfId="17" priority="1391">
       <formula>AND(ISNUMBER(L$2), L$2 &gt;= $B40, L$2 &lt;= $C40)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49 N59:O59 M63:O63 N65:O65 N71:P71 N73 P73 N77:P77">
-    <cfRule type="expression" dxfId="6" priority="1485">
+    <cfRule type="expression" dxfId="16" priority="1485">
       <formula>AND(ISNUMBER(M$2), M$2 &gt;= #REF!, M$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51 L53 L55 N61:O61 N75:P75">
-    <cfRule type="expression" dxfId="5" priority="1467">
+    <cfRule type="expression" dxfId="15" priority="1467">
       <formula>AND(ISNUMBER(M$2), M$2 &gt;= $B51, M$2 &lt;= $C51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60:O60 M62:O62 M66 O66 N74 P74 N76 P76">
-    <cfRule type="expression" dxfId="4" priority="1559">
+    <cfRule type="expression" dxfId="14" priority="1559">
       <formula>AND(ISNUMBER(N$2), N$2 &gt;= #REF!, N$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4567,14 +4637,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B5272A1-BEB8-421C-96FA-5A790BB37DC6}">
   <dimension ref="A3:AJ87"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="6" max="36" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="6" max="36" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -4684,7 +4754,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" s="26">
         <v>3</v>
       </c>
@@ -4728,7 +4798,7 @@
       <c r="AI4" s="30"/>
       <c r="AJ4" s="30"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="26">
         <v>3.1</v>
       </c>
@@ -4769,7 +4839,7 @@
       <c r="AI5" s="30"/>
       <c r="AJ5" s="30"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
         <v>248</v>
       </c>
@@ -4814,7 +4884,7 @@
       <c r="AI6" s="30"/>
       <c r="AJ6" s="30"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>249</v>
       </c>
@@ -4859,7 +4929,7 @@
       <c r="AI7" s="30"/>
       <c r="AJ7" s="30"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
         <v>251</v>
       </c>
@@ -4904,7 +4974,7 @@
       <c r="AI8" s="30"/>
       <c r="AJ8" s="30"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A9" s="26" t="s">
         <v>252</v>
       </c>
@@ -4949,7 +5019,7 @@
       <c r="AI9" s="30"/>
       <c r="AJ9" s="30"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" s="26" t="s">
         <v>253</v>
       </c>
@@ -4994,7 +5064,7 @@
       <c r="AI10" s="30"/>
       <c r="AJ10" s="30"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" s="26" t="s">
         <v>254</v>
       </c>
@@ -5039,7 +5109,7 @@
       <c r="AI11" s="30"/>
       <c r="AJ11" s="30"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
         <v>255</v>
       </c>
@@ -5084,7 +5154,7 @@
       <c r="AI12" s="30"/>
       <c r="AJ12" s="30"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A13" s="26" t="s">
         <v>256</v>
       </c>
@@ -5129,7 +5199,7 @@
       <c r="AI13" s="30"/>
       <c r="AJ13" s="30"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
         <v>257</v>
       </c>
@@ -5174,7 +5244,7 @@
       <c r="AI14" s="30"/>
       <c r="AJ14" s="30"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A15" s="26" t="s">
         <v>258</v>
       </c>
@@ -5219,7 +5289,7 @@
       <c r="AI15" s="30"/>
       <c r="AJ15" s="30"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A16" s="26" t="s">
         <v>259</v>
       </c>
@@ -5264,7 +5334,7 @@
       <c r="AI16" s="30"/>
       <c r="AJ16" s="30"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A17" s="26" t="s">
         <v>260</v>
       </c>
@@ -5309,7 +5379,7 @@
       <c r="AI17" s="30"/>
       <c r="AJ17" s="30"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
         <v>261</v>
       </c>
@@ -5354,7 +5424,7 @@
       <c r="AI18" s="30"/>
       <c r="AJ18" s="30"/>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A19" s="26" t="s">
         <v>262</v>
       </c>
@@ -5399,7 +5469,7 @@
       <c r="AI19" s="30"/>
       <c r="AJ19" s="30"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A20" s="26" t="s">
         <v>263</v>
       </c>
@@ -5444,7 +5514,7 @@
       <c r="AI20" s="30"/>
       <c r="AJ20" s="30"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A21" s="26" t="s">
         <v>264</v>
       </c>
@@ -5489,7 +5559,7 @@
       <c r="AI21" s="30"/>
       <c r="AJ21" s="30"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" s="26" t="s">
         <v>265</v>
       </c>
@@ -5534,7 +5604,7 @@
       <c r="AI22" s="30"/>
       <c r="AJ22" s="30"/>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
         <v>266</v>
       </c>
@@ -5579,7 +5649,7 @@
       <c r="AI23" s="30"/>
       <c r="AJ23" s="30"/>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" s="26" t="s">
         <v>267</v>
       </c>
@@ -5624,7 +5694,7 @@
       <c r="AI24" s="30"/>
       <c r="AJ24" s="30"/>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="26">
         <v>3.2</v>
       </c>
@@ -5665,7 +5735,7 @@
       <c r="AI25" s="30"/>
       <c r="AJ25" s="30"/>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
         <v>268</v>
       </c>
@@ -5706,7 +5776,7 @@
       <c r="AI26" s="30"/>
       <c r="AJ26" s="30"/>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="26" t="s">
         <v>269</v>
       </c>
@@ -5747,7 +5817,7 @@
       <c r="AI27" s="30"/>
       <c r="AJ27" s="30"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="26" t="s">
         <v>270</v>
       </c>
@@ -5788,7 +5858,7 @@
       <c r="AI28" s="30"/>
       <c r="AJ28" s="30"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
         <v>270</v>
       </c>
@@ -5829,7 +5899,7 @@
       <c r="AI29" s="30"/>
       <c r="AJ29" s="30"/>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
         <v>271</v>
       </c>
@@ -5870,7 +5940,7 @@
       <c r="AI30" s="30"/>
       <c r="AJ30" s="30"/>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" s="26" t="s">
         <v>272</v>
       </c>
@@ -5911,7 +5981,7 @@
       <c r="AI31" s="30"/>
       <c r="AJ31" s="30"/>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" s="26" t="s">
         <v>273</v>
       </c>
@@ -5952,7 +6022,7 @@
       <c r="AI32" s="30"/>
       <c r="AJ32" s="30"/>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33" s="26" t="s">
         <v>274</v>
       </c>
@@ -5993,7 +6063,7 @@
       <c r="AI33" s="30"/>
       <c r="AJ33" s="30"/>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34" s="26" t="s">
         <v>275</v>
       </c>
@@ -6034,7 +6104,7 @@
       <c r="AI34" s="30"/>
       <c r="AJ34" s="30"/>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A35" s="26" t="s">
         <v>276</v>
       </c>
@@ -6075,7 +6145,7 @@
       <c r="AI35" s="30"/>
       <c r="AJ35" s="30"/>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A36" s="26" t="s">
         <v>277</v>
       </c>
@@ -6116,7 +6186,7 @@
       <c r="AI36" s="30"/>
       <c r="AJ36" s="30"/>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A37" s="26" t="s">
         <v>278</v>
       </c>
@@ -6157,7 +6227,7 @@
       <c r="AI37" s="30"/>
       <c r="AJ37" s="30"/>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" s="26" t="s">
         <v>279</v>
       </c>
@@ -6198,7 +6268,7 @@
       <c r="AI38" s="30"/>
       <c r="AJ38" s="30"/>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A39" s="26" t="s">
         <v>280</v>
       </c>
@@ -6239,7 +6309,7 @@
       <c r="AI39" s="30"/>
       <c r="AJ39" s="30"/>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>281</v>
       </c>
@@ -6280,7 +6350,7 @@
       <c r="AI40" s="30"/>
       <c r="AJ40" s="30"/>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>282</v>
       </c>
@@ -6321,7 +6391,7 @@
       <c r="AI41" s="30"/>
       <c r="AJ41" s="30"/>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A42" s="29">
         <v>4</v>
       </c>
@@ -6365,7 +6435,7 @@
       <c r="AI42" s="30"/>
       <c r="AJ42" s="30"/>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A43" s="26">
         <v>4.2</v>
       </c>
@@ -6406,11 +6476,11 @@
       <c r="AI43" s="30"/>
       <c r="AJ43" s="30"/>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A44" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="B44" s="35" t="s">
+      <c r="B44" s="33" t="s">
         <v>311</v>
       </c>
       <c r="C44" s="24">
@@ -6449,11 +6519,11 @@
       <c r="AI44" s="30"/>
       <c r="AJ44" s="30"/>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A45" s="26" t="s">
         <v>285</v>
       </c>
-      <c r="B45" s="35" t="s">
+      <c r="B45" s="33" t="s">
         <v>332</v>
       </c>
       <c r="C45" s="24">
@@ -6494,18 +6564,18 @@
       <c r="AI45" s="30"/>
       <c r="AJ45" s="30"/>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A46" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="33" t="s">
         <v>331</v>
       </c>
       <c r="C46" s="24">
         <v>45801</v>
       </c>
       <c r="D46" s="24">
-        <v>45801</v>
+        <v>45802</v>
       </c>
       <c r="F46" s="31"/>
       <c r="G46" s="30"/>
@@ -6539,15 +6609,19 @@
       <c r="AI46" s="30"/>
       <c r="AJ46" s="30"/>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A47" s="26" t="s">
         <v>287</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>330</v>
       </c>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
+      <c r="C47" s="24">
+        <v>45803</v>
+      </c>
+      <c r="D47" s="24">
+        <v>45803</v>
+      </c>
       <c r="F47" s="30"/>
       <c r="G47" s="30"/>
       <c r="H47" s="30"/>
@@ -6580,15 +6654,19 @@
       <c r="AI47" s="30"/>
       <c r="AJ47" s="30"/>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A48" s="26" t="s">
         <v>288</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>329</v>
       </c>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
+      <c r="C48" s="24">
+        <v>45803</v>
+      </c>
+      <c r="D48" s="24">
+        <v>45803</v>
+      </c>
       <c r="F48" s="31"/>
       <c r="G48" s="30"/>
       <c r="H48" s="30"/>
@@ -6621,15 +6699,19 @@
       <c r="AI48" s="30"/>
       <c r="AJ48" s="30"/>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A49" s="26" t="s">
         <v>289</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>328</v>
       </c>
-      <c r="C49" s="24"/>
-      <c r="D49" s="24"/>
+      <c r="C49" s="24">
+        <v>45803</v>
+      </c>
+      <c r="D49" s="24">
+        <v>45803</v>
+      </c>
       <c r="F49" s="31"/>
       <c r="G49" s="30"/>
       <c r="H49" s="30"/>
@@ -6662,15 +6744,19 @@
       <c r="AI49" s="30"/>
       <c r="AJ49" s="30"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A50" s="26" t="s">
         <v>290</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>327</v>
       </c>
-      <c r="C50" s="24"/>
-      <c r="D50" s="24"/>
+      <c r="C50" s="24">
+        <v>45803</v>
+      </c>
+      <c r="D50" s="24">
+        <v>45803</v>
+      </c>
       <c r="F50" s="31"/>
       <c r="G50" s="30"/>
       <c r="H50" s="30"/>
@@ -6703,15 +6789,19 @@
       <c r="AI50" s="30"/>
       <c r="AJ50" s="30"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A51" s="26" t="s">
         <v>291</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="C51" s="24"/>
-      <c r="D51" s="24"/>
+      <c r="C51" s="24">
+        <v>45803</v>
+      </c>
+      <c r="D51" s="24">
+        <v>45803</v>
+      </c>
       <c r="F51" s="30"/>
       <c r="G51" s="30"/>
       <c r="H51" s="30"/>
@@ -6744,15 +6834,19 @@
       <c r="AI51" s="30"/>
       <c r="AJ51" s="30"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A52" s="26" t="s">
         <v>292</v>
       </c>
       <c r="B52" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
+      <c r="C52" s="24">
+        <v>45804</v>
+      </c>
+      <c r="D52" s="24">
+        <v>45804</v>
+      </c>
       <c r="F52" s="30"/>
       <c r="G52" s="30"/>
       <c r="H52" s="30"/>
@@ -6785,15 +6879,19 @@
       <c r="AI52" s="30"/>
       <c r="AJ52" s="30"/>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A53" s="26" t="s">
         <v>293</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>324</v>
       </c>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
+      <c r="C53" s="24">
+        <v>45805</v>
+      </c>
+      <c r="D53" s="24">
+        <v>45805</v>
+      </c>
       <c r="F53" s="30"/>
       <c r="G53" s="30"/>
       <c r="H53" s="30"/>
@@ -6826,7 +6924,7 @@
       <c r="AI53" s="30"/>
       <c r="AJ53" s="30"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A54" s="26" t="s">
         <v>294</v>
       </c>
@@ -6867,7 +6965,7 @@
       <c r="AI54" s="30"/>
       <c r="AJ54" s="30"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A55" s="26" t="s">
         <v>295</v>
       </c>
@@ -6908,7 +7006,7 @@
       <c r="AI55" s="30"/>
       <c r="AJ55" s="30"/>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A56" s="26" t="s">
         <v>296</v>
       </c>
@@ -6949,7 +7047,7 @@
       <c r="AI56" s="30"/>
       <c r="AJ56" s="30"/>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A57" s="26" t="s">
         <v>297</v>
       </c>
@@ -6990,7 +7088,7 @@
       <c r="AI57" s="30"/>
       <c r="AJ57" s="30"/>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A58" s="26" t="s">
         <v>298</v>
       </c>
@@ -7031,11 +7129,11 @@
       <c r="AI58" s="30"/>
       <c r="AJ58" s="30"/>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A59" s="26" t="s">
         <v>299</v>
       </c>
-      <c r="B59" s="35" t="s">
+      <c r="B59" s="33" t="s">
         <v>319</v>
       </c>
       <c r="C59" s="24">
@@ -7076,11 +7174,11 @@
       <c r="AI59" s="30"/>
       <c r="AJ59" s="30"/>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A60" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="B60" s="35" t="s">
+      <c r="B60" s="33" t="s">
         <v>318</v>
       </c>
       <c r="C60" s="24">
@@ -7121,7 +7219,7 @@
       <c r="AI60" s="30"/>
       <c r="AJ60" s="30"/>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A61" s="26" t="s">
         <v>301</v>
       </c>
@@ -7166,7 +7264,7 @@
       <c r="AI61" s="30"/>
       <c r="AJ61" s="30"/>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A62" s="26" t="s">
         <v>302</v>
       </c>
@@ -7207,7 +7305,7 @@
       <c r="AI62" s="30"/>
       <c r="AJ62" s="30"/>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A63" s="26" t="s">
         <v>303</v>
       </c>
@@ -7248,7 +7346,7 @@
       <c r="AI63" s="30"/>
       <c r="AJ63" s="30"/>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A64" s="26" t="s">
         <v>304</v>
       </c>
@@ -7289,7 +7387,7 @@
       <c r="AI64" s="30"/>
       <c r="AJ64" s="30"/>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A65" s="26" t="s">
         <v>305</v>
       </c>
@@ -7330,7 +7428,7 @@
       <c r="AI65" s="30"/>
       <c r="AJ65" s="30"/>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A66" s="26">
         <v>4.3</v>
       </c>
@@ -7371,11 +7469,11 @@
       <c r="AI66" s="30"/>
       <c r="AJ66" s="30"/>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A67" s="26" t="s">
         <v>306</v>
       </c>
-      <c r="B67" s="35" t="s">
+      <c r="B67" s="33" t="s">
         <v>311</v>
       </c>
       <c r="C67" s="24"/>
@@ -7412,11 +7510,11 @@
       <c r="AI67" s="30"/>
       <c r="AJ67" s="30"/>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A68" s="26" t="s">
         <v>307</v>
       </c>
-      <c r="B68" s="35" t="s">
+      <c r="B68" s="33" t="s">
         <v>310</v>
       </c>
       <c r="C68" s="24"/>
@@ -7453,7 +7551,7 @@
       <c r="AI68" s="30"/>
       <c r="AJ68" s="30"/>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A69" s="26" t="s">
         <v>308</v>
       </c>
@@ -7494,83 +7592,83 @@
       <c r="AI69" s="30"/>
       <c r="AJ69" s="30"/>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C70" s="24"/>
       <c r="D70" s="24"/>
       <c r="J70" s="8"/>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C71" s="24"/>
       <c r="D71" s="24"/>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C72" s="24"/>
       <c r="D72" s="24"/>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C73" s="24"/>
       <c r="D73" s="24"/>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C74" s="24"/>
       <c r="D74" s="24"/>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C75" s="24"/>
       <c r="D75" s="24"/>
       <c r="J75" s="8"/>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C76" s="24"/>
       <c r="D76" s="24"/>
       <c r="J76" s="8"/>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C77" s="24"/>
       <c r="D77" s="24"/>
       <c r="J77" s="8"/>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C78" s="24"/>
       <c r="D78" s="24"/>
       <c r="J78" s="8"/>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C79" s="24"/>
       <c r="D79" s="24"/>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.3">
       <c r="C80" s="24"/>
       <c r="D80" s="24"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C81" s="24"/>
       <c r="D81" s="24"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C82" s="24"/>
       <c r="D82" s="24"/>
       <c r="J82" s="8"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C83" s="24"/>
       <c r="D83" s="24"/>
       <c r="J83" s="8"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C84" s="24"/>
       <c r="D84" s="24"/>
       <c r="J84" s="8"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C85" s="24"/>
       <c r="D85" s="24"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C86" s="24"/>
       <c r="D86" s="24"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="26"/>
       <c r="B87" s="26"/>
       <c r="C87" s="24"/>
@@ -7579,7 +7677,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F4:AJ69">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>AND(F$3&gt;=$C4,F$3&lt;=$D4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7591,15 +7689,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE8D46A-5F9F-434F-B5A2-7214C3C85F86}">
   <dimension ref="A3:AJ66"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
-    <col min="2" max="2" width="22.83203125" customWidth="1"/>
-    <col min="3" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="36" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="4" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="36" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -7707,7 +7805,7 @@
       </c>
       <c r="AJ3" s="23"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4" s="26" t="s">
         <v>279</v>
       </c>
@@ -7755,7 +7853,7 @@
       <c r="AI4" s="30"/>
       <c r="AJ4" s="30"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A5" s="26" t="s">
         <v>280</v>
       </c>
@@ -7803,7 +7901,7 @@
       <c r="AI5" s="30"/>
       <c r="AJ5" s="30"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
         <v>281</v>
       </c>
@@ -7851,7 +7949,7 @@
       <c r="AI6" s="30"/>
       <c r="AJ6" s="30"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A7" s="26" t="s">
         <v>282</v>
       </c>
@@ -7899,7 +7997,7 @@
       <c r="AI7" s="30"/>
       <c r="AJ7" s="30"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B8" s="26" t="s">
         <v>344</v>
       </c>
@@ -7941,7 +8039,7 @@
       <c r="AI8" s="30"/>
       <c r="AJ8" s="30"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B9" s="26" t="s">
         <v>343</v>
       </c>
@@ -7949,6 +8047,7 @@
       <c r="D9" s="24"/>
       <c r="F9" s="31"/>
       <c r="G9" s="30"/>
+      <c r="H9" s="30"/>
       <c r="I9" s="30"/>
       <c r="J9" s="30"/>
       <c r="K9" s="30"/>
@@ -7978,7 +8077,7 @@
       <c r="AI9" s="30"/>
       <c r="AJ9" s="30"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B10" s="26" t="s">
         <v>342</v>
       </c>
@@ -7990,9 +8089,10 @@
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="30"/>
+      <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
-      <c r="K10" s="8"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="30"/>
       <c r="M10" s="30"/>
       <c r="N10" s="30"/>
@@ -8019,7 +8119,7 @@
       <c r="AI10" s="30"/>
       <c r="AJ10" s="30"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B11" s="26" t="s">
         <v>341</v>
       </c>
@@ -8031,9 +8131,10 @@
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
-      <c r="K11" s="8"/>
+      <c r="K11" s="31"/>
       <c r="L11" s="30"/>
       <c r="M11" s="30"/>
       <c r="N11" s="30"/>
@@ -8060,7 +8161,7 @@
       <c r="AI11" s="30"/>
       <c r="AJ11" s="30"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B12" s="26" t="s">
         <v>340</v>
       </c>
@@ -8072,6 +8173,7 @@
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="30"/>
+      <c r="H12" s="30"/>
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
       <c r="K12" s="30"/>
@@ -8101,7 +8203,7 @@
       <c r="AI12" s="30"/>
       <c r="AJ12" s="30"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B13" s="26" t="s">
         <v>323</v>
       </c>
@@ -8113,6 +8215,7 @@
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="30"/>
+      <c r="H13" s="30"/>
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
       <c r="K13" s="30"/>
@@ -8142,7 +8245,7 @@
       <c r="AI13" s="30"/>
       <c r="AJ13" s="30"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B14" s="26" t="s">
         <v>339</v>
       </c>
@@ -8154,6 +8257,7 @@
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="30"/>
+      <c r="H14" s="30"/>
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
       <c r="K14" s="30"/>
@@ -8183,7 +8287,7 @@
       <c r="AI14" s="30"/>
       <c r="AJ14" s="30"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B15" s="26" t="s">
         <v>338</v>
       </c>
@@ -8195,6 +8299,7 @@
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
       <c r="K15" s="30"/>
@@ -8224,7 +8329,7 @@
       <c r="AI15" s="30"/>
       <c r="AJ15" s="30"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B16" s="26" t="s">
         <v>337</v>
       </c>
@@ -8236,6 +8341,7 @@
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
@@ -8265,7 +8371,7 @@
       <c r="AI16" s="30"/>
       <c r="AJ16" s="30"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B17" s="26" t="s">
         <v>336</v>
       </c>
@@ -8277,6 +8383,7 @@
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
       <c r="K17" s="30"/>
@@ -8306,7 +8413,7 @@
       <c r="AI17" s="30"/>
       <c r="AJ17" s="30"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B18" s="26" t="s">
         <v>335</v>
       </c>
@@ -8318,6 +8425,7 @@
       </c>
       <c r="F18" s="30"/>
       <c r="G18" s="30"/>
+      <c r="H18" s="30"/>
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
       <c r="K18" s="30"/>
@@ -8347,7 +8455,7 @@
       <c r="AI18" s="30"/>
       <c r="AJ18" s="30"/>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B19" s="26" t="s">
         <v>334</v>
       </c>
@@ -8359,6 +8467,7 @@
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="30"/>
+      <c r="H19" s="30"/>
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
       <c r="K19" s="30"/>
@@ -8388,7 +8497,7 @@
       <c r="AI19" s="30"/>
       <c r="AJ19" s="30"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B20" s="26" t="s">
         <v>333</v>
       </c>
@@ -8400,6 +8509,7 @@
       </c>
       <c r="F20" s="30"/>
       <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
       <c r="K20" s="30"/>
@@ -8429,7 +8539,7 @@
       <c r="AI20" s="30"/>
       <c r="AJ20" s="30"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
       <c r="B21" s="26" t="s">
         <v>391</v>
       </c>
@@ -8441,6 +8551,7 @@
       </c>
       <c r="F21" s="30"/>
       <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
       <c r="K21" s="30"/>
@@ -8470,7 +8581,7 @@
       <c r="AI21" s="30"/>
       <c r="AJ21" s="30"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" s="26">
         <v>4.3</v>
       </c>
@@ -8484,6 +8595,7 @@
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="30"/>
+      <c r="H22" s="30"/>
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
       <c r="K22" s="30"/>
@@ -8513,7 +8625,7 @@
       <c r="AI22" s="30"/>
       <c r="AJ22" s="30"/>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
         <v>306</v>
       </c>
@@ -8527,6 +8639,7 @@
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
       <c r="K23" s="30"/>
@@ -8556,7 +8669,7 @@
       <c r="AI23" s="30"/>
       <c r="AJ23" s="30"/>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A24" s="26" t="s">
         <v>351</v>
       </c>
@@ -8570,6 +8683,7 @@
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
       <c r="K24" s="30"/>
@@ -8599,7 +8713,7 @@
       <c r="AI24" s="30"/>
       <c r="AJ24" s="30"/>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A25" s="26" t="s">
         <v>352</v>
       </c>
@@ -8613,6 +8727,7 @@
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
       <c r="I25" s="30"/>
       <c r="J25" s="30"/>
       <c r="K25" s="30"/>
@@ -8642,7 +8757,7 @@
       <c r="AI25" s="30"/>
       <c r="AJ25" s="30"/>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" s="26" t="s">
         <v>353</v>
       </c>
@@ -8656,6 +8771,7 @@
       </c>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
       <c r="I26" s="30"/>
       <c r="J26" s="30"/>
       <c r="K26" s="30"/>
@@ -8685,7 +8801,7 @@
       <c r="AI26" s="30"/>
       <c r="AJ26" s="30"/>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" s="26" t="s">
         <v>368</v>
       </c>
@@ -8699,6 +8815,7 @@
       </c>
       <c r="F27" s="31"/>
       <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
       <c r="I27" s="30"/>
       <c r="J27" s="30"/>
       <c r="K27" s="30"/>
@@ -8728,7 +8845,7 @@
       <c r="AI27" s="30"/>
       <c r="AJ27" s="30"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A28" s="26" t="s">
         <v>354</v>
       </c>
@@ -8742,6 +8859,7 @@
       </c>
       <c r="F28" s="31"/>
       <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="30"/>
       <c r="J28" s="30"/>
       <c r="K28" s="30"/>
@@ -8771,7 +8889,7 @@
       <c r="AI28" s="30"/>
       <c r="AJ28" s="30"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A29" s="26" t="s">
         <v>355</v>
       </c>
@@ -8785,6 +8903,7 @@
       </c>
       <c r="F29" s="30"/>
       <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
       <c r="I29" s="30"/>
       <c r="J29" s="30"/>
       <c r="K29" s="30"/>
@@ -8814,7 +8933,7 @@
       <c r="AI29" s="30"/>
       <c r="AJ29" s="30"/>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" s="26" t="s">
         <v>356</v>
       </c>
@@ -8828,6 +8947,7 @@
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
       <c r="I30" s="30"/>
       <c r="J30" s="30"/>
       <c r="K30" s="30"/>
@@ -8857,7 +8977,7 @@
       <c r="AI30" s="30"/>
       <c r="AJ30" s="30"/>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A31" s="26" t="s">
         <v>357</v>
       </c>
@@ -8871,6 +8991,7 @@
       </c>
       <c r="F31" s="30"/>
       <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
       <c r="I31" s="30"/>
       <c r="J31" s="30"/>
       <c r="K31" s="30"/>
@@ -8900,7 +9021,7 @@
       <c r="AI31" s="30"/>
       <c r="AJ31" s="30"/>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A32" s="26" t="s">
         <v>358</v>
       </c>
@@ -8914,6 +9035,7 @@
       </c>
       <c r="F32" s="30"/>
       <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
       <c r="I32" s="30"/>
       <c r="J32" s="31"/>
       <c r="K32" s="30"/>
@@ -8943,7 +9065,7 @@
       <c r="AI32" s="30"/>
       <c r="AJ32" s="30"/>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A33" s="26" t="s">
         <v>369</v>
       </c>
@@ -8957,6 +9079,7 @@
       </c>
       <c r="F33" s="30"/>
       <c r="G33" s="30"/>
+      <c r="H33" s="30"/>
       <c r="I33" s="30"/>
       <c r="J33" s="31"/>
       <c r="K33" s="30"/>
@@ -8986,7 +9109,7 @@
       <c r="AI33" s="30"/>
       <c r="AJ33" s="30"/>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A34" s="26" t="s">
         <v>359</v>
       </c>
@@ -9000,6 +9123,7 @@
       </c>
       <c r="F34" s="30"/>
       <c r="G34" s="30"/>
+      <c r="H34" s="30"/>
       <c r="I34" s="30"/>
       <c r="J34" s="31"/>
       <c r="K34" s="30"/>
@@ -9029,7 +9153,7 @@
       <c r="AI34" s="30"/>
       <c r="AJ34" s="30"/>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A35" s="26" t="s">
         <v>360</v>
       </c>
@@ -9073,7 +9197,7 @@
       <c r="AI35" s="30"/>
       <c r="AJ35" s="30"/>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A36" s="26" t="s">
         <v>370</v>
       </c>
@@ -9117,7 +9241,7 @@
       <c r="AI36" s="30"/>
       <c r="AJ36" s="30"/>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A37" s="26" t="s">
         <v>361</v>
       </c>
@@ -9161,7 +9285,7 @@
       <c r="AI37" s="30"/>
       <c r="AJ37" s="30"/>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" s="26" t="s">
         <v>362</v>
       </c>
@@ -9205,7 +9329,7 @@
       <c r="AI38" s="30"/>
       <c r="AJ38" s="30"/>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A39" s="26" t="s">
         <v>363</v>
       </c>
@@ -9249,7 +9373,7 @@
       <c r="AI39" s="30"/>
       <c r="AJ39" s="30"/>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A40" s="26" t="s">
         <v>364</v>
       </c>
@@ -9293,7 +9417,7 @@
       <c r="AI40" s="30"/>
       <c r="AJ40" s="30"/>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A41" s="26" t="s">
         <v>371</v>
       </c>
@@ -9337,7 +9461,7 @@
       <c r="AI41" s="30"/>
       <c r="AJ41" s="30"/>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A42" s="26" t="s">
         <v>365</v>
       </c>
@@ -9381,7 +9505,7 @@
       <c r="AI42" s="30"/>
       <c r="AJ42" s="30"/>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A43" s="26" t="s">
         <v>366</v>
       </c>
@@ -9425,7 +9549,7 @@
       <c r="AI43" s="30"/>
       <c r="AJ43" s="30"/>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A44" s="26" t="s">
         <v>367</v>
       </c>
@@ -9469,7 +9593,7 @@
       <c r="AI44" s="30"/>
       <c r="AJ44" s="30"/>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A45" s="26">
         <v>4.4000000000000004</v>
       </c>
@@ -9513,7 +9637,7 @@
       <c r="AI45" s="30"/>
       <c r="AJ45" s="30"/>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A46" s="26" t="s">
         <v>372</v>
       </c>
@@ -9557,7 +9681,7 @@
       <c r="AI46" s="30"/>
       <c r="AJ46" s="30"/>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
       <c r="F47" s="30"/>
       <c r="G47" s="30"/>
       <c r="H47" s="30"/>
@@ -9590,7 +9714,7 @@
       <c r="AI47" s="30"/>
       <c r="AJ47" s="30"/>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="F48" s="30"/>
       <c r="G48" s="30"/>
       <c r="H48" s="30"/>
@@ -9623,53 +9747,53 @@
       <c r="AI48" s="30"/>
       <c r="AJ48" s="30"/>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
       <c r="J49" s="8"/>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
       <c r="J54" s="8"/>
     </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
       <c r="J55" s="8"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
       <c r="J56" s="8"/>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
       <c r="J57" s="8"/>
     </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C59" s="24"/>
       <c r="D59" s="24"/>
     </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C60" s="24"/>
       <c r="D60" s="24"/>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C61" s="24"/>
       <c r="D61" s="24"/>
       <c r="J61" s="8"/>
     </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C62" s="24"/>
       <c r="D62" s="24"/>
       <c r="J62" s="8"/>
     </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C63" s="24"/>
       <c r="D63" s="24"/>
       <c r="J63" s="8"/>
     </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="26"/>
       <c r="B66" s="26"/>
       <c r="C66" s="24"/>
@@ -9677,19 +9801,19 @@
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="F4:AI7">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="F4:AI46">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>AND(F$3&gt;=$C4,F$3&lt;=$D4)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22:AI33">
-    <cfRule type="expression" dxfId="1" priority="1563">
-      <formula>AND(F$3&gt;=$C35,F$3&lt;=$D35)</formula>
+  <conditionalFormatting sqref="F8:AI21">
+    <cfRule type="expression" dxfId="4" priority="1565">
+      <formula>AND(F$3&gt;=$C22,F$3&lt;=$D22)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F8:AI21">
-    <cfRule type="expression" dxfId="0" priority="1564">
-      <formula>AND(F$3&gt;=$C22,F$3&lt;=$D22)</formula>
+  <conditionalFormatting sqref="F22:AI33">
+    <cfRule type="expression" dxfId="3" priority="1564">
+      <formula>AND(F$3&gt;=$C35,F$3&lt;=$D35)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9700,13 +9824,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7BD34BE-E30F-40B4-B28D-0BE83B9217E7}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="6" max="36" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="6" max="36" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -9825,13 +9949,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53079CFF-55B9-4D5D-98A9-95E3A3A1065C}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="6" max="36" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="6" max="36" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -9950,13 +10074,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2556B67F-871D-483A-9A7E-BEC7C4A203C4}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="6" max="36" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="6" max="36" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -10073,13 +10197,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BCA75F-35B4-4193-9D7C-1615CE129556}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="6" max="36" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="6" max="36" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -10198,13 +10322,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D4A06CE-94E2-4CB6-8F60-16007918C401}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.83203125" customWidth="1"/>
-    <col min="6" max="36" width="5.33203125" customWidth="1"/>
+    <col min="2" max="2" width="13.875" customWidth="1"/>
+    <col min="6" max="36" width="5.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>246</v>
       </c>

--- a/간트차트_250526.xlsx
+++ b/간트차트_250526.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD38511-BA64-4201-93C7-9812686991FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F18265-8BD3-49DA-A78D-E97A6546E1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1597,77 +1597,7 @@
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="15">
     <dxf>
       <fill>
         <patternFill>
@@ -4576,57 +4506,57 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="E42:K42 M42:JK42 E44:K44 M44:JK44 E46:K46 M46:JK46 E50:L50 N50:JK50 E52:L52 N52:JK52 E54:L54 N54:JK54 E56:L56 N56:JK56 E60:L60 Q60:JK60 E62:L62 Q62:JK62 E66:L66 Q66:JK66 E68:JK68 E74:M74 R74:JK74 E76:M76 R76:JK76 E81:N81 P81:JK81 E83:N83 P83:JK83 E85:N85 P85:JK85 E87:N87 P87:JK87 E89:N89 P89:JK89 E95:O95 Q95:JK95 E97:O97 Q97:JK97 E99:P99 R99:JK99 E101:P101 R101:JK101 E105:P105 S105:JK105 E107:P107 S107:JK107 E109:Q109 S109:JK109">
-    <cfRule type="expression" dxfId="24" priority="427">
+    <cfRule type="expression" dxfId="14" priority="427">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E51:K51 N51:JK51 E53:K53 N53:JK53 E55:K55 N55:JK55 E61:L61 Q61:JK61 E75:M75 R75:JK75 E82:JK82 E84:JK84 E86:JK86 E88:JK88 E96:JK96 E98:JK98 E100:JK100 E106:JK106 E108:JK108">
-    <cfRule type="expression" dxfId="23" priority="510">
+    <cfRule type="expression" dxfId="13" priority="510">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= $B51, E$2 &lt;= $C51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E3:JK11 E13:JK13 E15:JK15 E17:JK17 E19:JK19 E21:JK21 E23:JK23 E25:JK26 E28:JK28 E30:JK30 E32:JK32 E36:JK36 E38:JK39 E40:J40 M40:JK40 E48:K48 N48:JK48 E58:L58 Q58:JK58 E64:L64 Q64:JK64 E70:M70 R70:JK70 E72:M72 R72:JK72 E78:JK79 O81 O83 O85 O87 O89 E91:JK91 E93:JK93 P95 P97 Q99 Q101 E103:JK103 Q105:R105 Q107:R107 R109 E112:JK114 E116:JK116 E118:JK119 E121:JK121 E123:JK123 E125:JK125 E127:JK127 E129:JK129 E131:JK131 E133:JK133 E135:JK135 E137:JK137 E139:JK139 E141:JK141 E143:JK143 E145:JK145 E147:JK147 E149:JK149 E151:JK151 E153:JK153 E155:JK155 E157:JK157 E159:JK159 E161:JK161 E163:JK164 E166:JK166 E168:JK168 E170:JK170 E172:JK172 E174:JK174 E176:JK176 E178:JK178 E180:JK180 E182:JK182 E184:JK184 E186:JK186 E188:JK188 E190:JK190 E192:JK192 E194:JK194 E196:JK196 E198:JK198 E200:JK200 E202:JK202 E204:JK204 E206:JK206 E208:JK209 E211:JK211 E213:JK219 E221:JK221 E223:JK223 E225:JK225">
-    <cfRule type="expression" dxfId="22" priority="208">
+    <cfRule type="expression" dxfId="12" priority="208">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= $B3, E$2 &lt;= $C3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E12:JK12 E14:JK14 E16:JK16 E18:JK18 E20:JK20 E22:JK22 E24:JK24 E27:JK27 E29:JK29 E31:JK31 E33:JK33 E34:F34 H34:JK34 E35:JK35 E37:JK37 E41:JK41 E43:JK43 E45:JK45 E49:K49 N49:JK49 E57:JK57 E59:L59 Q59:JK59 E63:L63 Q63:JK63 E65:L65 Q65:JK65 E67:JK67 E69:JK69 E71:M71 R71:JK71 E73:M73 R73:JK73 E77:M77 R77:JK77 E80:JK80 E90:JK90 E92:JK92 E94:JK94 E102:JK102 E104:JK104 E110:JK111 E115:JK115 E117:JK117 E120:JK120 E122:JK122 E124:JK124 E126:JK126 E128:JK128 E130:JK130 E132:JK132 E134:JK134 E136:JK136 E138:JK138 E140:JK140 E142:JK142 E144:JK144 E146:JK146 E148:JK148 E150:JK150 E152:JK152 E154:JK154 E156:JK156 E158:JK158 E160:JK160 E162:JK162 E165:JK165 E167:JK167 E169:JK169 E171:JK171 E173:JK173 E175:JK175 E177:JK177 E179:JK179 E181:JK181 E183:JK183 E185:JK185 E187:JK187 E189:JK189 E191:JK191 E193:JK193 E195:JK195 E197:JK197 E201:JK201 E203:JK203 E205:JK205 E207:JK207 E210:JK210 E212:JK212 E220:JK220 E222:JK222 E224:JK224 E226:JK226">
-    <cfRule type="expression" dxfId="21" priority="1227">
+    <cfRule type="expression" dxfId="11" priority="1227">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E47:JK47">
-    <cfRule type="expression" dxfId="20" priority="584">
+    <cfRule type="expression" dxfId="10" priority="584">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E199:JK199">
-    <cfRule type="expression" dxfId="19" priority="1324">
+    <cfRule type="expression" dxfId="9" priority="1324">
       <formula>AND(ISNUMBER(E$2), E$2 &gt;= #REF!, E$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G34">
-    <cfRule type="expression" dxfId="18" priority="30">
+    <cfRule type="expression" dxfId="8" priority="30">
       <formula>AND(ISNUMBER(G$2), G$2 &gt;= $B34, G$2 &lt;= $C34)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K40 K42 K44 K46 L48 L50 L52 L54 L56 N58:O58 M58:M59 M61 N64:O64 M64:M65 N66 N70:P70 N72:P72 O74 O76">
-    <cfRule type="expression" dxfId="17" priority="1391">
+    <cfRule type="expression" dxfId="7" priority="1391">
       <formula>AND(ISNUMBER(L$2), L$2 &gt;= $B40, L$2 &lt;= $C40)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L49 N59:O59 M63:O63 N65:O65 N71:P71 N73 P73 N77:P77">
-    <cfRule type="expression" dxfId="16" priority="1485">
+    <cfRule type="expression" dxfId="6" priority="1485">
       <formula>AND(ISNUMBER(M$2), M$2 &gt;= #REF!, M$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L51 L53 L55 N61:O61 N75:P75">
-    <cfRule type="expression" dxfId="15" priority="1467">
+    <cfRule type="expression" dxfId="5" priority="1467">
       <formula>AND(ISNUMBER(M$2), M$2 &gt;= $B51, M$2 &lt;= $C51)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60:O60 M62:O62 M66 O66 N74 P74 N76 P76">
-    <cfRule type="expression" dxfId="14" priority="1559">
+    <cfRule type="expression" dxfId="4" priority="1559">
       <formula>AND(ISNUMBER(N$2), N$2 &gt;= #REF!, N$2 &lt;= #REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6613,7 +6543,7 @@
       <c r="A47" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="B47" s="26" t="s">
+      <c r="B47" s="33" t="s">
         <v>330</v>
       </c>
       <c r="C47" s="24">
@@ -6658,7 +6588,7 @@
       <c r="A48" s="26" t="s">
         <v>288</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="B48" s="33" t="s">
         <v>329</v>
       </c>
       <c r="C48" s="24">
@@ -6703,7 +6633,7 @@
       <c r="A49" s="26" t="s">
         <v>289</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="33" t="s">
         <v>328</v>
       </c>
       <c r="C49" s="24">
@@ -6748,7 +6678,7 @@
       <c r="A50" s="26" t="s">
         <v>290</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B50" s="33" t="s">
         <v>327</v>
       </c>
       <c r="C50" s="24">
@@ -7677,7 +7607,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F4:AJ69">
-    <cfRule type="expression" dxfId="13" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>AND(F$3&gt;=$C4,F$3&lt;=$D4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9802,17 +9732,17 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="F4:AI46">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>AND(F$3&gt;=$C4,F$3&lt;=$D4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8:AI21">
-    <cfRule type="expression" dxfId="4" priority="1565">
+    <cfRule type="expression" dxfId="1" priority="1565">
       <formula>AND(F$3&gt;=$C22,F$3&lt;=$D22)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F22:AI33">
-    <cfRule type="expression" dxfId="3" priority="1564">
+    <cfRule type="expression" dxfId="0" priority="1564">
       <formula>AND(F$3&gt;=$C35,F$3&lt;=$D35)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/간트차트_250526.xlsx
+++ b/간트차트_250526.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\Desktop\storage\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1F18265-8BD3-49DA-A78D-E97A6546E1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C38377-D12D-4DE7-8471-D9C8F102E9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1960" yWindow="900" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="간트 차트 시각화" sheetId="1" r:id="rId1"/>
@@ -1363,7 +1363,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1415,6 +1415,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1536,7 +1548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1593,6 +1605,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2013,20 +2033,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BE226"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.625" customWidth="1"/>
-    <col min="2" max="3" width="14.375" style="3" customWidth="1"/>
+    <col min="1" max="1" width="31.58203125" customWidth="1"/>
+    <col min="2" max="3" width="14.33203125" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.5" style="3" customWidth="1"/>
-    <col min="5" max="330" width="5.875" customWidth="1"/>
+    <col min="5" max="330" width="5.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.45">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
     </row>
-    <row r="2" spans="1:57" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:57" ht="34" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
@@ -2088,7 +2108,7 @@
       <c r="AP2" s="35"/>
       <c r="AQ2" s="35"/>
     </row>
-    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>240</v>
       </c>
@@ -2233,7 +2253,7 @@
       <c r="BD3"/>
       <c r="BE3"/>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>241</v>
       </c>
@@ -2253,7 +2273,7 @@
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
         <v>14</v>
       </c>
@@ -2266,7 +2286,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>15</v>
       </c>
@@ -2280,7 +2300,7 @@
       <c r="F6" s="17"/>
       <c r="G6" s="17"/>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
         <v>17</v>
       </c>
@@ -2295,7 +2315,7 @@
       <c r="I7" s="17"/>
       <c r="J7" s="17"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
@@ -2309,7 +2329,7 @@
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
     </row>
-    <row r="9" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2328,7 +2348,7 @@
       <c r="J9" s="22"/>
       <c r="K9" s="22"/>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
         <v>20</v>
       </c>
@@ -2345,7 +2365,7 @@
       <c r="J10" s="17"/>
       <c r="K10" s="17"/>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>21</v>
       </c>
@@ -2358,7 +2378,7 @@
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -2366,7 +2386,7 @@
       <c r="C12" s="11"/>
       <c r="D12" s="5"/>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -2379,7 +2399,7 @@
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2387,7 +2407,7 @@
       <c r="C14" s="11"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A15" s="8" t="s">
         <v>27</v>
       </c>
@@ -2398,16 +2418,16 @@
       </c>
       <c r="E15" s="17"/>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
-      <c r="A16" s="8" t="s">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.45">
+      <c r="A16" s="37" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A17" s="38" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="11"/>
@@ -2417,16 +2437,16 @@
       </c>
       <c r="E17" s="17"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="8" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A18" s="38" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
       <c r="D18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A19" s="8" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A19" s="38" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="11"/>
@@ -2437,16 +2457,16 @@
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="8" t="s">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A20" s="38" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="11"/>
       <c r="C20" s="11"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A21" s="36" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="11"/>
@@ -2459,16 +2479,16 @@
       <c r="J21" s="17"/>
       <c r="K21" s="17"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A22" s="36" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
       <c r="D22" s="5"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A23" s="36" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="11"/>
@@ -2481,8 +2501,8 @@
       <c r="J23" s="17"/>
       <c r="K23" s="17"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A24" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="11"/>
@@ -2491,7 +2511,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25" s="6" t="s">
         <v>37</v>
       </c>
@@ -2508,7 +2528,7 @@
       <c r="J25" s="17"/>
       <c r="K25" s="17"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>38</v>
       </c>
@@ -2521,7 +2541,7 @@
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -2529,7 +2549,7 @@
       <c r="C27" s="11"/>
       <c r="D27" s="5"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28" s="8" t="s">
         <v>40</v>
       </c>
@@ -2540,7 +2560,7 @@
       </c>
       <c r="E28" s="17"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29" s="8" t="s">
         <v>41</v>
       </c>
@@ -2548,8 +2568,8 @@
       <c r="C29" s="11"/>
       <c r="D29" s="5"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A30" s="8" t="s">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A30" s="38" t="s">
         <v>42</v>
       </c>
       <c r="B30" s="11"/>
@@ -2560,16 +2580,16 @@
       <c r="E30" s="17"/>
       <c r="F30" s="17"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="8" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A31" s="38" t="s">
         <v>43</v>
       </c>
       <c r="B31" s="11"/>
       <c r="C31" s="11"/>
       <c r="D31" s="5"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="8" t="s">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A32" s="38" t="s">
         <v>44</v>
       </c>
       <c r="B32" s="11"/>
@@ -2580,16 +2600,16 @@
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A33" s="38" t="s">
         <v>45</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
       <c r="D33" s="5"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="8" t="s">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A34" s="38" t="s">
         <v>46</v>
       </c>
       <c r="B34" s="11"/>
@@ -2597,15 +2617,15 @@
       <c r="D34" s="5"/>
       <c r="G34" s="17"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="8" t="s">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A35" s="38" t="s">
         <v>47</v>
       </c>
       <c r="B35" s="11"/>
       <c r="C35" s="11"/>
       <c r="D35" s="5"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>48</v>
       </c>
@@ -2619,7 +2639,7 @@
       <c r="J36" s="17"/>
       <c r="K36" s="17"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>49</v>
       </c>
@@ -2627,7 +2647,7 @@
       <c r="C37" s="11"/>
       <c r="D37" s="5"/>
     </row>
-    <row r="38" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A38" s="1" t="s">
         <v>50</v>
       </c>
@@ -2645,7 +2665,7 @@
       <c r="Q38" s="22"/>
       <c r="R38" s="22"/>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A39" s="6" t="s">
         <v>51</v>
       </c>
@@ -2659,7 +2679,7 @@
       <c r="M39" s="17"/>
       <c r="N39" s="17"/>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>52</v>
       </c>
@@ -2668,7 +2688,7 @@
       <c r="D40" s="5"/>
       <c r="K40" s="17"/>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>53</v>
       </c>
@@ -2678,7 +2698,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A42" s="8" t="s">
         <v>54</v>
       </c>
@@ -2687,7 +2707,7 @@
       <c r="D42" s="5"/>
       <c r="K42" s="17"/>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A43" s="8" t="s">
         <v>55</v>
       </c>
@@ -2697,7 +2717,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A44" s="8" t="s">
         <v>56</v>
       </c>
@@ -2706,7 +2726,7 @@
       <c r="D44" s="5"/>
       <c r="K44" s="17"/>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A45" s="8" t="s">
         <v>57</v>
       </c>
@@ -2716,7 +2736,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A46" s="8" t="s">
         <v>58</v>
       </c>
@@ -2725,7 +2745,7 @@
       <c r="D46" s="5"/>
       <c r="K46" s="17"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A47" s="8" t="s">
         <v>59</v>
       </c>
@@ -2735,7 +2755,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>60</v>
       </c>
@@ -2744,7 +2764,7 @@
       <c r="D48" s="5"/>
       <c r="L48" s="17"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>61</v>
       </c>
@@ -2754,7 +2774,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A50" s="8" t="s">
         <v>62</v>
       </c>
@@ -2763,7 +2783,7 @@
       <c r="D50" s="5"/>
       <c r="L50" s="17"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A51" s="8" t="s">
         <v>63</v>
       </c>
@@ -2773,7 +2793,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A52" s="8" t="s">
         <v>64</v>
       </c>
@@ -2782,7 +2802,7 @@
       <c r="D52" s="5"/>
       <c r="L52" s="17"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A53" s="8" t="s">
         <v>65</v>
       </c>
@@ -2792,7 +2812,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A54" s="8" t="s">
         <v>66</v>
       </c>
@@ -2801,7 +2821,7 @@
       <c r="D54" s="5"/>
       <c r="L54" s="17"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A55" s="8" t="s">
         <v>67</v>
       </c>
@@ -2811,7 +2831,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A56" s="8" t="s">
         <v>68</v>
       </c>
@@ -2820,7 +2840,7 @@
       <c r="D56" s="5"/>
       <c r="L56" s="17"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A57" s="8" t="s">
         <v>69</v>
       </c>
@@ -2830,7 +2850,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>70</v>
       </c>
@@ -2839,7 +2859,7 @@
       <c r="D58" s="5"/>
       <c r="M58" s="17"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>71</v>
       </c>
@@ -2850,7 +2870,7 @@
       </c>
       <c r="M59" s="17"/>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A60" s="8" t="s">
         <v>72</v>
       </c>
@@ -2858,7 +2878,7 @@
       <c r="C60" s="11"/>
       <c r="D60" s="5"/>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A61" s="8" t="s">
         <v>73</v>
       </c>
@@ -2869,7 +2889,7 @@
       </c>
       <c r="M61" s="17"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A62" s="8" t="s">
         <v>74</v>
       </c>
@@ -2877,7 +2897,7 @@
       <c r="C62" s="11"/>
       <c r="D62" s="5"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A63" s="8" t="s">
         <v>75</v>
       </c>
@@ -2887,7 +2907,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>76</v>
       </c>
@@ -2897,7 +2917,7 @@
       <c r="M64" s="17"/>
       <c r="N64" s="17"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>77</v>
       </c>
@@ -2908,7 +2928,7 @@
       </c>
       <c r="M65" s="17"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A66" s="8" t="s">
         <v>78</v>
       </c>
@@ -2917,7 +2937,7 @@
       <c r="D66" s="5"/>
       <c r="N66" s="17"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A67" s="8" t="s">
         <v>79</v>
       </c>
@@ -2927,7 +2947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A68" s="8" t="s">
         <v>80</v>
       </c>
@@ -2935,7 +2955,7 @@
       <c r="C68" s="11"/>
       <c r="D68" s="5"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A69" s="8" t="s">
         <v>81</v>
       </c>
@@ -2945,7 +2965,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>82</v>
       </c>
@@ -2954,7 +2974,7 @@
       <c r="D70" s="5"/>
       <c r="N70" s="17"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>83</v>
       </c>
@@ -2964,7 +2984,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -2973,7 +2993,7 @@
       <c r="D72" s="5"/>
       <c r="O72" s="17"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>85</v>
       </c>
@@ -2983,7 +3003,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A74" s="8" t="s">
         <v>86</v>
       </c>
@@ -2992,7 +3012,7 @@
       <c r="D74" s="5"/>
       <c r="O74" s="17"/>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A75" s="8" t="s">
         <v>87</v>
       </c>
@@ -3002,7 +3022,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A76" s="8" t="s">
         <v>88</v>
       </c>
@@ -3011,7 +3031,7 @@
       <c r="D76" s="5"/>
       <c r="O76" s="17"/>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A77" s="8" t="s">
         <v>89</v>
       </c>
@@ -3021,7 +3041,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A78" s="6" t="s">
         <v>90</v>
       </c>
@@ -3035,7 +3055,7 @@
       <c r="Q78" s="17"/>
       <c r="R78" s="17"/>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>91</v>
       </c>
@@ -3044,7 +3064,7 @@
       <c r="D79" s="5"/>
       <c r="O79" s="17"/>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -3054,7 +3074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A81" s="8" t="s">
         <v>93</v>
       </c>
@@ -3063,7 +3083,7 @@
       <c r="D81" s="5"/>
       <c r="O81" s="17"/>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A82" s="8" t="s">
         <v>94</v>
       </c>
@@ -3073,7 +3093,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A83" s="8" t="s">
         <v>95</v>
       </c>
@@ -3082,7 +3102,7 @@
       <c r="D83" s="5"/>
       <c r="O83" s="17"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A84" s="8" t="s">
         <v>96</v>
       </c>
@@ -3092,7 +3112,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A85" s="8" t="s">
         <v>97</v>
       </c>
@@ -3101,7 +3121,7 @@
       <c r="D85" s="5"/>
       <c r="O85" s="17"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A86" s="8" t="s">
         <v>98</v>
       </c>
@@ -3111,7 +3131,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A87" s="8" t="s">
         <v>99</v>
       </c>
@@ -3120,7 +3140,7 @@
       <c r="D87" s="5"/>
       <c r="O87" s="17"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A88" s="8" t="s">
         <v>100</v>
       </c>
@@ -3130,7 +3150,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A89" s="8" t="s">
         <v>101</v>
       </c>
@@ -3139,7 +3159,7 @@
       <c r="D89" s="5"/>
       <c r="O89" s="17"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A90" s="8" t="s">
         <v>102</v>
       </c>
@@ -3149,7 +3169,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>103</v>
       </c>
@@ -3159,7 +3179,7 @@
       <c r="O91" s="17"/>
       <c r="P91" s="17"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -3169,7 +3189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>105</v>
       </c>
@@ -3179,7 +3199,7 @@
       <c r="P93" s="17"/>
       <c r="Q93" s="17"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>106</v>
       </c>
@@ -3189,7 +3209,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A95" s="8" t="s">
         <v>107</v>
       </c>
@@ -3198,7 +3218,7 @@
       <c r="D95" s="5"/>
       <c r="P95" s="17"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A96" s="8" t="s">
         <v>108</v>
       </c>
@@ -3208,7 +3228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A97" s="8" t="s">
         <v>109</v>
       </c>
@@ -3217,7 +3237,7 @@
       <c r="D97" s="5"/>
       <c r="P97" s="17"/>
     </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A98" s="8" t="s">
         <v>110</v>
       </c>
@@ -3227,7 +3247,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A99" s="8" t="s">
         <v>111</v>
       </c>
@@ -3236,7 +3256,7 @@
       <c r="D99" s="5"/>
       <c r="Q99" s="17"/>
     </row>
-    <row r="100" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A100" s="8" t="s">
         <v>112</v>
       </c>
@@ -3246,7 +3266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A101" s="8" t="s">
         <v>113</v>
       </c>
@@ -3255,7 +3275,7 @@
       <c r="D101" s="5"/>
       <c r="Q101" s="17"/>
     </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A102" s="8" t="s">
         <v>114</v>
       </c>
@@ -3265,7 +3285,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>115</v>
       </c>
@@ -3275,7 +3295,7 @@
       <c r="Q103" s="17"/>
       <c r="R103" s="17"/>
     </row>
-    <row r="104" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -3285,7 +3305,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A105" s="8" t="s">
         <v>117</v>
       </c>
@@ -3295,7 +3315,7 @@
       <c r="Q105" s="17"/>
       <c r="R105" s="17"/>
     </row>
-    <row r="106" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A106" s="8" t="s">
         <v>118</v>
       </c>
@@ -3305,7 +3325,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A107" s="8" t="s">
         <v>119</v>
       </c>
@@ -3315,7 +3335,7 @@
       <c r="Q107" s="17"/>
       <c r="R107" s="17"/>
     </row>
-    <row r="108" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A108" s="8" t="s">
         <v>120</v>
       </c>
@@ -3325,7 +3345,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A109" s="8" t="s">
         <v>121</v>
       </c>
@@ -3334,7 +3354,7 @@
       <c r="D109" s="5"/>
       <c r="R109" s="17"/>
     </row>
-    <row r="110" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A110" s="8" t="s">
         <v>122</v>
       </c>
@@ -3344,7 +3364,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A111" s="8" t="s">
         <v>388</v>
       </c>
@@ -3352,7 +3372,7 @@
       <c r="C111" s="11"/>
       <c r="D111" s="5"/>
     </row>
-    <row r="112" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
         <v>123</v>
       </c>
@@ -3376,7 +3396,7 @@
       <c r="V112" s="22"/>
       <c r="W112" s="22"/>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A113" s="6" t="s">
         <v>124</v>
       </c>
@@ -3388,7 +3408,7 @@
       <c r="J113" s="17"/>
       <c r="K113" s="17"/>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>125</v>
       </c>
@@ -3399,7 +3419,7 @@
       </c>
       <c r="J114" s="17"/>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>126</v>
       </c>
@@ -3409,8 +3429,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A116" s="39" t="s">
         <v>127</v>
       </c>
       <c r="B116" s="11"/>
@@ -3420,15 +3440,15 @@
       </c>
       <c r="K116" s="17"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A117" s="39" t="s">
         <v>128</v>
       </c>
       <c r="B117" s="11"/>
       <c r="C117" s="11"/>
       <c r="D117" s="5"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A118" s="6" t="s">
         <v>129</v>
       </c>
@@ -3444,7 +3464,7 @@
       <c r="P118" s="17"/>
       <c r="Q118" s="17"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>130</v>
       </c>
@@ -3456,7 +3476,7 @@
       <c r="L119" s="17"/>
       <c r="M119" s="17"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>131</v>
       </c>
@@ -3464,7 +3484,7 @@
       <c r="C120" s="11"/>
       <c r="D120" s="5"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A121" s="8" t="s">
         <v>132</v>
       </c>
@@ -3475,7 +3495,7 @@
       </c>
       <c r="L121" s="17"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A122" s="8" t="s">
         <v>133</v>
       </c>
@@ -3483,7 +3503,7 @@
       <c r="C122" s="11"/>
       <c r="D122" s="5"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A123" s="8" t="s">
         <v>134</v>
       </c>
@@ -3494,7 +3514,7 @@
       </c>
       <c r="L123" s="17"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A124" s="8" t="s">
         <v>135</v>
       </c>
@@ -3502,7 +3522,7 @@
       <c r="C124" s="11"/>
       <c r="D124" s="5"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A125" s="8" t="s">
         <v>136</v>
       </c>
@@ -3514,7 +3534,7 @@
       <c r="L125" s="17"/>
       <c r="M125" s="17"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A126" s="8" t="s">
         <v>137</v>
       </c>
@@ -3522,7 +3542,7 @@
       <c r="C126" s="11"/>
       <c r="D126" s="5"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A127" s="8" t="s">
         <v>138</v>
       </c>
@@ -3533,7 +3553,7 @@
       </c>
       <c r="M127" s="17"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.45">
       <c r="A128" s="8" t="s">
         <v>139</v>
       </c>
@@ -3541,7 +3561,7 @@
       <c r="C128" s="11"/>
       <c r="D128" s="5"/>
     </row>
-    <row r="129" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A129" s="8" t="s">
         <v>140</v>
       </c>
@@ -3552,7 +3572,7 @@
       </c>
       <c r="M129" s="17"/>
     </row>
-    <row r="130" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A130" s="8" t="s">
         <v>141</v>
       </c>
@@ -3560,7 +3580,7 @@
       <c r="C130" s="11"/>
       <c r="D130" s="5"/>
     </row>
-    <row r="131" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A131" s="8" t="s">
         <v>142</v>
       </c>
@@ -3571,7 +3591,7 @@
       </c>
       <c r="M131" s="17"/>
     </row>
-    <row r="132" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A132" s="8" t="s">
         <v>143</v>
       </c>
@@ -3579,7 +3599,7 @@
       <c r="C132" s="11"/>
       <c r="D132" s="5"/>
     </row>
-    <row r="133" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>144</v>
       </c>
@@ -3590,7 +3610,7 @@
       </c>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>145</v>
       </c>
@@ -3598,7 +3618,7 @@
       <c r="C134" s="11"/>
       <c r="D134" s="5"/>
     </row>
-    <row r="135" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A135" s="8" t="s">
         <v>146</v>
       </c>
@@ -3609,7 +3629,7 @@
       </c>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A136" s="8" t="s">
         <v>147</v>
       </c>
@@ -3617,8 +3637,8 @@
       <c r="C136" s="11"/>
       <c r="D136" s="5"/>
     </row>
-    <row r="137" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A137" s="8" t="s">
+    <row r="137" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A137" s="37" t="s">
         <v>148</v>
       </c>
       <c r="B137" s="11"/>
@@ -3628,16 +3648,16 @@
       </c>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A138" s="8" t="s">
+    <row r="138" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A138" s="37" t="s">
         <v>149</v>
       </c>
       <c r="B138" s="11"/>
       <c r="C138" s="11"/>
       <c r="D138" s="5"/>
     </row>
-    <row r="139" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A139" s="8" t="s">
+    <row r="139" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A139" s="37" t="s">
         <v>150</v>
       </c>
       <c r="B139" s="11"/>
@@ -3647,16 +3667,16 @@
       </c>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A140" s="8" t="s">
+    <row r="140" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A140" s="37" t="s">
         <v>151</v>
       </c>
       <c r="B140" s="11"/>
       <c r="C140" s="11"/>
       <c r="D140" s="5"/>
     </row>
-    <row r="141" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A141" s="8" t="s">
+    <row r="141" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A141" s="37" t="s">
         <v>152</v>
       </c>
       <c r="B141" s="11"/>
@@ -3666,15 +3686,15 @@
       </c>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A142" s="8" t="s">
+    <row r="142" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="A142" s="37" t="s">
         <v>153</v>
       </c>
       <c r="B142" s="11"/>
       <c r="C142" s="11"/>
       <c r="D142" s="5"/>
     </row>
-    <row r="143" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>154</v>
       </c>
@@ -3685,7 +3705,7 @@
       </c>
       <c r="O143" s="17"/>
     </row>
-    <row r="144" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>155</v>
       </c>
@@ -3693,8 +3713,8 @@
       <c r="C144" s="11"/>
       <c r="D144" s="5"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A145" s="8" t="s">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A145" s="37" t="s">
         <v>156</v>
       </c>
       <c r="B145" s="11"/>
@@ -3704,16 +3724,16 @@
       </c>
       <c r="O145" s="17"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A146" s="8" t="s">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A146" s="37" t="s">
         <v>157</v>
       </c>
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
       <c r="D146" s="5"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A147" s="8" t="s">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A147" s="37" t="s">
         <v>158</v>
       </c>
       <c r="B147" s="11"/>
@@ -3723,15 +3743,15 @@
       </c>
       <c r="O147" s="17"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A148" s="8" t="s">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A148" s="37" t="s">
         <v>159</v>
       </c>
       <c r="B148" s="11"/>
       <c r="C148" s="11"/>
       <c r="D148" s="5"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>160</v>
       </c>
@@ -3742,7 +3762,7 @@
       </c>
       <c r="O149" s="17"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>161</v>
       </c>
@@ -3750,8 +3770,8 @@
       <c r="C150" s="11"/>
       <c r="D150" s="5"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A151" s="8" t="s">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A151" s="37" t="s">
         <v>162</v>
       </c>
       <c r="B151" s="11"/>
@@ -3761,16 +3781,16 @@
       </c>
       <c r="O151" s="17"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A152" s="8" t="s">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A152" s="37" t="s">
         <v>163</v>
       </c>
       <c r="B152" s="11"/>
       <c r="C152" s="11"/>
       <c r="D152" s="5"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A153" s="8" t="s">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A153" s="38" t="s">
         <v>164</v>
       </c>
       <c r="B153" s="11"/>
@@ -3780,15 +3800,15 @@
       </c>
       <c r="O153" s="17"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A154" s="8" t="s">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A154" s="38" t="s">
         <v>165</v>
       </c>
       <c r="B154" s="11"/>
       <c r="C154" s="11"/>
       <c r="D154" s="5"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>166</v>
       </c>
@@ -3799,7 +3819,7 @@
       </c>
       <c r="O155" s="17"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>167</v>
       </c>
@@ -3807,7 +3827,7 @@
       <c r="C156" s="11"/>
       <c r="D156" s="5"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>168</v>
       </c>
@@ -3818,7 +3838,7 @@
       </c>
       <c r="P157" s="17"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>169</v>
       </c>
@@ -3826,8 +3846,8 @@
       <c r="C158" s="11"/>
       <c r="D158" s="5"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A159" s="8" t="s">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A159" s="38" t="s">
         <v>170</v>
       </c>
       <c r="B159" s="11"/>
@@ -3837,16 +3857,16 @@
       </c>
       <c r="P159" s="17"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A160" s="8" t="s">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A160" s="38" t="s">
         <v>171</v>
       </c>
       <c r="B160" s="11"/>
       <c r="C160" s="11"/>
       <c r="D160" s="5"/>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A161" s="8" t="s">
+    <row r="161" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A161" s="38" t="s">
         <v>172</v>
       </c>
       <c r="B161" s="11"/>
@@ -3856,15 +3876,15 @@
       </c>
       <c r="P161" s="17"/>
     </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A162" s="8" t="s">
+    <row r="162" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A162" s="38" t="s">
         <v>173</v>
       </c>
       <c r="B162" s="11"/>
       <c r="C162" s="11"/>
       <c r="D162" s="5"/>
     </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A163" s="6" t="s">
         <v>174</v>
       </c>
@@ -3879,7 +3899,7 @@
       <c r="T163" s="17"/>
       <c r="U163" s="17"/>
     </row>
-    <row r="164" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>175</v>
       </c>
@@ -3891,7 +3911,7 @@
       <c r="Q164" s="17"/>
       <c r="R164" s="17"/>
     </row>
-    <row r="165" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>176</v>
       </c>
@@ -3899,7 +3919,7 @@
       <c r="C165" s="11"/>
       <c r="D165" s="5"/>
     </row>
-    <row r="166" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A166" s="8" t="s">
         <v>177</v>
       </c>
@@ -3910,7 +3930,7 @@
       </c>
       <c r="Q166" s="17"/>
     </row>
-    <row r="167" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A167" s="8" t="s">
         <v>178</v>
       </c>
@@ -3918,8 +3938,8 @@
       <c r="C167" s="11"/>
       <c r="D167" s="5"/>
     </row>
-    <row r="168" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A168" s="8" t="s">
+    <row r="168" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A168" s="38" t="s">
         <v>179</v>
       </c>
       <c r="B168" s="11"/>
@@ -3930,16 +3950,16 @@
       <c r="Q168" s="17"/>
       <c r="R168" s="17"/>
     </row>
-    <row r="169" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A169" s="8" t="s">
+    <row r="169" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A169" s="38" t="s">
         <v>180</v>
       </c>
       <c r="B169" s="11"/>
       <c r="C169" s="11"/>
       <c r="D169" s="5"/>
     </row>
-    <row r="170" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A170" s="8" t="s">
+    <row r="170" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A170" s="37" t="s">
         <v>181</v>
       </c>
       <c r="B170" s="11"/>
@@ -3949,15 +3969,15 @@
       </c>
       <c r="R170" s="17"/>
     </row>
-    <row r="171" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A171" s="8" t="s">
+    <row r="171" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A171" s="37" t="s">
         <v>182</v>
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="11"/>
       <c r="D171" s="5"/>
     </row>
-    <row r="172" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>183</v>
       </c>
@@ -3969,7 +3989,7 @@
       <c r="R172" s="17"/>
       <c r="S172" s="17"/>
     </row>
-    <row r="173" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>184</v>
       </c>
@@ -3977,7 +3997,7 @@
       <c r="C173" s="11"/>
       <c r="D173" s="5"/>
     </row>
-    <row r="174" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A174" s="8" t="s">
         <v>185</v>
       </c>
@@ -3988,7 +4008,7 @@
       </c>
       <c r="R174" s="17"/>
     </row>
-    <row r="175" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A175" s="8" t="s">
         <v>186</v>
       </c>
@@ -3996,8 +4016,8 @@
       <c r="C175" s="11"/>
       <c r="D175" s="5"/>
     </row>
-    <row r="176" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A176" s="8" t="s">
+    <row r="176" spans="1:21" x14ac:dyDescent="0.45">
+      <c r="A176" s="38" t="s">
         <v>187</v>
       </c>
       <c r="B176" s="11"/>
@@ -4008,16 +4028,16 @@
       <c r="R176" s="17"/>
       <c r="S176" s="17"/>
     </row>
-    <row r="177" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A177" s="8" t="s">
+    <row r="177" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A177" s="38" t="s">
         <v>188</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="11"/>
       <c r="D177" s="5"/>
     </row>
-    <row r="178" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A178" s="8" t="s">
+    <row r="178" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A178" s="37" t="s">
         <v>189</v>
       </c>
       <c r="B178" s="11"/>
@@ -4028,16 +4048,16 @@
       <c r="R178" s="17"/>
       <c r="S178" s="17"/>
     </row>
-    <row r="179" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A179" s="8" t="s">
+    <row r="179" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A179" s="37" t="s">
         <v>190</v>
       </c>
       <c r="B179" s="11"/>
       <c r="C179" s="11"/>
       <c r="D179" s="5"/>
     </row>
-    <row r="180" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A180" s="8" t="s">
+    <row r="180" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A180" s="37" t="s">
         <v>191</v>
       </c>
       <c r="B180" s="11"/>
@@ -4048,15 +4068,15 @@
       <c r="R180" s="17"/>
       <c r="S180" s="17"/>
     </row>
-    <row r="181" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A181" s="8" t="s">
+    <row r="181" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A181" s="37" t="s">
         <v>192</v>
       </c>
       <c r="B181" s="11"/>
       <c r="C181" s="11"/>
       <c r="D181" s="5"/>
     </row>
-    <row r="182" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A182" s="8" t="s">
         <v>193</v>
       </c>
@@ -4067,7 +4087,7 @@
       </c>
       <c r="R182" s="17"/>
     </row>
-    <row r="183" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A183" s="8" t="s">
         <v>194</v>
       </c>
@@ -4075,7 +4095,7 @@
       <c r="C183" s="11"/>
       <c r="D183" s="5"/>
     </row>
-    <row r="184" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>195</v>
       </c>
@@ -4086,7 +4106,7 @@
       </c>
       <c r="S184" s="17"/>
     </row>
-    <row r="185" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>196</v>
       </c>
@@ -4094,7 +4114,7 @@
       <c r="C185" s="11"/>
       <c r="D185" s="5"/>
     </row>
-    <row r="186" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A186" s="8" t="s">
         <v>197</v>
       </c>
@@ -4105,7 +4125,7 @@
       </c>
       <c r="S186" s="17"/>
     </row>
-    <row r="187" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A187" s="8" t="s">
         <v>198</v>
       </c>
@@ -4113,8 +4133,8 @@
       <c r="C187" s="11"/>
       <c r="D187" s="5"/>
     </row>
-    <row r="188" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A188" s="8" t="s">
+    <row r="188" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A188" s="37" t="s">
         <v>199</v>
       </c>
       <c r="B188" s="11"/>
@@ -4124,15 +4144,15 @@
       </c>
       <c r="S188" s="17"/>
     </row>
-    <row r="189" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A189" s="8" t="s">
+    <row r="189" spans="1:20" x14ac:dyDescent="0.45">
+      <c r="A189" s="37" t="s">
         <v>200</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="11"/>
       <c r="D189" s="5"/>
     </row>
-    <row r="190" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>201</v>
       </c>
@@ -4144,7 +4164,7 @@
       <c r="S190" s="17"/>
       <c r="T190" s="17"/>
     </row>
-    <row r="191" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>202</v>
       </c>
@@ -4152,7 +4172,7 @@
       <c r="C191" s="11"/>
       <c r="D191" s="5"/>
     </row>
-    <row r="192" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A192" s="8" t="s">
         <v>203</v>
       </c>
@@ -4163,7 +4183,7 @@
       </c>
       <c r="S192" s="17"/>
     </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A193" s="8" t="s">
         <v>204</v>
       </c>
@@ -4171,7 +4191,7 @@
       <c r="C193" s="11"/>
       <c r="D193" s="5"/>
     </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A194" s="8" t="s">
         <v>205</v>
       </c>
@@ -4182,7 +4202,7 @@
       </c>
       <c r="T194" s="17"/>
     </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A195" s="8" t="s">
         <v>206</v>
       </c>
@@ -4190,7 +4210,7 @@
       <c r="C195" s="11"/>
       <c r="D195" s="5"/>
     </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A196" s="8" t="s">
         <v>207</v>
       </c>
@@ -4201,7 +4221,7 @@
       </c>
       <c r="T196" s="17"/>
     </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A197" s="8" t="s">
         <v>208</v>
       </c>
@@ -4209,8 +4229,8 @@
       <c r="C197" s="11"/>
       <c r="D197" s="5"/>
     </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A198" s="8" t="s">
+    <row r="198" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A198" s="37" t="s">
         <v>209</v>
       </c>
       <c r="B198" s="11"/>
@@ -4220,15 +4240,15 @@
       </c>
       <c r="T198" s="17"/>
     </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A199" s="8" t="s">
+    <row r="199" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A199" s="37" t="s">
         <v>210</v>
       </c>
       <c r="B199" s="11"/>
       <c r="C199" s="11"/>
       <c r="D199" s="5"/>
     </row>
-    <row r="200" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
         <v>211</v>
       </c>
@@ -4240,16 +4260,16 @@
       <c r="T200" s="18"/>
       <c r="U200" s="18"/>
     </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A201" t="s">
+    <row r="201" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A201" s="36" t="s">
         <v>212</v>
       </c>
       <c r="B201" s="11"/>
       <c r="C201" s="11"/>
       <c r="D201" s="5"/>
     </row>
-    <row r="202" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="8" t="s">
+    <row r="202" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A202" s="37" t="s">
         <v>213</v>
       </c>
       <c r="B202" s="11"/>
@@ -4259,16 +4279,16 @@
       </c>
       <c r="T202" s="18"/>
     </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A203" s="8" t="s">
+    <row r="203" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A203" s="37" t="s">
         <v>214</v>
       </c>
       <c r="B203" s="11"/>
       <c r="C203" s="11"/>
       <c r="D203" s="5"/>
     </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A204" s="8" t="s">
+    <row r="204" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A204" s="37" t="s">
         <v>215</v>
       </c>
       <c r="B204" s="11"/>
@@ -4278,16 +4298,16 @@
       </c>
       <c r="U204" s="17"/>
     </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A205" s="8" t="s">
+    <row r="205" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A205" s="37" t="s">
         <v>216</v>
       </c>
       <c r="B205" s="11"/>
       <c r="C205" s="11"/>
       <c r="D205" s="5"/>
     </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A206" s="8" t="s">
+    <row r="206" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A206" s="37" t="s">
         <v>217</v>
       </c>
       <c r="B206" s="11"/>
@@ -4297,16 +4317,16 @@
       </c>
       <c r="U206" s="17"/>
     </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A207" s="8" t="s">
+    <row r="207" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A207" s="37" t="s">
         <v>218</v>
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="11"/>
       <c r="D207" s="5"/>
     </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="A208" s="6" t="s">
+    <row r="208" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="A208" s="36" t="s">
         <v>219</v>
       </c>
       <c r="B208" s="11"/>
@@ -4317,8 +4337,8 @@
       <c r="U208" s="17"/>
       <c r="V208" s="17"/>
     </row>
-    <row r="209" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A209" t="s">
+    <row r="209" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A209" s="36" t="s">
         <v>220</v>
       </c>
       <c r="B209" s="11"/>
@@ -4328,16 +4348,16 @@
       </c>
       <c r="U209" s="17"/>
     </row>
-    <row r="210" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A210" t="s">
+    <row r="210" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A210" s="36" t="s">
         <v>221</v>
       </c>
       <c r="B210" s="11"/>
       <c r="C210" s="11"/>
       <c r="D210" s="5"/>
     </row>
-    <row r="211" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A211" t="s">
+    <row r="211" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A211" s="36" t="s">
         <v>222</v>
       </c>
       <c r="B211" s="11"/>
@@ -4347,15 +4367,15 @@
       </c>
       <c r="V211" s="17"/>
     </row>
-    <row r="212" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A212" t="s">
+    <row r="212" spans="1:41" x14ac:dyDescent="0.45">
+      <c r="A212" s="36" t="s">
         <v>223</v>
       </c>
       <c r="B212" s="11"/>
       <c r="C212" s="11"/>
       <c r="D212" s="5"/>
     </row>
-    <row r="213" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
         <v>224</v>
       </c>
@@ -4375,7 +4395,7 @@
       <c r="AD213" s="22"/>
       <c r="AE213" s="22"/>
     </row>
-    <row r="214" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A214" s="6" t="s">
         <v>225</v>
       </c>
@@ -4383,7 +4403,7 @@
       <c r="C214" s="11"/>
       <c r="D214" s="5"/>
     </row>
-    <row r="215" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A215" s="6" t="s">
         <v>226</v>
       </c>
@@ -4391,7 +4411,7 @@
       <c r="C215" s="11"/>
       <c r="D215" s="5"/>
     </row>
-    <row r="216" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
         <v>227</v>
       </c>
@@ -4412,7 +4432,7 @@
       <c r="AN216" s="22"/>
       <c r="AO216" s="22"/>
     </row>
-    <row r="217" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A217" s="6" t="s">
         <v>228</v>
       </c>
@@ -4420,7 +4440,7 @@
       <c r="C217" s="11"/>
       <c r="D217" s="5"/>
     </row>
-    <row r="218" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A218" s="6" t="s">
         <v>229</v>
       </c>
@@ -4428,7 +4448,7 @@
       <c r="C218" s="11"/>
       <c r="D218" s="5"/>
     </row>
-    <row r="219" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
         <v>230</v>
       </c>
@@ -4436,7 +4456,7 @@
       <c r="C219" s="11"/>
       <c r="D219" s="5"/>
     </row>
-    <row r="220" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
         <v>231</v>
       </c>
@@ -4444,7 +4464,7 @@
       <c r="C220" s="11"/>
       <c r="D220" s="5"/>
     </row>
-    <row r="221" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
         <v>232</v>
       </c>
@@ -4452,7 +4472,7 @@
       <c r="C221" s="11"/>
       <c r="D221" s="5"/>
     </row>
-    <row r="222" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
         <v>233</v>
       </c>
@@ -4460,7 +4480,7 @@
       <c r="C222" s="11"/>
       <c r="D222" s="5"/>
     </row>
-    <row r="223" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
         <v>234</v>
       </c>
@@ -4468,7 +4488,7 @@
       <c r="C223" s="11"/>
       <c r="D223" s="5"/>
     </row>
-    <row r="224" spans="1:41" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
         <v>235</v>
       </c>
@@ -4476,7 +4496,7 @@
       <c r="C224" s="11"/>
       <c r="D224" s="5"/>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
         <v>236</v>
       </c>
@@ -4484,7 +4504,7 @@
       <c r="C225" s="11"/>
       <c r="D225" s="5"/>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
         <v>237</v>
       </c>
@@ -4567,14 +4587,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B5272A1-BEB8-421C-96FA-5A790BB37DC6}">
   <dimension ref="A3:AJ87"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
-    <col min="2" max="2" width="22.875" customWidth="1"/>
-    <col min="6" max="36" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="6" max="36" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -4684,7 +4704,7 @@
         <v>45808</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" s="26">
         <v>3</v>
       </c>
@@ -4728,7 +4748,7 @@
       <c r="AI4" s="30"/>
       <c r="AJ4" s="30"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" s="26">
         <v>3.1</v>
       </c>
@@ -4769,7 +4789,7 @@
       <c r="AI5" s="30"/>
       <c r="AJ5" s="30"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="26" t="s">
         <v>248</v>
       </c>
@@ -4814,7 +4834,7 @@
       <c r="AI6" s="30"/>
       <c r="AJ6" s="30"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="26" t="s">
         <v>249</v>
       </c>
@@ -4859,7 +4879,7 @@
       <c r="AI7" s="30"/>
       <c r="AJ7" s="30"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" s="26" t="s">
         <v>251</v>
       </c>
@@ -4904,7 +4924,7 @@
       <c r="AI8" s="30"/>
       <c r="AJ8" s="30"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
         <v>252</v>
       </c>
@@ -4949,7 +4969,7 @@
       <c r="AI9" s="30"/>
       <c r="AJ9" s="30"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" s="26" t="s">
         <v>253</v>
       </c>
@@ -4994,7 +5014,7 @@
       <c r="AI10" s="30"/>
       <c r="AJ10" s="30"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" s="26" t="s">
         <v>254</v>
       </c>
@@ -5039,7 +5059,7 @@
       <c r="AI11" s="30"/>
       <c r="AJ11" s="30"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" s="26" t="s">
         <v>255</v>
       </c>
@@ -5084,7 +5104,7 @@
       <c r="AI12" s="30"/>
       <c r="AJ12" s="30"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" s="26" t="s">
         <v>256</v>
       </c>
@@ -5129,7 +5149,7 @@
       <c r="AI13" s="30"/>
       <c r="AJ13" s="30"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" s="26" t="s">
         <v>257</v>
       </c>
@@ -5174,7 +5194,7 @@
       <c r="AI14" s="30"/>
       <c r="AJ14" s="30"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" s="26" t="s">
         <v>258</v>
       </c>
@@ -5219,7 +5239,7 @@
       <c r="AI15" s="30"/>
       <c r="AJ15" s="30"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" s="26" t="s">
         <v>259</v>
       </c>
@@ -5264,7 +5284,7 @@
       <c r="AI16" s="30"/>
       <c r="AJ16" s="30"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A17" s="26" t="s">
         <v>260</v>
       </c>
@@ -5309,7 +5329,7 @@
       <c r="AI17" s="30"/>
       <c r="AJ17" s="30"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A18" s="26" t="s">
         <v>261</v>
       </c>
@@ -5354,7 +5374,7 @@
       <c r="AI18" s="30"/>
       <c r="AJ18" s="30"/>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A19" s="26" t="s">
         <v>262</v>
       </c>
@@ -5399,7 +5419,7 @@
       <c r="AI19" s="30"/>
       <c r="AJ19" s="30"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A20" s="26" t="s">
         <v>263</v>
       </c>
@@ -5444,7 +5464,7 @@
       <c r="AI20" s="30"/>
       <c r="AJ20" s="30"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A21" s="26" t="s">
         <v>264</v>
       </c>
@@ -5489,7 +5509,7 @@
       <c r="AI21" s="30"/>
       <c r="AJ21" s="30"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A22" s="26" t="s">
         <v>265</v>
       </c>
@@ -5534,7 +5554,7 @@
       <c r="AI22" s="30"/>
       <c r="AJ22" s="30"/>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A23" s="26" t="s">
         <v>266</v>
       </c>
@@ -5579,7 +5599,7 @@
       <c r="AI23" s="30"/>
       <c r="AJ23" s="30"/>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A24" s="26" t="s">
         <v>267</v>
       </c>
@@ -5624,7 +5644,7 @@
       <c r="AI24" s="30"/>
       <c r="AJ24" s="30"/>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A25" s="26">
         <v>3.2</v>
       </c>
@@ -5665,7 +5685,7 @@
       <c r="AI25" s="30"/>
       <c r="AJ25" s="30"/>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A26" s="26" t="s">
         <v>268</v>
       </c>
@@ -5706,7 +5726,7 @@
       <c r="AI26" s="30"/>
       <c r="AJ26" s="30"/>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A27" s="26" t="s">
         <v>269</v>
       </c>
@@ -5747,7 +5767,7 @@
       <c r="AI27" s="30"/>
       <c r="AJ27" s="30"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A28" s="26" t="s">
         <v>270</v>
       </c>
@@ -5788,7 +5808,7 @@
       <c r="AI28" s="30"/>
       <c r="AJ28" s="30"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A29" s="26" t="s">
         <v>270</v>
       </c>
@@ -5829,7 +5849,7 @@
       <c r="AI29" s="30"/>
       <c r="AJ29" s="30"/>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A30" s="26" t="s">
         <v>271</v>
       </c>
@@ -5870,7 +5890,7 @@
       <c r="AI30" s="30"/>
       <c r="AJ30" s="30"/>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A31" s="26" t="s">
         <v>272</v>
       </c>
@@ -5911,7 +5931,7 @@
       <c r="AI31" s="30"/>
       <c r="AJ31" s="30"/>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A32" s="26" t="s">
         <v>273</v>
       </c>
@@ -5952,7 +5972,7 @@
       <c r="AI32" s="30"/>
       <c r="AJ32" s="30"/>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A33" s="26" t="s">
         <v>274</v>
       </c>
@@ -5993,7 +6013,7 @@
       <c r="AI33" s="30"/>
       <c r="AJ33" s="30"/>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A34" s="26" t="s">
         <v>275</v>
       </c>
@@ -6034,7 +6054,7 @@
       <c r="AI34" s="30"/>
       <c r="AJ34" s="30"/>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A35" s="26" t="s">
         <v>276</v>
       </c>
@@ -6075,7 +6095,7 @@
       <c r="AI35" s="30"/>
       <c r="AJ35" s="30"/>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A36" s="26" t="s">
         <v>277</v>
       </c>
@@ -6116,7 +6136,7 @@
       <c r="AI36" s="30"/>
       <c r="AJ36" s="30"/>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A37" s="26" t="s">
         <v>278</v>
       </c>
@@ -6157,7 +6177,7 @@
       <c r="AI37" s="30"/>
       <c r="AJ37" s="30"/>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A38" s="26" t="s">
         <v>279</v>
       </c>
@@ -6198,7 +6218,7 @@
       <c r="AI38" s="30"/>
       <c r="AJ38" s="30"/>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A39" s="26" t="s">
         <v>280</v>
       </c>
@@ -6239,7 +6259,7 @@
       <c r="AI39" s="30"/>
       <c r="AJ39" s="30"/>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A40" s="26" t="s">
         <v>281</v>
       </c>
@@ -6280,7 +6300,7 @@
       <c r="AI40" s="30"/>
       <c r="AJ40" s="30"/>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A41" s="26" t="s">
         <v>282</v>
       </c>
@@ -6321,7 +6341,7 @@
       <c r="AI41" s="30"/>
       <c r="AJ41" s="30"/>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A42" s="29">
         <v>4</v>
       </c>
@@ -6365,7 +6385,7 @@
       <c r="AI42" s="30"/>
       <c r="AJ42" s="30"/>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A43" s="26">
         <v>4.2</v>
       </c>
@@ -6406,7 +6426,7 @@
       <c r="AI43" s="30"/>
       <c r="AJ43" s="30"/>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A44" s="26" t="s">
         <v>284</v>
       </c>
@@ -6449,7 +6469,7 @@
       <c r="AI44" s="30"/>
       <c r="AJ44" s="30"/>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A45" s="26" t="s">
         <v>285</v>
       </c>
@@ -6494,7 +6514,7 @@
       <c r="AI45" s="30"/>
       <c r="AJ45" s="30"/>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A46" s="26" t="s">
         <v>286</v>
       </c>
@@ -6539,7 +6559,7 @@
       <c r="AI46" s="30"/>
       <c r="AJ46" s="30"/>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A47" s="26" t="s">
         <v>287</v>
       </c>
@@ -6584,7 +6604,7 @@
       <c r="AI47" s="30"/>
       <c r="AJ47" s="30"/>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A48" s="26" t="s">
         <v>288</v>
       </c>
@@ -6629,7 +6649,7 @@
       <c r="AI48" s="30"/>
       <c r="AJ48" s="30"/>
     </row>
-    <row r="49" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A49" s="26" t="s">
         <v>289</v>
       </c>
@@ -6674,7 +6694,7 @@
       <c r="AI49" s="30"/>
       <c r="AJ49" s="30"/>
     </row>
-    <row r="50" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A50" s="26" t="s">
         <v>290</v>
       </c>
@@ -6719,7 +6739,7 @@
       <c r="AI50" s="30"/>
       <c r="AJ50" s="30"/>
     </row>
-    <row r="51" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A51" s="26" t="s">
         <v>291</v>
       </c>
@@ -6764,7 +6784,7 @@
       <c r="AI51" s="30"/>
       <c r="AJ51" s="30"/>
     </row>
-    <row r="52" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A52" s="26" t="s">
         <v>292</v>
       </c>
@@ -6809,7 +6829,7 @@
       <c r="AI52" s="30"/>
       <c r="AJ52" s="30"/>
     </row>
-    <row r="53" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A53" s="26" t="s">
         <v>293</v>
       </c>
@@ -6854,7 +6874,7 @@
       <c r="AI53" s="30"/>
       <c r="AJ53" s="30"/>
     </row>
-    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A54" s="26" t="s">
         <v>294</v>
       </c>
@@ -6895,7 +6915,7 @@
       <c r="AI54" s="30"/>
       <c r="AJ54" s="30"/>
     </row>
-    <row r="55" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A55" s="26" t="s">
         <v>295</v>
       </c>
@@ -6936,7 +6956,7 @@
       <c r="AI55" s="30"/>
       <c r="AJ55" s="30"/>
     </row>
-    <row r="56" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A56" s="26" t="s">
         <v>296</v>
       </c>
@@ -6977,7 +6997,7 @@
       <c r="AI56" s="30"/>
       <c r="AJ56" s="30"/>
     </row>
-    <row r="57" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A57" s="26" t="s">
         <v>297</v>
       </c>
@@ -7018,7 +7038,7 @@
       <c r="AI57" s="30"/>
       <c r="AJ57" s="30"/>
     </row>
-    <row r="58" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A58" s="26" t="s">
         <v>298</v>
       </c>
@@ -7059,7 +7079,7 @@
       <c r="AI58" s="30"/>
       <c r="AJ58" s="30"/>
     </row>
-    <row r="59" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A59" s="26" t="s">
         <v>299</v>
       </c>
@@ -7104,7 +7124,7 @@
       <c r="AI59" s="30"/>
       <c r="AJ59" s="30"/>
     </row>
-    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A60" s="26" t="s">
         <v>300</v>
       </c>
@@ -7149,7 +7169,7 @@
       <c r="AI60" s="30"/>
       <c r="AJ60" s="30"/>
     </row>
-    <row r="61" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A61" s="26" t="s">
         <v>301</v>
       </c>
@@ -7194,7 +7214,7 @@
       <c r="AI61" s="30"/>
       <c r="AJ61" s="30"/>
     </row>
-    <row r="62" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A62" s="26" t="s">
         <v>302</v>
       </c>
@@ -7235,7 +7255,7 @@
       <c r="AI62" s="30"/>
       <c r="AJ62" s="30"/>
     </row>
-    <row r="63" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A63" s="26" t="s">
         <v>303</v>
       </c>
@@ -7276,7 +7296,7 @@
       <c r="AI63" s="30"/>
       <c r="AJ63" s="30"/>
     </row>
-    <row r="64" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A64" s="26" t="s">
         <v>304</v>
       </c>
@@ -7317,7 +7337,7 @@
       <c r="AI64" s="30"/>
       <c r="AJ64" s="30"/>
     </row>
-    <row r="65" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A65" s="26" t="s">
         <v>305</v>
       </c>
@@ -7358,7 +7378,7 @@
       <c r="AI65" s="30"/>
       <c r="AJ65" s="30"/>
     </row>
-    <row r="66" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A66" s="26">
         <v>4.3</v>
       </c>
@@ -7399,7 +7419,7 @@
       <c r="AI66" s="30"/>
       <c r="AJ66" s="30"/>
     </row>
-    <row r="67" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A67" s="26" t="s">
         <v>306</v>
       </c>
@@ -7440,7 +7460,7 @@
       <c r="AI67" s="30"/>
       <c r="AJ67" s="30"/>
     </row>
-    <row r="68" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A68" s="26" t="s">
         <v>307</v>
       </c>
@@ -7481,7 +7501,7 @@
       <c r="AI68" s="30"/>
       <c r="AJ68" s="30"/>
     </row>
-    <row r="69" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A69" s="26" t="s">
         <v>308</v>
       </c>
@@ -7522,83 +7542,83 @@
       <c r="AI69" s="30"/>
       <c r="AJ69" s="30"/>
     </row>
-    <row r="70" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C70" s="24"/>
       <c r="D70" s="24"/>
       <c r="J70" s="8"/>
     </row>
-    <row r="71" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C71" s="24"/>
       <c r="D71" s="24"/>
     </row>
-    <row r="72" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C72" s="24"/>
       <c r="D72" s="24"/>
     </row>
-    <row r="73" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C73" s="24"/>
       <c r="D73" s="24"/>
     </row>
-    <row r="74" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C74" s="24"/>
       <c r="D74" s="24"/>
     </row>
-    <row r="75" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C75" s="24"/>
       <c r="D75" s="24"/>
       <c r="J75" s="8"/>
     </row>
-    <row r="76" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C76" s="24"/>
       <c r="D76" s="24"/>
       <c r="J76" s="8"/>
     </row>
-    <row r="77" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C77" s="24"/>
       <c r="D77" s="24"/>
       <c r="J77" s="8"/>
     </row>
-    <row r="78" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C78" s="24"/>
       <c r="D78" s="24"/>
       <c r="J78" s="8"/>
     </row>
-    <row r="79" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C79" s="24"/>
       <c r="D79" s="24"/>
     </row>
-    <row r="80" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:36" x14ac:dyDescent="0.45">
       <c r="C80" s="24"/>
       <c r="D80" s="24"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C81" s="24"/>
       <c r="D81" s="24"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C82" s="24"/>
       <c r="D82" s="24"/>
       <c r="J82" s="8"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C83" s="24"/>
       <c r="D83" s="24"/>
       <c r="J83" s="8"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C84" s="24"/>
       <c r="D84" s="24"/>
       <c r="J84" s="8"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C85" s="24"/>
       <c r="D85" s="24"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.45">
       <c r="C86" s="24"/>
       <c r="D86" s="24"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A87" s="26"/>
       <c r="B87" s="26"/>
       <c r="C87" s="24"/>
@@ -7619,15 +7639,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEE8D46A-5F9F-434F-B5A2-7214C3C85F86}">
   <dimension ref="A3:AJ66"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.75" customWidth="1"/>
-    <col min="2" max="2" width="22.875" customWidth="1"/>
-    <col min="3" max="4" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="36" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" customWidth="1"/>
+    <col min="3" max="4" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="36" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -7735,7 +7755,7 @@
       </c>
       <c r="AJ3" s="23"/>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" s="26" t="s">
         <v>279</v>
       </c>
@@ -7783,7 +7803,7 @@
       <c r="AI4" s="30"/>
       <c r="AJ4" s="30"/>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" s="26" t="s">
         <v>280</v>
       </c>
@@ -7831,7 +7851,7 @@
       <c r="AI5" s="30"/>
       <c r="AJ5" s="30"/>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="26" t="s">
         <v>281</v>
       </c>
@@ -7879,7 +7899,7 @@
       <c r="AI6" s="30"/>
       <c r="AJ6" s="30"/>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="26" t="s">
         <v>282</v>
       </c>
@@ -7927,7 +7947,7 @@
       <c r="AI7" s="30"/>
       <c r="AJ7" s="30"/>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B8" s="26" t="s">
         <v>344</v>
       </c>
@@ -7969,7 +7989,7 @@
       <c r="AI8" s="30"/>
       <c r="AJ8" s="30"/>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B9" s="26" t="s">
         <v>343</v>
       </c>
@@ -8007,7 +8027,7 @@
       <c r="AI9" s="30"/>
       <c r="AJ9" s="30"/>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B10" s="26" t="s">
         <v>342</v>
       </c>
@@ -8049,7 +8069,7 @@
       <c r="AI10" s="30"/>
       <c r="AJ10" s="30"/>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B11" s="26" t="s">
         <v>341</v>
       </c>
@@ -8091,7 +8111,7 @@
       <c r="AI11" s="30"/>
       <c r="AJ11" s="30"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B12" s="26" t="s">
         <v>340</v>
       </c>
@@ -8133,7 +8153,7 @@
       <c r="AI12" s="30"/>
       <c r="AJ12" s="30"/>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B13" s="26" t="s">
         <v>323</v>
       </c>
@@ -8175,7 +8195,7 @@
       <c r="AI13" s="30"/>
       <c r="AJ13" s="30"/>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B14" s="26" t="s">
         <v>339</v>
       </c>
@@ -8217,7 +8237,7 @@
       <c r="AI14" s="30"/>
       <c r="AJ14" s="30"/>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B15" s="26" t="s">
         <v>338</v>
       </c>
@@ -8259,7 +8279,7 @@
       <c r="AI15" s="30"/>
       <c r="AJ15" s="30"/>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B16" s="26" t="s">
         <v>337</v>
       </c>
@@ -8301,7 +8321,7 @@
       <c r="AI16" s="30"/>
       <c r="AJ16" s="30"/>
     </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B17" s="26" t="s">
         <v>336</v>
       </c>
@@ -8343,7 +8363,7 @@
       <c r="AI17" s="30"/>
       <c r="AJ17" s="30"/>
     </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B18" s="26" t="s">
         <v>335</v>
       </c>
@@ -8385,7 +8405,7 @@
       <c r="AI18" s="30"/>
       <c r="AJ18" s="30"/>
     </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B19" s="26" t="s">
         <v>334</v>
       </c>
@@ -8427,7 +8447,7 @@
       <c r="AI19" s="30"/>
       <c r="AJ19" s="30"/>
     </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B20" s="26" t="s">
         <v>333</v>
       </c>
@@ -8469,7 +8489,7 @@
       <c r="AI20" s="30"/>
       <c r="AJ20" s="30"/>
     </row>
-    <row r="21" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B21" s="26" t="s">
         <v>391</v>
       </c>
@@ -8511,7 +8531,7 @@
       <c r="AI21" s="30"/>
       <c r="AJ21" s="30"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A22" s="26">
         <v>4.3</v>
       </c>
@@ -8555,7 +8575,7 @@
       <c r="AI22" s="30"/>
       <c r="AJ22" s="30"/>
     </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A23" s="26" t="s">
         <v>306</v>
       </c>
@@ -8599,7 +8619,7 @@
       <c r="AI23" s="30"/>
       <c r="AJ23" s="30"/>
     </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A24" s="26" t="s">
         <v>351</v>
       </c>
@@ -8643,7 +8663,7 @@
       <c r="AI24" s="30"/>
       <c r="AJ24" s="30"/>
     </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A25" s="26" t="s">
         <v>352</v>
       </c>
@@ -8687,7 +8707,7 @@
       <c r="AI25" s="30"/>
       <c r="AJ25" s="30"/>
     </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A26" s="26" t="s">
         <v>353</v>
       </c>
@@ -8731,7 +8751,7 @@
       <c r="AI26" s="30"/>
       <c r="AJ26" s="30"/>
     </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A27" s="26" t="s">
         <v>368</v>
       </c>
@@ -8775,7 +8795,7 @@
       <c r="AI27" s="30"/>
       <c r="AJ27" s="30"/>
     </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A28" s="26" t="s">
         <v>354</v>
       </c>
@@ -8819,7 +8839,7 @@
       <c r="AI28" s="30"/>
       <c r="AJ28" s="30"/>
     </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A29" s="26" t="s">
         <v>355</v>
       </c>
@@ -8863,7 +8883,7 @@
       <c r="AI29" s="30"/>
       <c r="AJ29" s="30"/>
     </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A30" s="26" t="s">
         <v>356</v>
       </c>
@@ -8907,7 +8927,7 @@
       <c r="AI30" s="30"/>
       <c r="AJ30" s="30"/>
     </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A31" s="26" t="s">
         <v>357</v>
       </c>
@@ -8951,7 +8971,7 @@
       <c r="AI31" s="30"/>
       <c r="AJ31" s="30"/>
     </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A32" s="26" t="s">
         <v>358</v>
       </c>
@@ -8995,7 +9015,7 @@
       <c r="AI32" s="30"/>
       <c r="AJ32" s="30"/>
     </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A33" s="26" t="s">
         <v>369</v>
       </c>
@@ -9039,7 +9059,7 @@
       <c r="AI33" s="30"/>
       <c r="AJ33" s="30"/>
     </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A34" s="26" t="s">
         <v>359</v>
       </c>
@@ -9083,7 +9103,7 @@
       <c r="AI34" s="30"/>
       <c r="AJ34" s="30"/>
     </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A35" s="26" t="s">
         <v>360</v>
       </c>
@@ -9127,7 +9147,7 @@
       <c r="AI35" s="30"/>
       <c r="AJ35" s="30"/>
     </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A36" s="26" t="s">
         <v>370</v>
       </c>
@@ -9171,7 +9191,7 @@
       <c r="AI36" s="30"/>
       <c r="AJ36" s="30"/>
     </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A37" s="26" t="s">
         <v>361</v>
       </c>
@@ -9215,7 +9235,7 @@
       <c r="AI37" s="30"/>
       <c r="AJ37" s="30"/>
     </row>
-    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A38" s="26" t="s">
         <v>362</v>
       </c>
@@ -9259,7 +9279,7 @@
       <c r="AI38" s="30"/>
       <c r="AJ38" s="30"/>
     </row>
-    <row r="39" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A39" s="26" t="s">
         <v>363</v>
       </c>
@@ -9303,7 +9323,7 @@
       <c r="AI39" s="30"/>
       <c r="AJ39" s="30"/>
     </row>
-    <row r="40" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A40" s="26" t="s">
         <v>364</v>
       </c>
@@ -9347,7 +9367,7 @@
       <c r="AI40" s="30"/>
       <c r="AJ40" s="30"/>
     </row>
-    <row r="41" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A41" s="26" t="s">
         <v>371</v>
       </c>
@@ -9391,7 +9411,7 @@
       <c r="AI41" s="30"/>
       <c r="AJ41" s="30"/>
     </row>
-    <row r="42" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A42" s="26" t="s">
         <v>365</v>
       </c>
@@ -9435,7 +9455,7 @@
       <c r="AI42" s="30"/>
       <c r="AJ42" s="30"/>
     </row>
-    <row r="43" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A43" s="26" t="s">
         <v>366</v>
       </c>
@@ -9479,7 +9499,7 @@
       <c r="AI43" s="30"/>
       <c r="AJ43" s="30"/>
     </row>
-    <row r="44" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A44" s="26" t="s">
         <v>367</v>
       </c>
@@ -9523,7 +9543,7 @@
       <c r="AI44" s="30"/>
       <c r="AJ44" s="30"/>
     </row>
-    <row r="45" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A45" s="26">
         <v>4.4000000000000004</v>
       </c>
@@ -9567,7 +9587,7 @@
       <c r="AI45" s="30"/>
       <c r="AJ45" s="30"/>
     </row>
-    <row r="46" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A46" s="26" t="s">
         <v>372</v>
       </c>
@@ -9611,7 +9631,7 @@
       <c r="AI46" s="30"/>
       <c r="AJ46" s="30"/>
     </row>
-    <row r="47" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" x14ac:dyDescent="0.45">
       <c r="F47" s="30"/>
       <c r="G47" s="30"/>
       <c r="H47" s="30"/>
@@ -9644,7 +9664,7 @@
       <c r="AI47" s="30"/>
       <c r="AJ47" s="30"/>
     </row>
-    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.45">
       <c r="F48" s="30"/>
       <c r="G48" s="30"/>
       <c r="H48" s="30"/>
@@ -9677,53 +9697,53 @@
       <c r="AI48" s="30"/>
       <c r="AJ48" s="30"/>
     </row>
-    <row r="49" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="3:10" x14ac:dyDescent="0.45">
       <c r="J49" s="8"/>
     </row>
-    <row r="54" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="3:10" x14ac:dyDescent="0.45">
       <c r="J54" s="8"/>
     </row>
-    <row r="55" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="3:10" x14ac:dyDescent="0.45">
       <c r="J55" s="8"/>
     </row>
-    <row r="56" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="3:10" x14ac:dyDescent="0.45">
       <c r="J56" s="8"/>
     </row>
-    <row r="57" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="3:10" x14ac:dyDescent="0.45">
       <c r="J57" s="8"/>
     </row>
-    <row r="59" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C59" s="24"/>
       <c r="D59" s="24"/>
     </row>
-    <row r="60" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C60" s="24"/>
       <c r="D60" s="24"/>
     </row>
-    <row r="61" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C61" s="24"/>
       <c r="D61" s="24"/>
       <c r="J61" s="8"/>
     </row>
-    <row r="62" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C62" s="24"/>
       <c r="D62" s="24"/>
       <c r="J62" s="8"/>
     </row>
-    <row r="63" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C63" s="24"/>
       <c r="D63" s="24"/>
       <c r="J63" s="8"/>
     </row>
-    <row r="64" spans="3:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="3:10" x14ac:dyDescent="0.45">
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="26"/>
       <c r="B66" s="26"/>
       <c r="C66" s="24"/>
@@ -9754,13 +9774,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7BD34BE-E30F-40B4-B28D-0BE83B9217E7}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="6" max="36" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="6" max="36" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -9879,13 +9899,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53079CFF-55B9-4D5D-98A9-95E3A3A1065C}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="6" max="36" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="6" max="36" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -10004,13 +10024,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2556B67F-871D-483A-9A7E-BEC7C4A203C4}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="6" max="36" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="6" max="36" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -10127,13 +10147,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BCA75F-35B4-4193-9D7C-1615CE129556}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="6" max="36" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="6" max="36" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>246</v>
       </c>
@@ -10252,13 +10272,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D4A06CE-94E2-4CB6-8F60-16007918C401}">
   <dimension ref="A3:AJ3"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="13.875" customWidth="1"/>
-    <col min="6" max="36" width="5.375" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
+    <col min="6" max="36" width="5.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>246</v>
       </c>

--- a/간트차트_250526.xlsx
+++ b/간트차트_250526.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47C38377-D12D-4DE7-8471-D9C8F102E9E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AF8C19-18C3-4F23-A6D4-28B47F139962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1960" yWindow="900" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="간트 차트 시각화" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="393">
   <si>
     <t>3월</t>
   </si>
@@ -482,858 +482,864 @@
     <t>4.2.2.3 영웅 정보 (계획)</t>
   </si>
   <si>
+    <t>4.2.2.4 시설 강화 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.2.4 시설 강화 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.3 의무실 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.3 의무실 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.3.1 영웅 회복 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.3.1 영웅 회복 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.3.2 시설 강화 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.3.2 시설 강화 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.4 상점 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.4 상점 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.4.1 로컬 상점 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.4.1 로컬 상점 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.4.2 온라인 상점 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.4.2 온라인 상점 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.5 보유 재화 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.5 보유 재화 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.6 친구 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.6 친구 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.6.1 친구 목록 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.6.1 친구 목록 (실제)</t>
+  </si>
+  <si>
+    <t>4.2.6.2 우편함 (계획)</t>
+  </si>
+  <si>
+    <t>4.2.6.2 우편함 (실제)</t>
+  </si>
+  <si>
+    <t>4.3 던전 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.1 던전 진입 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.1 던전 진입 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.1.1 오브젝트 랜덤 배정 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.1.1 오브젝트 랜덤 배정 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.1.2 미니맵 정보 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.1.2 미니맵 정보 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.1.3 몬스터 스폰 랜덤 배정 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.1.3 몬스터 스폰 랜덤 배정 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.2 기본 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.2 기본 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.2.1 이동 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.2.1 이동 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.2.2 미니맵 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.2.2 미니맵 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.2.3 탐험 포기 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.2.3 탐험 포기 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.2.4 인벤토리 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.2.4 인벤토리 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.2.5 카메라 제어 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.2.5 카메라 제어 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.3 상호작용 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.3 상호작용 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.3.1 오브젝트 탐지 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.3.1 오브젝트 탐지 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.3.2 상호작용 이벤트 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.3.2 상호작용 이벤트 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.4 전투 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.4 전투 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.4.1 영웅 정보 호출 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.4.1 영웅 정보 호출 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.4.2 스킬 정보 호출 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.4.2 스킬 정보 호출 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.4.3 대상 선택 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.4.3 대상 선택 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.4.4 카메라 이동 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.4.4 카메라 이동 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.5 던전 완료 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.5 던전 완료 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.5.1 성공/실패 확인 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.5.1 성공/실패 확인 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.5.2 영웅 데이터 저장 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.5.2 영웅 데이터 저장 (실제)</t>
+  </si>
+  <si>
+    <t>4.3.5.3 아이템 데이터 저장 (계획)</t>
+  </si>
+  <si>
+    <t>4.3.5.3 아이템 데이터 저장 (실제)</t>
+  </si>
+  <si>
+    <t>4.4 아웃라인 쉐이더 (계획)</t>
+  </si>
+  <si>
+    <t>4.4.1 캐릭터 아웃라인 (계획)</t>
+  </si>
+  <si>
+    <t>4.4.1 캐릭터 아웃라인 (실제)</t>
+  </si>
+  <si>
+    <t>4.4.2 오브젝트 아웃라인 (계획)</t>
+  </si>
+  <si>
+    <t>4.4.2 오브젝트 아웃라인 (실제)</t>
+  </si>
+  <si>
+    <t>5 테스트 (계획)</t>
+  </si>
+  <si>
+    <t>5.1 1차 테스트 실시 (계획)</t>
+  </si>
+  <si>
+    <t>5.2 2차 테스트 실시 (계획)</t>
+  </si>
+  <si>
+    <t>6 버그 수정 및 밸런스 조정 (계획)</t>
+  </si>
+  <si>
+    <t>6.1 버그 수정 (계획)</t>
+  </si>
+  <si>
+    <t>6.2 능력치 밸런스 조정 (계획)</t>
+  </si>
+  <si>
+    <t>6.2.1 영웅 능력치 밸런스 (계획)</t>
+  </si>
+  <si>
+    <t>6.2.1 영웅 능력치 밸런스 (실제)</t>
+  </si>
+  <si>
+    <t>6.2.2 스킬 능력치 밸런스 (계획)</t>
+  </si>
+  <si>
+    <t>6.2.2 스킬 능력치 밸런스 (실제)</t>
+  </si>
+  <si>
+    <t>6.2.3 아이템 밸런스 (계획)</t>
+  </si>
+  <si>
+    <t>6.2.3 아이템 밸런스 (실제)</t>
+  </si>
+  <si>
+    <t>6.2.4 몬스터 밸런스 (계획)</t>
+  </si>
+  <si>
+    <t>6.2.4 몬스터 밸런스 (실제)</t>
+  </si>
+  <si>
+    <t>실제 소요 기간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예상 소요 기간</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업명</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 문서 작성 (계획)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시작일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>종료일</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작업 이름</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WBS 번호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>메인로비</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UI/UX 디자인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.2.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.2.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.3.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.4.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.4.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.6.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.1.6.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.3.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.3.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.3.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.4.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.4.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.4.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기능 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.1.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.1.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.1.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.1.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.2.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.2.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.2.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.2.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.3.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.3.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.4.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.4.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.6.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.2.6.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.3.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.3.1.1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.3.1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미니맵 정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트 랜덤 배정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전 진입</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>우편함</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>친구 목록</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>친구</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유재화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>온라인 상점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로컬 상점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시설 강화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 회복</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의무실</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 정보</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 성장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 고용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 관리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 장착 여부 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유 아이템 정보 호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파티 영웅 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유 영웅 정보 호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과 패널</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐험 완료 전환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트 UI 변경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>던전 완료</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>대상 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 패널</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전투</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용 UI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>탐험 포기</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미니맵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인벤토리 탭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>퀘스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동 버튼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본 화면</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보유 재화</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>파티 구성</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 선택</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.3.1.1</t>
+  </si>
+  <si>
+    <t>4.3.1.2</t>
+  </si>
+  <si>
+    <t>4.3.1.3</t>
+  </si>
+  <si>
+    <t>4.3.2.1</t>
+  </si>
+  <si>
+    <t>4.3.2.2</t>
+  </si>
+  <si>
+    <t>4.3.2.3</t>
+  </si>
+  <si>
+    <t>4.3.2.4</t>
+  </si>
+  <si>
+    <t>4.3.2.5</t>
+  </si>
+  <si>
+    <t>4.3.3.1</t>
+  </si>
+  <si>
+    <t>4.3.3.2</t>
+  </si>
+  <si>
+    <t>4.3.4.1</t>
+  </si>
+  <si>
+    <t>4.3.4.2</t>
+  </si>
+  <si>
+    <t>4.3.4.3</t>
+  </si>
+  <si>
+    <t>4.3.4.4</t>
+  </si>
+  <si>
+    <t>4.3.5.1</t>
+  </si>
+  <si>
+    <t>4.3.5.2</t>
+  </si>
+  <si>
+    <t>4.3.5.3</t>
+  </si>
+  <si>
+    <t>4.3.2</t>
+  </si>
+  <si>
+    <t>4.3.3</t>
+  </si>
+  <si>
+    <t>4.3.4</t>
+  </si>
+  <si>
+    <t>4.3.5</t>
+  </si>
+  <si>
+    <t>4.4.1</t>
+  </si>
+  <si>
+    <t>캐릭터 아웃라인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아웃라인 쉐이더</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이템 데이터 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 데이터 저장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성공/실패 확인</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 정보 호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>영웅 정보 호출</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용 이벤트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오브젝트 탐지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상호작용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카메라 제어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이동</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기본</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>몬스터 스폰 랜덤 배정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.2.5 튜토리얼 관련</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김한서</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박태영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>애니메이션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>4.2.2.3 영웅 정보 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.2.4 시설 강화 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.2.4 시설 강화 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.3 의무실 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.3 의무실 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.3.1 영웅 회복 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.3.1 영웅 회복 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.3.2 시설 강화 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.3.2 시설 강화 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.4 상점 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.4 상점 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.4.1 로컬 상점 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.4.1 로컬 상점 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.4.2 온라인 상점 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.4.2 온라인 상점 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.5 보유 재화 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.5 보유 재화 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.6 친구 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.6 친구 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.6.1 친구 목록 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.6.1 친구 목록 (실제)</t>
-  </si>
-  <si>
-    <t>4.2.6.2 우편함 (계획)</t>
-  </si>
-  <si>
-    <t>4.2.6.2 우편함 (실제)</t>
-  </si>
-  <si>
-    <t>4.3 던전 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.1 던전 진입 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.1 던전 진입 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.1.1 오브젝트 랜덤 배정 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.1.1 오브젝트 랜덤 배정 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.1.2 미니맵 정보 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.1.2 미니맵 정보 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.1.3 몬스터 스폰 랜덤 배정 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.1.3 몬스터 스폰 랜덤 배정 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.2 기본 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.2 기본 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.2.1 이동 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.2.1 이동 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.2.2 미니맵 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.2.2 미니맵 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.2.3 탐험 포기 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.2.3 탐험 포기 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.2.4 인벤토리 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.2.4 인벤토리 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.2.5 카메라 제어 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.2.5 카메라 제어 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.3 상호작용 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.3 상호작용 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.3.1 오브젝트 탐지 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.3.1 오브젝트 탐지 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.3.2 상호작용 이벤트 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.3.2 상호작용 이벤트 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.4 전투 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.4 전투 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.4.1 영웅 정보 호출 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.4.1 영웅 정보 호출 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.4.2 스킬 정보 호출 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.4.2 스킬 정보 호출 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.4.3 대상 선택 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.4.3 대상 선택 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.4.4 카메라 이동 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.4.4 카메라 이동 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.5 던전 완료 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.5 던전 완료 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.5.1 성공/실패 확인 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.5.1 성공/실패 확인 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.5.2 영웅 데이터 저장 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.5.2 영웅 데이터 저장 (실제)</t>
-  </si>
-  <si>
-    <t>4.3.5.3 아이템 데이터 저장 (계획)</t>
-  </si>
-  <si>
-    <t>4.3.5.3 아이템 데이터 저장 (실제)</t>
-  </si>
-  <si>
-    <t>4.4 아웃라인 쉐이더 (계획)</t>
-  </si>
-  <si>
-    <t>4.4.1 캐릭터 아웃라인 (계획)</t>
-  </si>
-  <si>
-    <t>4.4.1 캐릭터 아웃라인 (실제)</t>
-  </si>
-  <si>
-    <t>4.4.2 오브젝트 아웃라인 (계획)</t>
-  </si>
-  <si>
-    <t>4.4.2 오브젝트 아웃라인 (실제)</t>
-  </si>
-  <si>
-    <t>5 테스트 (계획)</t>
-  </si>
-  <si>
-    <t>5.1 1차 테스트 실시 (계획)</t>
-  </si>
-  <si>
-    <t>5.2 2차 테스트 실시 (계획)</t>
-  </si>
-  <si>
-    <t>6 버그 수정 및 밸런스 조정 (계획)</t>
-  </si>
-  <si>
-    <t>6.1 버그 수정 (계획)</t>
-  </si>
-  <si>
-    <t>6.2 능력치 밸런스 조정 (계획)</t>
-  </si>
-  <si>
-    <t>6.2.1 영웅 능력치 밸런스 (계획)</t>
-  </si>
-  <si>
-    <t>6.2.1 영웅 능력치 밸런스 (실제)</t>
-  </si>
-  <si>
-    <t>6.2.2 스킬 능력치 밸런스 (계획)</t>
-  </si>
-  <si>
-    <t>6.2.2 스킬 능력치 밸런스 (실제)</t>
-  </si>
-  <si>
-    <t>6.2.3 아이템 밸런스 (계획)</t>
-  </si>
-  <si>
-    <t>6.2.3 아이템 밸런스 (실제)</t>
-  </si>
-  <si>
-    <t>6.2.4 몬스터 밸런스 (계획)</t>
-  </si>
-  <si>
-    <t>6.2.4 몬스터 밸런스 (실제)</t>
-  </si>
-  <si>
-    <t>실제 소요 기간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>예상 소요 기간</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업명</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1 문서 작성 (계획)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>담당자</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시작일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>종료일</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>작업 이름</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>WBS 번호</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>메인로비</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UI/UX 디자인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.2.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.2.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.2.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.3.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.3.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.4.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.4.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.6.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.1.6.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.1.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.3.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.3.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.3.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.3.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.4.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.4.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.4.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기능 구현</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.1.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.1.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.1.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.1.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.2.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.2.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.2.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.2.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.3.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.3.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.4.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.4.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.6.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.2.6.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.3.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.3.1.1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.3.1.2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미니맵 정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오브젝트 랜덤 배정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>던전 진입</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>던전</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>우편함</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>친구 목록</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>친구</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보유재화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>온라인 상점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>로컬 상점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시설 강화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅 회복</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>의무실</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅 정보</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅 성장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅 고용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅 관리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 장착 여부 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인벤토리 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보유 아이템 정보 호출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파티 영웅 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보유 영웅 정보 호출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>던전 선택</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결과 패널</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탐험 완료 전환</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>퀘스트 UI 변경</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>던전 완료</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>대상 선택</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인벤토리</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 패널</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전투</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상호작용 UI</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>탐험 포기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미니맵</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인벤토리 탭</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>퀘스트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동 버튼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본 화면</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>보유 재화</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>파티 구성</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템 선택</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4.3.1.1</t>
-  </si>
-  <si>
-    <t>4.3.1.2</t>
-  </si>
-  <si>
-    <t>4.3.1.3</t>
-  </si>
-  <si>
-    <t>4.3.2.1</t>
-  </si>
-  <si>
-    <t>4.3.2.2</t>
-  </si>
-  <si>
-    <t>4.3.2.3</t>
-  </si>
-  <si>
-    <t>4.3.2.4</t>
-  </si>
-  <si>
-    <t>4.3.2.5</t>
-  </si>
-  <si>
-    <t>4.3.3.1</t>
-  </si>
-  <si>
-    <t>4.3.3.2</t>
-  </si>
-  <si>
-    <t>4.3.4.1</t>
-  </si>
-  <si>
-    <t>4.3.4.2</t>
-  </si>
-  <si>
-    <t>4.3.4.3</t>
-  </si>
-  <si>
-    <t>4.3.4.4</t>
-  </si>
-  <si>
-    <t>4.3.5.1</t>
-  </si>
-  <si>
-    <t>4.3.5.2</t>
-  </si>
-  <si>
-    <t>4.3.5.3</t>
-  </si>
-  <si>
-    <t>4.3.2</t>
-  </si>
-  <si>
-    <t>4.3.3</t>
-  </si>
-  <si>
-    <t>4.3.4</t>
-  </si>
-  <si>
-    <t>4.3.5</t>
-  </si>
-  <si>
-    <t>4.4.1</t>
-  </si>
-  <si>
-    <t>캐릭터 아웃라인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아웃라인 쉐이더</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>아이템 데이터 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅 데이터 저장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>성공/실패 확인</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카메라 이동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>스킬 정보 호출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>영웅 정보 호출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상호작용 이벤트</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>오브젝트 탐지</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>상호작용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>카메라 제어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>이동</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>기본</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>몬스터 스폰 랜덤 배정</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3.2.5 튜토리얼 관련</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>김한서</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>박태영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>애니메이션</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">하늘색: 당연적  자주: 일차원적
+분홍: 매력적   노랑: 미완 주황: 삭제   </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1363,7 +1369,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1420,13 +1426,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1548,7 +1566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1599,20 +1617,33 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2047,79 +2078,82 @@
       <c r="D1"/>
     </row>
     <row r="2" spans="1:57" ht="34" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="39" t="s">
+        <v>392</v>
+      </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="34" t="s">
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="34" t="s">
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="37"/>
+      <c r="N2" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="34" t="s">
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="34" t="s">
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="34" t="s">
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="37"/>
+      <c r="AA2" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="AB2" s="35"/>
-      <c r="AC2" s="35"/>
-      <c r="AD2" s="35"/>
-      <c r="AE2" s="34" t="s">
+      <c r="AB2" s="37"/>
+      <c r="AC2" s="37"/>
+      <c r="AD2" s="37"/>
+      <c r="AE2" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="35"/>
-      <c r="AG2" s="35"/>
-      <c r="AH2" s="35"/>
-      <c r="AI2" s="34" t="s">
+      <c r="AF2" s="37"/>
+      <c r="AG2" s="37"/>
+      <c r="AH2" s="37"/>
+      <c r="AI2" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="AJ2" s="35"/>
-      <c r="AK2" s="35"/>
-      <c r="AL2" s="35"/>
-      <c r="AM2" s="35"/>
-      <c r="AN2" s="34" t="s">
+      <c r="AJ2" s="37"/>
+      <c r="AK2" s="37"/>
+      <c r="AL2" s="37"/>
+      <c r="AM2" s="37"/>
+      <c r="AN2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="AO2" s="35"/>
-      <c r="AP2" s="35"/>
-      <c r="AQ2" s="35"/>
+      <c r="AO2" s="37"/>
+      <c r="AP2" s="37"/>
+      <c r="AQ2" s="37"/>
     </row>
     <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D3" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>9</v>
@@ -2255,7 +2289,7 @@
     </row>
     <row r="4" spans="1:57" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B4" s="19">
         <v>8</v>
@@ -2419,7 +2453,7 @@
       <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.45">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="40" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="11"/>
@@ -2427,7 +2461,7 @@
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="40" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="11"/>
@@ -2438,7 +2472,7 @@
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="40" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="11"/>
@@ -2446,7 +2480,7 @@
       <c r="D18" s="5"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A19" s="38" t="s">
+      <c r="A19" s="34" t="s">
         <v>31</v>
       </c>
       <c r="B19" s="11"/>
@@ -2458,7 +2492,7 @@
       <c r="G19" s="17"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="34" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="11"/>
@@ -2466,7 +2500,7 @@
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A21" s="36" t="s">
+      <c r="A21" s="43" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="11"/>
@@ -2480,7 +2514,7 @@
       <c r="K21" s="17"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A22" s="36" t="s">
+      <c r="A22" s="43" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="11"/>
@@ -2488,7 +2522,7 @@
       <c r="D22" s="5"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="43" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="11"/>
@@ -2502,7 +2536,7 @@
       <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="43" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="11"/>
@@ -2589,7 +2623,7 @@
       <c r="D31" s="5"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A32" s="38" t="s">
+      <c r="A32" s="34" t="s">
         <v>44</v>
       </c>
       <c r="B32" s="11"/>
@@ -2601,7 +2635,7 @@
       <c r="G32" s="17"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A33" s="38" t="s">
+      <c r="A33" s="34" t="s">
         <v>45</v>
       </c>
       <c r="B33" s="11"/>
@@ -2609,7 +2643,7 @@
       <c r="D33" s="5"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A34" s="38" t="s">
+      <c r="A34" s="34" t="s">
         <v>46</v>
       </c>
       <c r="B34" s="11"/>
@@ -2618,7 +2652,7 @@
       <c r="G34" s="17"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A35" s="38" t="s">
+      <c r="A35" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B35" s="11"/>
@@ -3366,7 +3400,7 @@
     </row>
     <row r="111" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A111" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B111" s="11"/>
       <c r="C111" s="11"/>
@@ -3409,7 +3443,7 @@
       <c r="K113" s="17"/>
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A114" t="s">
+      <c r="A114" s="35" t="s">
         <v>125</v>
       </c>
       <c r="B114" s="11"/>
@@ -3420,7 +3454,7 @@
       <c r="J114" s="17"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A115" t="s">
+      <c r="A115" s="35" t="s">
         <v>126</v>
       </c>
       <c r="B115" s="11"/>
@@ -3430,7 +3464,7 @@
       </c>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A116" s="39" t="s">
+      <c r="A116" s="35" t="s">
         <v>127</v>
       </c>
       <c r="B116" s="11"/>
@@ -3441,7 +3475,7 @@
       <c r="K116" s="17"/>
     </row>
     <row r="117" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A117" s="39" t="s">
+      <c r="A117" s="35" t="s">
         <v>128</v>
       </c>
       <c r="B117" s="11"/>
@@ -3638,7 +3672,7 @@
       <c r="D136" s="5"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A137" s="37" t="s">
+      <c r="A137" s="40" t="s">
         <v>148</v>
       </c>
       <c r="B137" s="11"/>
@@ -3649,7 +3683,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A138" s="37" t="s">
+      <c r="A138" s="40" t="s">
         <v>149</v>
       </c>
       <c r="B138" s="11"/>
@@ -3657,7 +3691,7 @@
       <c r="D138" s="5"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A139" s="37" t="s">
+      <c r="A139" s="42" t="s">
         <v>150</v>
       </c>
       <c r="B139" s="11"/>
@@ -3668,16 +3702,16 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A140" s="37" t="s">
-        <v>151</v>
+      <c r="A140" s="42" t="s">
+        <v>391</v>
       </c>
       <c r="B140" s="11"/>
       <c r="C140" s="11"/>
       <c r="D140" s="5"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A141" s="37" t="s">
-        <v>152</v>
+      <c r="A141" s="42" t="s">
+        <v>151</v>
       </c>
       <c r="B141" s="11"/>
       <c r="C141" s="11"/>
@@ -3687,8 +3721,8 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A142" s="37" t="s">
-        <v>153</v>
+      <c r="A142" s="42" t="s">
+        <v>152</v>
       </c>
       <c r="B142" s="11"/>
       <c r="C142" s="11"/>
@@ -3696,7 +3730,7 @@
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="11"/>
@@ -3707,15 +3741,15 @@
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B144" s="11"/>
       <c r="C144" s="11"/>
       <c r="D144" s="5"/>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A145" s="37" t="s">
-        <v>156</v>
+      <c r="A145" s="40" t="s">
+        <v>155</v>
       </c>
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
@@ -3725,16 +3759,16 @@
       <c r="O145" s="17"/>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A146" s="37" t="s">
-        <v>157</v>
+      <c r="A146" s="40" t="s">
+        <v>156</v>
       </c>
       <c r="B146" s="11"/>
       <c r="C146" s="11"/>
       <c r="D146" s="5"/>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A147" s="37" t="s">
-        <v>158</v>
+      <c r="A147" s="42" t="s">
+        <v>157</v>
       </c>
       <c r="B147" s="11"/>
       <c r="C147" s="11"/>
@@ -3744,8 +3778,8 @@
       <c r="O147" s="17"/>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A148" s="37" t="s">
-        <v>159</v>
+      <c r="A148" s="42" t="s">
+        <v>158</v>
       </c>
       <c r="B148" s="11"/>
       <c r="C148" s="11"/>
@@ -3753,7 +3787,7 @@
     </row>
     <row r="149" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B149" s="11"/>
       <c r="C149" s="11"/>
@@ -3764,15 +3798,15 @@
     </row>
     <row r="150" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B150" s="11"/>
       <c r="C150" s="11"/>
       <c r="D150" s="5"/>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A151" s="37" t="s">
-        <v>162</v>
+      <c r="A151" s="40" t="s">
+        <v>161</v>
       </c>
       <c r="B151" s="11"/>
       <c r="C151" s="11"/>
@@ -3782,16 +3816,16 @@
       <c r="O151" s="17"/>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A152" s="37" t="s">
-        <v>163</v>
+      <c r="A152" s="40" t="s">
+        <v>162</v>
       </c>
       <c r="B152" s="11"/>
       <c r="C152" s="11"/>
       <c r="D152" s="5"/>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A153" s="38" t="s">
-        <v>164</v>
+      <c r="A153" s="34" t="s">
+        <v>163</v>
       </c>
       <c r="B153" s="11"/>
       <c r="C153" s="11"/>
@@ -3801,8 +3835,8 @@
       <c r="O153" s="17"/>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A154" s="38" t="s">
-        <v>165</v>
+      <c r="A154" s="34" t="s">
+        <v>164</v>
       </c>
       <c r="B154" s="11"/>
       <c r="C154" s="11"/>
@@ -3810,7 +3844,7 @@
     </row>
     <row r="155" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B155" s="11"/>
       <c r="C155" s="11"/>
@@ -3821,7 +3855,7 @@
     </row>
     <row r="156" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B156" s="11"/>
       <c r="C156" s="11"/>
@@ -3829,7 +3863,7 @@
     </row>
     <row r="157" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B157" s="11"/>
       <c r="C157" s="11"/>
@@ -3840,15 +3874,15 @@
     </row>
     <row r="158" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B158" s="11"/>
       <c r="C158" s="11"/>
       <c r="D158" s="5"/>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A159" s="38" t="s">
-        <v>170</v>
+      <c r="A159" s="34" t="s">
+        <v>169</v>
       </c>
       <c r="B159" s="11"/>
       <c r="C159" s="11"/>
@@ -3858,16 +3892,16 @@
       <c r="P159" s="17"/>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A160" s="38" t="s">
-        <v>171</v>
+      <c r="A160" s="34" t="s">
+        <v>170</v>
       </c>
       <c r="B160" s="11"/>
       <c r="C160" s="11"/>
       <c r="D160" s="5"/>
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A161" s="38" t="s">
-        <v>172</v>
+      <c r="A161" s="34" t="s">
+        <v>171</v>
       </c>
       <c r="B161" s="11"/>
       <c r="C161" s="11"/>
@@ -3877,8 +3911,8 @@
       <c r="P161" s="17"/>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A162" s="38" t="s">
-        <v>173</v>
+      <c r="A162" s="34" t="s">
+        <v>172</v>
       </c>
       <c r="B162" s="11"/>
       <c r="C162" s="11"/>
@@ -3886,7 +3920,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A163" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B163" s="11"/>
       <c r="C163" s="11"/>
@@ -3901,7 +3935,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B164" s="11"/>
       <c r="C164" s="11"/>
@@ -3913,7 +3947,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B165" s="11"/>
       <c r="C165" s="11"/>
@@ -3921,7 +3955,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A166" s="8" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B166" s="11"/>
       <c r="C166" s="11"/>
@@ -3932,15 +3966,15 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A167" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B167" s="11"/>
       <c r="C167" s="11"/>
       <c r="D167" s="5"/>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A168" s="38" t="s">
-        <v>179</v>
+      <c r="A168" s="34" t="s">
+        <v>178</v>
       </c>
       <c r="B168" s="11"/>
       <c r="C168" s="11"/>
@@ -3951,16 +3985,16 @@
       <c r="R168" s="17"/>
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A169" s="38" t="s">
-        <v>180</v>
+      <c r="A169" s="34" t="s">
+        <v>179</v>
       </c>
       <c r="B169" s="11"/>
       <c r="C169" s="11"/>
       <c r="D169" s="5"/>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A170" s="37" t="s">
-        <v>181</v>
+      <c r="A170" s="40" t="s">
+        <v>180</v>
       </c>
       <c r="B170" s="11"/>
       <c r="C170" s="11"/>
@@ -3970,8 +4004,8 @@
       <c r="R170" s="17"/>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A171" s="37" t="s">
-        <v>182</v>
+      <c r="A171" s="40" t="s">
+        <v>181</v>
       </c>
       <c r="B171" s="11"/>
       <c r="C171" s="11"/>
@@ -3979,7 +4013,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B172" s="11"/>
       <c r="C172" s="11"/>
@@ -3991,7 +4025,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B173" s="11"/>
       <c r="C173" s="11"/>
@@ -3999,7 +4033,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A174" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B174" s="11"/>
       <c r="C174" s="11"/>
@@ -4010,15 +4044,15 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.45">
       <c r="A175" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B175" s="11"/>
       <c r="C175" s="11"/>
       <c r="D175" s="5"/>
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A176" s="38" t="s">
-        <v>187</v>
+      <c r="A176" s="34" t="s">
+        <v>186</v>
       </c>
       <c r="B176" s="11"/>
       <c r="C176" s="11"/>
@@ -4029,16 +4063,16 @@
       <c r="S176" s="17"/>
     </row>
     <row r="177" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A177" s="38" t="s">
-        <v>188</v>
+      <c r="A177" s="34" t="s">
+        <v>187</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="11"/>
       <c r="D177" s="5"/>
     </row>
     <row r="178" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A178" s="37" t="s">
-        <v>189</v>
+      <c r="A178" s="42" t="s">
+        <v>188</v>
       </c>
       <c r="B178" s="11"/>
       <c r="C178" s="11"/>
@@ -4049,16 +4083,16 @@
       <c r="S178" s="17"/>
     </row>
     <row r="179" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A179" s="37" t="s">
-        <v>190</v>
+      <c r="A179" s="42" t="s">
+        <v>189</v>
       </c>
       <c r="B179" s="11"/>
       <c r="C179" s="11"/>
       <c r="D179" s="5"/>
     </row>
     <row r="180" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A180" s="37" t="s">
-        <v>191</v>
+      <c r="A180" s="40" t="s">
+        <v>190</v>
       </c>
       <c r="B180" s="11"/>
       <c r="C180" s="11"/>
@@ -4069,8 +4103,8 @@
       <c r="S180" s="17"/>
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A181" s="37" t="s">
-        <v>192</v>
+      <c r="A181" s="40" t="s">
+        <v>191</v>
       </c>
       <c r="B181" s="11"/>
       <c r="C181" s="11"/>
@@ -4078,7 +4112,7 @@
     </row>
     <row r="182" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A182" s="8" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B182" s="11"/>
       <c r="C182" s="11"/>
@@ -4089,7 +4123,7 @@
     </row>
     <row r="183" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A183" s="8" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B183" s="11"/>
       <c r="C183" s="11"/>
@@ -4097,7 +4131,7 @@
     </row>
     <row r="184" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B184" s="11"/>
       <c r="C184" s="11"/>
@@ -4108,7 +4142,7 @@
     </row>
     <row r="185" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B185" s="11"/>
       <c r="C185" s="11"/>
@@ -4116,7 +4150,7 @@
     </row>
     <row r="186" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A186" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B186" s="11"/>
       <c r="C186" s="11"/>
@@ -4127,15 +4161,15 @@
     </row>
     <row r="187" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A187" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B187" s="11"/>
       <c r="C187" s="11"/>
       <c r="D187" s="5"/>
     </row>
     <row r="188" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A188" s="37" t="s">
-        <v>199</v>
+      <c r="A188" s="44" t="s">
+        <v>198</v>
       </c>
       <c r="B188" s="11"/>
       <c r="C188" s="11"/>
@@ -4145,8 +4179,8 @@
       <c r="S188" s="17"/>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A189" s="37" t="s">
-        <v>200</v>
+      <c r="A189" s="44" t="s">
+        <v>199</v>
       </c>
       <c r="B189" s="11"/>
       <c r="C189" s="11"/>
@@ -4154,7 +4188,7 @@
     </row>
     <row r="190" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B190" s="11"/>
       <c r="C190" s="11"/>
@@ -4166,7 +4200,7 @@
     </row>
     <row r="191" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B191" s="11"/>
       <c r="C191" s="11"/>
@@ -4174,7 +4208,7 @@
     </row>
     <row r="192" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A192" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B192" s="11"/>
       <c r="C192" s="11"/>
@@ -4185,7 +4219,7 @@
     </row>
     <row r="193" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A193" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B193" s="11"/>
       <c r="C193" s="11"/>
@@ -4193,7 +4227,7 @@
     </row>
     <row r="194" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A194" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B194" s="11"/>
       <c r="C194" s="11"/>
@@ -4204,7 +4238,7 @@
     </row>
     <row r="195" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A195" s="8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B195" s="11"/>
       <c r="C195" s="11"/>
@@ -4212,7 +4246,7 @@
     </row>
     <row r="196" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A196" s="8" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B196" s="11"/>
       <c r="C196" s="11"/>
@@ -4223,15 +4257,15 @@
     </row>
     <row r="197" spans="1:22" x14ac:dyDescent="0.45">
       <c r="A197" s="8" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B197" s="11"/>
       <c r="C197" s="11"/>
       <c r="D197" s="5"/>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A198" s="37" t="s">
-        <v>209</v>
+      <c r="A198" s="44" t="s">
+        <v>208</v>
       </c>
       <c r="B198" s="11"/>
       <c r="C198" s="11"/>
@@ -4241,8 +4275,8 @@
       <c r="T198" s="17"/>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A199" s="37" t="s">
-        <v>210</v>
+      <c r="A199" s="44" t="s">
+        <v>209</v>
       </c>
       <c r="B199" s="11"/>
       <c r="C199" s="11"/>
@@ -4250,7 +4284,7 @@
     </row>
     <row r="200" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A200" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B200" s="11"/>
       <c r="C200" s="11"/>
@@ -4261,16 +4295,16 @@
       <c r="U200" s="18"/>
     </row>
     <row r="201" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A201" s="36" t="s">
-        <v>212</v>
+      <c r="A201" s="41" t="s">
+        <v>211</v>
       </c>
       <c r="B201" s="11"/>
       <c r="C201" s="11"/>
       <c r="D201" s="5"/>
     </row>
     <row r="202" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A202" s="37" t="s">
-        <v>213</v>
+      <c r="A202" s="40" t="s">
+        <v>212</v>
       </c>
       <c r="B202" s="11"/>
       <c r="C202" s="11"/>
@@ -4280,16 +4314,16 @@
       <c r="T202" s="18"/>
     </row>
     <row r="203" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A203" s="37" t="s">
-        <v>214</v>
+      <c r="A203" s="40" t="s">
+        <v>213</v>
       </c>
       <c r="B203" s="11"/>
       <c r="C203" s="11"/>
       <c r="D203" s="5"/>
     </row>
     <row r="204" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A204" s="37" t="s">
-        <v>215</v>
+      <c r="A204" s="40" t="s">
+        <v>214</v>
       </c>
       <c r="B204" s="11"/>
       <c r="C204" s="11"/>
@@ -4299,16 +4333,16 @@
       <c r="U204" s="17"/>
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A205" s="37" t="s">
-        <v>216</v>
+      <c r="A205" s="40" t="s">
+        <v>215</v>
       </c>
       <c r="B205" s="11"/>
       <c r="C205" s="11"/>
       <c r="D205" s="5"/>
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A206" s="37" t="s">
-        <v>217</v>
+      <c r="A206" s="40" t="s">
+        <v>216</v>
       </c>
       <c r="B206" s="11"/>
       <c r="C206" s="11"/>
@@ -4318,16 +4352,16 @@
       <c r="U206" s="17"/>
     </row>
     <row r="207" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A207" s="37" t="s">
-        <v>218</v>
+      <c r="A207" s="40" t="s">
+        <v>217</v>
       </c>
       <c r="B207" s="11"/>
       <c r="C207" s="11"/>
       <c r="D207" s="5"/>
     </row>
     <row r="208" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A208" s="36" t="s">
-        <v>219</v>
+      <c r="A208" s="43" t="s">
+        <v>218</v>
       </c>
       <c r="B208" s="11"/>
       <c r="C208" s="11"/>
@@ -4338,8 +4372,8 @@
       <c r="V208" s="17"/>
     </row>
     <row r="209" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A209" s="36" t="s">
-        <v>220</v>
+      <c r="A209" s="43" t="s">
+        <v>219</v>
       </c>
       <c r="B209" s="11"/>
       <c r="C209" s="11"/>
@@ -4349,16 +4383,16 @@
       <c r="U209" s="17"/>
     </row>
     <row r="210" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A210" s="36" t="s">
-        <v>221</v>
+      <c r="A210" s="43" t="s">
+        <v>220</v>
       </c>
       <c r="B210" s="11"/>
       <c r="C210" s="11"/>
       <c r="D210" s="5"/>
     </row>
     <row r="211" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A211" s="36" t="s">
-        <v>222</v>
+      <c r="A211" s="43" t="s">
+        <v>221</v>
       </c>
       <c r="B211" s="11"/>
       <c r="C211" s="11"/>
@@ -4368,8 +4402,8 @@
       <c r="V211" s="17"/>
     </row>
     <row r="212" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A212" s="36" t="s">
-        <v>223</v>
+      <c r="A212" s="43" t="s">
+        <v>222</v>
       </c>
       <c r="B212" s="11"/>
       <c r="C212" s="11"/>
@@ -4377,7 +4411,7 @@
     </row>
     <row r="213" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B213" s="12"/>
       <c r="C213" s="12"/>
@@ -4397,7 +4431,7 @@
     </row>
     <row r="214" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A214" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B214" s="11"/>
       <c r="C214" s="11"/>
@@ -4405,7 +4439,7 @@
     </row>
     <row r="215" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A215" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B215" s="11"/>
       <c r="C215" s="11"/>
@@ -4413,7 +4447,7 @@
     </row>
     <row r="216" spans="1:41" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B216" s="12"/>
       <c r="C216" s="12"/>
@@ -4434,7 +4468,7 @@
     </row>
     <row r="217" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A217" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B217" s="11"/>
       <c r="C217" s="11"/>
@@ -4442,7 +4476,7 @@
     </row>
     <row r="218" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A218" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B218" s="11"/>
       <c r="C218" s="11"/>
@@ -4450,7 +4484,7 @@
     </row>
     <row r="219" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A219" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B219" s="11"/>
       <c r="C219" s="11"/>
@@ -4458,7 +4492,7 @@
     </row>
     <row r="220" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A220" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B220" s="11"/>
       <c r="C220" s="11"/>
@@ -4466,7 +4500,7 @@
     </row>
     <row r="221" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A221" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B221" s="11"/>
       <c r="C221" s="11"/>
@@ -4474,7 +4508,7 @@
     </row>
     <row r="222" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A222" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B222" s="11"/>
       <c r="C222" s="11"/>
@@ -4482,7 +4516,7 @@
     </row>
     <row r="223" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A223" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B223" s="11"/>
       <c r="C223" s="11"/>
@@ -4490,7 +4524,7 @@
     </row>
     <row r="224" spans="1:41" x14ac:dyDescent="0.45">
       <c r="A224" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B224" s="11"/>
       <c r="C224" s="11"/>
@@ -4498,7 +4532,7 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A225" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B225" s="11"/>
       <c r="C225" s="11"/>
@@ -4506,7 +4540,7 @@
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A226" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B226" s="11"/>
       <c r="C226" s="11"/>
@@ -4596,19 +4630,19 @@
   <sheetData>
     <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="s">
-        <v>244</v>
-      </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="23">
         <v>45778</v>
@@ -4709,12 +4743,12 @@
         <v>3</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C4" s="24"/>
       <c r="D4" s="24"/>
       <c r="E4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -4753,7 +4787,7 @@
         <v>3.1</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
@@ -4791,10 +4825,10 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C6" s="24">
         <v>45789</v>
@@ -4836,10 +4870,10 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="26" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C7" s="24">
         <v>45789</v>
@@ -4881,10 +4915,10 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A8" s="26" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C8" s="24">
         <v>45790</v>
@@ -4926,10 +4960,10 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C9" s="24">
         <v>45790</v>
@@ -4971,10 +5005,10 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A10" s="26" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C10" s="24">
         <v>45796</v>
@@ -5016,10 +5050,10 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A11" s="26" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C11" s="24">
         <v>45796</v>
@@ -5061,10 +5095,10 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A12" s="26" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C12" s="24">
         <v>45799</v>
@@ -5106,10 +5140,10 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A13" s="26" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C13" s="24">
         <v>45798</v>
@@ -5151,10 +5185,10 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A14" s="26" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C14" s="24">
         <v>45803</v>
@@ -5196,10 +5230,10 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A15" s="26" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C15" s="24">
         <v>45805</v>
@@ -5241,10 +5275,10 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A16" s="26" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C16" s="24">
         <v>45805</v>
@@ -5286,10 +5320,10 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A17" s="26" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C17" s="24">
         <v>45806</v>
@@ -5331,10 +5365,10 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A18" s="26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C18" s="24">
         <v>45783</v>
@@ -5376,10 +5410,10 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A19" s="26" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C19" s="24">
         <v>45783</v>
@@ -5421,10 +5455,10 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A20" s="26" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C20" s="24">
         <v>45785</v>
@@ -5466,10 +5500,10 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A21" s="26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C21" s="24">
         <v>45782</v>
@@ -5511,10 +5545,10 @@
     </row>
     <row r="22" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A22" s="26" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C22" s="24">
         <v>45807</v>
@@ -5556,10 +5590,10 @@
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A23" s="26" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C23" s="24">
         <v>45807</v>
@@ -5601,10 +5635,10 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A24" s="26" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C24" s="24">
         <v>45804</v>
@@ -5649,7 +5683,7 @@
         <v>3.2</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C25" s="24"/>
       <c r="D25" s="24"/>
@@ -5687,10 +5721,10 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A26" s="26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
@@ -5728,10 +5762,10 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A27" s="26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
@@ -5769,10 +5803,10 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A28" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
@@ -5810,10 +5844,10 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A29" s="26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
@@ -5851,10 +5885,10 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A30" s="26" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
@@ -5892,10 +5926,10 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A31" s="26" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
@@ -5933,10 +5967,10 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A32" s="26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
@@ -5974,10 +6008,10 @@
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A33" s="26" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
@@ -6015,10 +6049,10 @@
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A34" s="26" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
@@ -6056,10 +6090,10 @@
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A35" s="26" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
@@ -6097,10 +6131,10 @@
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A36" s="26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
@@ -6138,10 +6172,10 @@
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A37" s="26" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
@@ -6179,10 +6213,10 @@
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A38" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
@@ -6220,10 +6254,10 @@
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A39" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C39" s="24"/>
       <c r="D39" s="24"/>
@@ -6261,10 +6295,10 @@
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A40" s="26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B40" s="26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
@@ -6302,10 +6336,10 @@
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A41" s="26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
@@ -6346,12 +6380,12 @@
         <v>4</v>
       </c>
       <c r="B42" s="25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C42" s="24"/>
       <c r="D42" s="24"/>
       <c r="E42" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F42" s="31"/>
       <c r="G42" s="30"/>
@@ -6390,7 +6424,7 @@
         <v>4.2</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C43" s="24"/>
       <c r="D43" s="24"/>
@@ -6428,10 +6462,10 @@
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A44" s="26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C44" s="24">
         <v>45801</v>
@@ -6471,10 +6505,10 @@
     </row>
     <row r="45" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A45" s="26" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C45" s="24">
         <v>45801</v>
@@ -6516,10 +6550,10 @@
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A46" s="26" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C46" s="24">
         <v>45801</v>
@@ -6561,10 +6595,10 @@
     </row>
     <row r="47" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A47" s="26" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C47" s="24">
         <v>45803</v>
@@ -6606,10 +6640,10 @@
     </row>
     <row r="48" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A48" s="26" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C48" s="24">
         <v>45803</v>
@@ -6651,10 +6685,10 @@
     </row>
     <row r="49" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A49" s="26" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C49" s="24">
         <v>45803</v>
@@ -6696,10 +6730,10 @@
     </row>
     <row r="50" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A50" s="26" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C50" s="24">
         <v>45803</v>
@@ -6741,10 +6775,10 @@
     </row>
     <row r="51" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A51" s="26" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C51" s="24">
         <v>45803</v>
@@ -6786,10 +6820,10 @@
     </row>
     <row r="52" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A52" s="26" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B52" s="26" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C52" s="24">
         <v>45804</v>
@@ -6831,10 +6865,10 @@
     </row>
     <row r="53" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A53" s="26" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C53" s="24">
         <v>45805</v>
@@ -6876,10 +6910,10 @@
     </row>
     <row r="54" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A54" s="26" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C54" s="24"/>
       <c r="D54" s="24"/>
@@ -6917,10 +6951,10 @@
     </row>
     <row r="55" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A55" s="26" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C55" s="24"/>
       <c r="D55" s="24"/>
@@ -6958,10 +6992,10 @@
     </row>
     <row r="56" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A56" s="26" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B56" s="26" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C56" s="24"/>
       <c r="D56" s="24"/>
@@ -6999,10 +7033,10 @@
     </row>
     <row r="57" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A57" s="26" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C57" s="24"/>
       <c r="D57" s="24"/>
@@ -7040,10 +7074,10 @@
     </row>
     <row r="58" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A58" s="26" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C58" s="24"/>
       <c r="D58" s="24"/>
@@ -7081,10 +7115,10 @@
     </row>
     <row r="59" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A59" s="26" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C59" s="24">
         <v>45792</v>
@@ -7126,10 +7160,10 @@
     </row>
     <row r="60" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A60" s="26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C60" s="24">
         <v>45792</v>
@@ -7171,10 +7205,10 @@
     </row>
     <row r="61" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A61" s="26" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C61" s="24">
         <v>45798</v>
@@ -7216,10 +7250,10 @@
     </row>
     <row r="62" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A62" s="26" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B62" s="26" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C62" s="24"/>
       <c r="D62" s="24"/>
@@ -7257,10 +7291,10 @@
     </row>
     <row r="63" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A63" s="26" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C63" s="24"/>
       <c r="D63" s="24"/>
@@ -7298,10 +7332,10 @@
     </row>
     <row r="64" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A64" s="26" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B64" s="26" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C64" s="24"/>
       <c r="D64" s="24"/>
@@ -7339,10 +7373,10 @@
     </row>
     <row r="65" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A65" s="26" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C65" s="24"/>
       <c r="D65" s="24"/>
@@ -7383,7 +7417,7 @@
         <v>4.3</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C66" s="24"/>
       <c r="D66" s="24"/>
@@ -7421,10 +7455,10 @@
     </row>
     <row r="67" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A67" s="26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C67" s="24"/>
       <c r="D67" s="24"/>
@@ -7462,10 +7496,10 @@
     </row>
     <row r="68" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A68" s="26" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C68" s="24"/>
       <c r="D68" s="24"/>
@@ -7503,10 +7537,10 @@
     </row>
     <row r="69" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A69" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="B69" s="26" t="s">
         <v>308</v>
-      </c>
-      <c r="B69" s="26" t="s">
-        <v>309</v>
       </c>
       <c r="C69" s="24"/>
       <c r="D69" s="24"/>
@@ -7649,19 +7683,19 @@
   <sheetData>
     <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="s">
-        <v>244</v>
-      </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="23">
         <v>45809</v>
@@ -7757,10 +7791,10 @@
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A4" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C4" s="24">
         <v>45809</v>
@@ -7769,7 +7803,7 @@
         <v>45828</v>
       </c>
       <c r="E4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
@@ -7805,10 +7839,10 @@
     </row>
     <row r="5" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A5" s="26" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C5" s="24">
         <v>45809</v>
@@ -7817,7 +7851,7 @@
         <v>45809</v>
       </c>
       <c r="E5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
@@ -7853,10 +7887,10 @@
     </row>
     <row r="6" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A6" s="26" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C6" s="24">
         <v>45810</v>
@@ -7865,7 +7899,7 @@
         <v>45810</v>
       </c>
       <c r="E6" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
@@ -7901,10 +7935,10 @@
     </row>
     <row r="7" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A7" s="26" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C7" s="24">
         <v>45810</v>
@@ -7913,7 +7947,7 @@
         <v>45828</v>
       </c>
       <c r="E7" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
@@ -7949,7 +7983,7 @@
     </row>
     <row r="8" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B8" s="26" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C8" s="24">
         <v>45811</v>
@@ -7991,7 +8025,7 @@
     </row>
     <row r="9" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B9" s="26" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C9" s="24"/>
       <c r="D9" s="24"/>
@@ -8029,7 +8063,7 @@
     </row>
     <row r="10" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B10" s="26" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C10" s="24">
         <v>45813</v>
@@ -8071,7 +8105,7 @@
     </row>
     <row r="11" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B11" s="26" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="C11" s="24">
         <v>45814</v>
@@ -8113,7 +8147,7 @@
     </row>
     <row r="12" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B12" s="26" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C12" s="24">
         <v>45815</v>
@@ -8155,7 +8189,7 @@
     </row>
     <row r="13" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B13" s="26" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C13" s="24">
         <v>45817</v>
@@ -8197,7 +8231,7 @@
     </row>
     <row r="14" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B14" s="26" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C14" s="24">
         <v>45820</v>
@@ -8239,7 +8273,7 @@
     </row>
     <row r="15" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B15" s="26" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C15" s="24">
         <v>45822</v>
@@ -8281,7 +8315,7 @@
     </row>
     <row r="16" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B16" s="26" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C16" s="24">
         <v>45824</v>
@@ -8323,7 +8357,7 @@
     </row>
     <row r="17" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B17" s="26" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C17" s="24">
         <v>45826</v>
@@ -8365,7 +8399,7 @@
     </row>
     <row r="18" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B18" s="26" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C18" s="24">
         <v>45828</v>
@@ -8407,7 +8441,7 @@
     </row>
     <row r="19" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B19" s="26" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C19" s="24">
         <v>45813</v>
@@ -8449,7 +8483,7 @@
     </row>
     <row r="20" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B20" s="26" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C20" s="24">
         <v>45830</v>
@@ -8491,7 +8525,7 @@
     </row>
     <row r="21" spans="1:36" x14ac:dyDescent="0.45">
       <c r="B21" s="26" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C21" s="24">
         <v>45831</v>
@@ -8536,12 +8570,12 @@
         <v>4.3</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
       <c r="E22" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="30"/>
@@ -8577,15 +8611,15 @@
     </row>
     <row r="23" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A23" s="26" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B23" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C23" s="24"/>
       <c r="D23" s="24"/>
       <c r="E23" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="30"/>
@@ -8621,15 +8655,15 @@
     </row>
     <row r="24" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A24" s="26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C24" s="24"/>
       <c r="D24" s="24"/>
       <c r="E24" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="30"/>
@@ -8665,15 +8699,15 @@
     </row>
     <row r="25" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A25" s="26" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C25" s="24"/>
       <c r="D25" s="24"/>
       <c r="E25" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="30"/>
@@ -8709,15 +8743,15 @@
     </row>
     <row r="26" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A26" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C26" s="24"/>
       <c r="D26" s="24"/>
       <c r="E26" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F26" s="30"/>
       <c r="G26" s="30"/>
@@ -8753,15 +8787,15 @@
     </row>
     <row r="27" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A27" s="26" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C27" s="24"/>
       <c r="D27" s="24"/>
       <c r="E27" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F27" s="31"/>
       <c r="G27" s="30"/>
@@ -8797,15 +8831,15 @@
     </row>
     <row r="28" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A28" s="26" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C28" s="24"/>
       <c r="D28" s="24"/>
       <c r="E28" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F28" s="31"/>
       <c r="G28" s="30"/>
@@ -8841,15 +8875,15 @@
     </row>
     <row r="29" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A29" s="26" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C29" s="24"/>
       <c r="D29" s="24"/>
       <c r="E29" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F29" s="30"/>
       <c r="G29" s="30"/>
@@ -8885,15 +8919,15 @@
     </row>
     <row r="30" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A30" s="26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C30" s="24"/>
       <c r="D30" s="24"/>
       <c r="E30" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F30" s="31"/>
       <c r="G30" s="30"/>
@@ -8929,15 +8963,15 @@
     </row>
     <row r="31" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A31" s="26" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C31" s="24"/>
       <c r="D31" s="24"/>
       <c r="E31" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F31" s="30"/>
       <c r="G31" s="30"/>
@@ -8973,15 +9007,15 @@
     </row>
     <row r="32" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A32" s="26" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C32" s="24"/>
       <c r="D32" s="24"/>
       <c r="E32" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F32" s="30"/>
       <c r="G32" s="30"/>
@@ -9017,15 +9051,15 @@
     </row>
     <row r="33" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A33" s="26" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B33" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C33" s="24"/>
       <c r="D33" s="24"/>
       <c r="E33" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F33" s="30"/>
       <c r="G33" s="30"/>
@@ -9061,15 +9095,15 @@
     </row>
     <row r="34" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A34" s="26" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C34" s="24"/>
       <c r="D34" s="24"/>
       <c r="E34" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F34" s="30"/>
       <c r="G34" s="30"/>
@@ -9105,15 +9139,15 @@
     </row>
     <row r="35" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A35" s="26" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C35" s="24"/>
       <c r="D35" s="24"/>
       <c r="E35" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F35" s="30"/>
       <c r="G35" s="30"/>
@@ -9149,15 +9183,15 @@
     </row>
     <row r="36" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A36" s="26" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B36" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C36" s="24"/>
       <c r="D36" s="24"/>
       <c r="E36" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F36" s="30"/>
       <c r="G36" s="30"/>
@@ -9193,15 +9227,15 @@
     </row>
     <row r="37" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A37" s="26" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C37" s="24"/>
       <c r="D37" s="24"/>
       <c r="E37" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F37" s="30"/>
       <c r="G37" s="30"/>
@@ -9237,15 +9271,15 @@
     </row>
     <row r="38" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A38" s="26" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B38" s="8" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C38" s="24"/>
       <c r="D38" s="24"/>
       <c r="E38" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F38" s="30"/>
       <c r="G38" s="30"/>
@@ -9281,15 +9315,15 @@
     </row>
     <row r="39" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A39" s="26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C39" s="24"/>
       <c r="D39" s="24"/>
       <c r="E39" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F39" s="30"/>
       <c r="G39" s="30"/>
@@ -9325,15 +9359,15 @@
     </row>
     <row r="40" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A40" s="26" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C40" s="24"/>
       <c r="D40" s="24"/>
       <c r="E40" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F40" s="30"/>
       <c r="G40" s="30"/>
@@ -9369,15 +9403,15 @@
     </row>
     <row r="41" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A41" s="26" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B41" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C41" s="24"/>
       <c r="D41" s="24"/>
       <c r="E41" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F41" s="30"/>
       <c r="G41" s="30"/>
@@ -9413,15 +9447,15 @@
     </row>
     <row r="42" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A42" s="26" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C42" s="24"/>
       <c r="D42" s="24"/>
       <c r="E42" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F42" s="30"/>
       <c r="G42" s="30"/>
@@ -9457,15 +9491,15 @@
     </row>
     <row r="43" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A43" s="26" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C43" s="24"/>
       <c r="D43" s="24"/>
       <c r="E43" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F43" s="30"/>
       <c r="G43" s="30"/>
@@ -9501,15 +9535,15 @@
     </row>
     <row r="44" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A44" s="26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C44" s="24"/>
       <c r="D44" s="24"/>
       <c r="E44" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F44" s="30"/>
       <c r="G44" s="30"/>
@@ -9548,12 +9582,12 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C45" s="24"/>
       <c r="D45" s="24"/>
       <c r="E45" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F45" s="30"/>
       <c r="G45" s="30"/>
@@ -9589,15 +9623,15 @@
     </row>
     <row r="46" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A46" s="26" t="s">
+        <v>371</v>
+      </c>
+      <c r="B46" t="s">
         <v>372</v>
-      </c>
-      <c r="B46" t="s">
-        <v>373</v>
       </c>
       <c r="C46" s="24"/>
       <c r="D46" s="24"/>
       <c r="E46" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F46" s="30"/>
       <c r="G46" s="30"/>
@@ -9782,19 +9816,19 @@
   <sheetData>
     <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="s">
-        <v>244</v>
-      </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="23">
         <v>45839</v>
@@ -9907,19 +9941,19 @@
   <sheetData>
     <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="s">
-        <v>244</v>
-      </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="23">
         <v>45870</v>
@@ -10032,19 +10066,19 @@
   <sheetData>
     <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="s">
-        <v>244</v>
-      </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="23">
         <v>45901</v>
@@ -10155,19 +10189,19 @@
   <sheetData>
     <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="s">
-        <v>244</v>
-      </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="23">
         <v>45931</v>
@@ -10280,19 +10314,19 @@
   <sheetData>
     <row r="3" spans="1:36" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D3" t="s">
         <v>243</v>
       </c>
-      <c r="D3" t="s">
-        <v>244</v>
-      </c>
       <c r="E3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F3" s="23">
         <v>45962</v>

--- a/간트차트_250526.xlsx
+++ b/간트차트_250526.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\typar\OneDrive\바탕 화면\storage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9AF8C19-18C3-4F23-A6D4-28B47F139962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B65901-B6C7-488D-B59B-F4EB066C9074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="간트 차트 시각화" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="654" uniqueCount="394">
   <si>
     <t>3월</t>
   </si>
@@ -1340,6 +1340,10 @@
   <si>
     <t xml:space="preserve">하늘색: 당연적  자주: 일차원적
 분홍: 매력적   노랑: 미완 주황: 삭제   </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>업적 추가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1369,7 +1373,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1445,6 +1449,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1566,7 +1576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1621,12 +1631,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1642,6 +1646,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -2063,7 +2076,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BE226"/>
+  <dimension ref="A1:BE228"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="31.58203125" customWidth="1"/>
@@ -2078,69 +2091,69 @@
       <c r="D1"/>
     </row>
     <row r="2" spans="1:57" ht="34" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="37" t="s">
         <v>392</v>
       </c>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
       <c r="D2" s="14"/>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="36" t="s">
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="43" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="36" t="s">
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="43" t="s">
         <v>2</v>
       </c>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="36" t="s">
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="36" t="s">
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="36" t="s">
+      <c r="W2" s="44"/>
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+      <c r="Z2" s="44"/>
+      <c r="AA2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="36" t="s">
+      <c r="AB2" s="44"/>
+      <c r="AC2" s="44"/>
+      <c r="AD2" s="44"/>
+      <c r="AE2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="37"/>
-      <c r="AI2" s="36" t="s">
+      <c r="AF2" s="44"/>
+      <c r="AG2" s="44"/>
+      <c r="AH2" s="44"/>
+      <c r="AI2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="AJ2" s="37"/>
-      <c r="AK2" s="37"/>
-      <c r="AL2" s="37"/>
-      <c r="AM2" s="37"/>
-      <c r="AN2" s="36" t="s">
+      <c r="AJ2" s="44"/>
+      <c r="AK2" s="44"/>
+      <c r="AL2" s="44"/>
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="AO2" s="37"/>
-      <c r="AP2" s="37"/>
-      <c r="AQ2" s="37"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="44"/>
     </row>
     <row r="3" spans="1:57" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
@@ -2453,7 +2466,7 @@
       <c r="E15" s="17"/>
     </row>
     <row r="16" spans="1:57" x14ac:dyDescent="0.45">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="38" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="11"/>
@@ -2461,7 +2474,7 @@
       <c r="D16" s="5"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="34" t="s">
         <v>29</v>
       </c>
       <c r="B17" s="11"/>
@@ -2472,7 +2485,7 @@
       <c r="E17" s="17"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="34" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="11"/>
@@ -2500,7 +2513,7 @@
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="41" t="s">
         <v>33</v>
       </c>
       <c r="B21" s="11"/>
@@ -2514,7 +2527,7 @@
       <c r="K21" s="17"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="41" t="s">
         <v>34</v>
       </c>
       <c r="B22" s="11"/>
@@ -2522,7 +2535,7 @@
       <c r="D22" s="5"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="41" t="s">
         <v>35</v>
       </c>
       <c r="B23" s="11"/>
@@ -2536,7 +2549,7 @@
       <c r="K23" s="17"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A24" s="43" t="s">
+      <c r="A24" s="41" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="11"/>
@@ -2603,7 +2616,7 @@
       <c r="D29" s="5"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A30" s="38" t="s">
+      <c r="A30" s="36" t="s">
         <v>42</v>
       </c>
       <c r="B30" s="11"/>
@@ -2615,7 +2628,7 @@
       <c r="F30" s="17"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.45">
-      <c r="A31" s="38" t="s">
+      <c r="A31" s="36" t="s">
         <v>43</v>
       </c>
       <c r="B31" s="11"/>
@@ -3672,7 +3685,7 @@
       <c r="D136" s="5"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A137" s="40" t="s">
+      <c r="A137" s="34" t="s">
         <v>148</v>
       </c>
       <c r="B137" s="11"/>
@@ -3683,7 +3696,7 @@
       <c r="N137" s="17"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A138" s="40" t="s">
+      <c r="A138" s="34" t="s">
         <v>149</v>
       </c>
       <c r="B138" s="11"/>
@@ -3691,7 +3704,7 @@
       <c r="D138" s="5"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A139" s="42" t="s">
+      <c r="A139" s="34" t="s">
         <v>150</v>
       </c>
       <c r="B139" s="11"/>
@@ -3702,7 +3715,7 @@
       <c r="N139" s="17"/>
     </row>
     <row r="140" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A140" s="42" t="s">
+      <c r="A140" s="34" t="s">
         <v>391</v>
       </c>
       <c r="B140" s="11"/>
@@ -3710,7 +3723,7 @@
       <c r="D140" s="5"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A141" s="42" t="s">
+      <c r="A141" s="34" t="s">
         <v>151</v>
       </c>
       <c r="B141" s="11"/>
@@ -3721,7 +3734,7 @@
       <c r="N141" s="17"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.45">
-      <c r="A142" s="42" t="s">
+      <c r="A142" s="34" t="s">
         <v>152</v>
       </c>
       <c r="B142" s="11"/>
@@ -3748,7 +3761,7 @@
       <c r="D144" s="5"/>
     </row>
     <row r="145" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A145" s="40" t="s">
+      <c r="A145" s="34" t="s">
         <v>155</v>
       </c>
       <c r="B145" s="11"/>
@@ -3759,7 +3772,7 @@
       <c r="O145" s="17"/>
     </row>
     <row r="146" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A146" s="40" t="s">
+      <c r="A146" s="34" t="s">
         <v>156</v>
       </c>
       <c r="B146" s="11"/>
@@ -3767,7 +3780,7 @@
       <c r="D146" s="5"/>
     </row>
     <row r="147" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A147" s="42" t="s">
+      <c r="A147" s="34" t="s">
         <v>157</v>
       </c>
       <c r="B147" s="11"/>
@@ -3778,7 +3791,7 @@
       <c r="O147" s="17"/>
     </row>
     <row r="148" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A148" s="42" t="s">
+      <c r="A148" s="34" t="s">
         <v>158</v>
       </c>
       <c r="B148" s="11"/>
@@ -3805,7 +3818,7 @@
       <c r="D150" s="5"/>
     </row>
     <row r="151" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A151" s="40" t="s">
+      <c r="A151" s="38" t="s">
         <v>161</v>
       </c>
       <c r="B151" s="11"/>
@@ -3816,7 +3829,7 @@
       <c r="O151" s="17"/>
     </row>
     <row r="152" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A152" s="40" t="s">
+      <c r="A152" s="38" t="s">
         <v>162</v>
       </c>
       <c r="B152" s="11"/>
@@ -3824,7 +3837,7 @@
       <c r="D152" s="5"/>
     </row>
     <row r="153" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A153" s="34" t="s">
+      <c r="A153" s="45" t="s">
         <v>163</v>
       </c>
       <c r="B153" s="11"/>
@@ -3835,7 +3848,7 @@
       <c r="O153" s="17"/>
     </row>
     <row r="154" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A154" s="34" t="s">
+      <c r="A154" s="45" t="s">
         <v>164</v>
       </c>
       <c r="B154" s="11"/>
@@ -3881,7 +3894,7 @@
       <c r="D158" s="5"/>
     </row>
     <row r="159" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A159" s="34" t="s">
+      <c r="A159" s="45" t="s">
         <v>169</v>
       </c>
       <c r="B159" s="11"/>
@@ -3892,7 +3905,7 @@
       <c r="P159" s="17"/>
     </row>
     <row r="160" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A160" s="34" t="s">
+      <c r="A160" s="45" t="s">
         <v>170</v>
       </c>
       <c r="B160" s="11"/>
@@ -3900,7 +3913,7 @@
       <c r="D160" s="5"/>
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A161" s="34" t="s">
+      <c r="A161" s="42" t="s">
         <v>171</v>
       </c>
       <c r="B161" s="11"/>
@@ -3911,7 +3924,7 @@
       <c r="P161" s="17"/>
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A162" s="34" t="s">
+      <c r="A162" s="42" t="s">
         <v>172</v>
       </c>
       <c r="B162" s="11"/>
@@ -3993,7 +4006,7 @@
       <c r="D169" s="5"/>
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A170" s="40" t="s">
+      <c r="A170" s="38" t="s">
         <v>180</v>
       </c>
       <c r="B170" s="11"/>
@@ -4004,7 +4017,7 @@
       <c r="R170" s="17"/>
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.45">
-      <c r="A171" s="40" t="s">
+      <c r="A171" s="38" t="s">
         <v>181</v>
       </c>
       <c r="B171" s="11"/>
@@ -4071,7 +4084,7 @@
       <c r="D177" s="5"/>
     </row>
     <row r="178" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A178" s="42" t="s">
+      <c r="A178" s="40" t="s">
         <v>188</v>
       </c>
       <c r="B178" s="11"/>
@@ -4083,7 +4096,7 @@
       <c r="S178" s="17"/>
     </row>
     <row r="179" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A179" s="42" t="s">
+      <c r="A179" s="40" t="s">
         <v>189</v>
       </c>
       <c r="B179" s="11"/>
@@ -4091,7 +4104,7 @@
       <c r="D179" s="5"/>
     </row>
     <row r="180" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A180" s="40" t="s">
+      <c r="A180" s="38" t="s">
         <v>190</v>
       </c>
       <c r="B180" s="11"/>
@@ -4103,7 +4116,7 @@
       <c r="S180" s="17"/>
     </row>
     <row r="181" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A181" s="40" t="s">
+      <c r="A181" s="38" t="s">
         <v>191</v>
       </c>
       <c r="B181" s="11"/>
@@ -4168,7 +4181,7 @@
       <c r="D187" s="5"/>
     </row>
     <row r="188" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A188" s="44" t="s">
+      <c r="A188" s="42" t="s">
         <v>198</v>
       </c>
       <c r="B188" s="11"/>
@@ -4179,7 +4192,7 @@
       <c r="S188" s="17"/>
     </row>
     <row r="189" spans="1:20" x14ac:dyDescent="0.45">
-      <c r="A189" s="44" t="s">
+      <c r="A189" s="42" t="s">
         <v>199</v>
       </c>
       <c r="B189" s="11"/>
@@ -4264,7 +4277,7 @@
       <c r="D197" s="5"/>
     </row>
     <row r="198" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A198" s="44" t="s">
+      <c r="A198" s="42" t="s">
         <v>208</v>
       </c>
       <c r="B198" s="11"/>
@@ -4275,7 +4288,7 @@
       <c r="T198" s="17"/>
     </row>
     <row r="199" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A199" s="44" t="s">
+      <c r="A199" s="42" t="s">
         <v>209</v>
       </c>
       <c r="B199" s="11"/>
@@ -4295,7 +4308,7 @@
       <c r="U200" s="18"/>
     </row>
     <row r="201" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A201" s="41" t="s">
+      <c r="A201" s="39" t="s">
         <v>211</v>
       </c>
       <c r="B201" s="11"/>
@@ -4303,7 +4316,7 @@
       <c r="D201" s="5"/>
     </row>
     <row r="202" spans="1:22" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A202" s="40" t="s">
+      <c r="A202" s="38" t="s">
         <v>212</v>
       </c>
       <c r="B202" s="11"/>
@@ -4314,7 +4327,7 @@
       <c r="T202" s="18"/>
     </row>
     <row r="203" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A203" s="40" t="s">
+      <c r="A203" s="38" t="s">
         <v>213</v>
       </c>
       <c r="B203" s="11"/>
@@ -4322,7 +4335,7 @@
       <c r="D203" s="5"/>
     </row>
     <row r="204" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A204" s="40" t="s">
+      <c r="A204" s="38" t="s">
         <v>214</v>
       </c>
       <c r="B204" s="11"/>
@@ -4333,7 +4346,7 @@
       <c r="U204" s="17"/>
     </row>
     <row r="205" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A205" s="40" t="s">
+      <c r="A205" s="38" t="s">
         <v>215</v>
       </c>
       <c r="B205" s="11"/>
@@ -4341,7 +4354,7 @@
       <c r="D205" s="5"/>
     </row>
     <row r="206" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A206" s="40" t="s">
+      <c r="A206" s="38" t="s">
         <v>216</v>
       </c>
       <c r="B206" s="11"/>
@@ -4352,7 +4365,7 @@
       <c r="U206" s="17"/>
     </row>
     <row r="207" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A207" s="40" t="s">
+      <c r="A207" s="38" t="s">
         <v>217</v>
       </c>
       <c r="B207" s="11"/>
@@ -4360,7 +4373,7 @@
       <c r="D207" s="5"/>
     </row>
     <row r="208" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A208" s="43" t="s">
+      <c r="A208" s="41" t="s">
         <v>218</v>
       </c>
       <c r="B208" s="11"/>
@@ -4372,7 +4385,7 @@
       <c r="V208" s="17"/>
     </row>
     <row r="209" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A209" s="43" t="s">
+      <c r="A209" s="41" t="s">
         <v>219</v>
       </c>
       <c r="B209" s="11"/>
@@ -4383,7 +4396,7 @@
       <c r="U209" s="17"/>
     </row>
     <row r="210" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A210" s="43" t="s">
+      <c r="A210" s="41" t="s">
         <v>220</v>
       </c>
       <c r="B210" s="11"/>
@@ -4391,7 +4404,7 @@
       <c r="D210" s="5"/>
     </row>
     <row r="211" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A211" s="43" t="s">
+      <c r="A211" s="41" t="s">
         <v>221</v>
       </c>
       <c r="B211" s="11"/>
@@ -4402,7 +4415,7 @@
       <c r="V211" s="17"/>
     </row>
     <row r="212" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A212" s="43" t="s">
+      <c r="A212" s="41" t="s">
         <v>222</v>
       </c>
       <c r="B212" s="11"/>
@@ -4483,7 +4496,7 @@
       <c r="D218" s="5"/>
     </row>
     <row r="219" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A219" t="s">
+      <c r="A219" s="35" t="s">
         <v>229</v>
       </c>
       <c r="B219" s="11"/>
@@ -4491,7 +4504,7 @@
       <c r="D219" s="5"/>
     </row>
     <row r="220" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A220" t="s">
+      <c r="A220" s="35" t="s">
         <v>230</v>
       </c>
       <c r="B220" s="11"/>
@@ -4499,7 +4512,7 @@
       <c r="D220" s="5"/>
     </row>
     <row r="221" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A221" t="s">
+      <c r="A221" s="35" t="s">
         <v>231</v>
       </c>
       <c r="B221" s="11"/>
@@ -4507,7 +4520,7 @@
       <c r="D221" s="5"/>
     </row>
     <row r="222" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A222" t="s">
+      <c r="A222" s="35" t="s">
         <v>232</v>
       </c>
       <c r="B222" s="11"/>
@@ -4515,7 +4528,7 @@
       <c r="D222" s="5"/>
     </row>
     <row r="223" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A223" t="s">
+      <c r="A223" s="35" t="s">
         <v>233</v>
       </c>
       <c r="B223" s="11"/>
@@ -4523,7 +4536,7 @@
       <c r="D223" s="5"/>
     </row>
     <row r="224" spans="1:41" x14ac:dyDescent="0.45">
-      <c r="A224" t="s">
+      <c r="A224" s="35" t="s">
         <v>234</v>
       </c>
       <c r="B224" s="11"/>
@@ -4531,7 +4544,7 @@
       <c r="D224" s="5"/>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A225" t="s">
+      <c r="A225" s="35" t="s">
         <v>235</v>
       </c>
       <c r="B225" s="11"/>
@@ -4539,12 +4552,17 @@
       <c r="D225" s="5"/>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A226" t="s">
+      <c r="A226" s="35" t="s">
         <v>236</v>
       </c>
       <c r="B226" s="11"/>
       <c r="C226" s="11"/>
       <c r="D226" s="5"/>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A228" s="41" t="s">
+        <v>393</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
